--- a/artfynd/A 12276-2023 artfynd.xlsx
+++ b/artfynd/A 12276-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY129"/>
+  <dimension ref="A1:AY130"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14230,6 +14230,122 @@
       </c>
       <c r="AY129" t="inlineStr"/>
     </row>
+    <row r="130">
+      <c r="A130" t="n">
+        <v>113544517</v>
+      </c>
+      <c r="B130" t="n">
+        <v>97349</v>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E130" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I130" t="inlineStr"/>
+      <c r="J130" t="inlineStr"/>
+      <c r="K130" t="inlineStr"/>
+      <c r="L130" t="inlineStr"/>
+      <c r="N130" t="inlineStr"/>
+      <c r="P130" t="inlineStr">
+        <is>
+          <t>Rörbo ca 1 km N om (3) (knärot), Vstm</t>
+        </is>
+      </c>
+      <c r="Q130" t="n">
+        <v>572281</v>
+      </c>
+      <c r="R130" t="n">
+        <v>6634886</v>
+      </c>
+      <c r="S130" t="n">
+        <v>10</v>
+      </c>
+      <c r="T130" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U130" t="inlineStr">
+        <is>
+          <t>Sala</t>
+        </is>
+      </c>
+      <c r="V130" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W130" t="inlineStr">
+        <is>
+          <t>Fläckebo</t>
+        </is>
+      </c>
+      <c r="X130" t="inlineStr">
+        <is>
+          <t>U-Sal-0788</t>
+        </is>
+      </c>
+      <c r="Y130" t="inlineStr">
+        <is>
+          <t>2023-09-23</t>
+        </is>
+      </c>
+      <c r="AA130" t="inlineStr">
+        <is>
+          <t>2023-09-23</t>
+        </is>
+      </c>
+      <c r="AD130" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE130" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF130" t="inlineStr"/>
+      <c r="AG130" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT130" t="inlineStr"/>
+      <c r="AW130" t="inlineStr">
+        <is>
+          <t>Bo Eriksson</t>
+        </is>
+      </c>
+      <c r="AX130" t="inlineStr">
+        <is>
+          <t>Erik Berg</t>
+        </is>
+      </c>
+      <c r="AY130" t="inlineStr">
+        <is>
+          <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 12276-2023 artfynd.xlsx
+++ b/artfynd/A 12276-2023 artfynd.xlsx
@@ -14235,7 +14235,7 @@
         <v>113544517</v>
       </c>
       <c r="B130" t="n">
-        <v>97349</v>
+        <v>97352</v>
       </c>
       <c r="C130" t="inlineStr">
         <is>

--- a/artfynd/A 12276-2023 artfynd.xlsx
+++ b/artfynd/A 12276-2023 artfynd.xlsx
@@ -14235,7 +14235,7 @@
         <v>113544517</v>
       </c>
       <c r="B130" t="n">
-        <v>97352</v>
+        <v>97358</v>
       </c>
       <c r="C130" t="inlineStr">
         <is>

--- a/artfynd/A 12276-2023 artfynd.xlsx
+++ b/artfynd/A 12276-2023 artfynd.xlsx
@@ -14235,7 +14235,7 @@
         <v>113544517</v>
       </c>
       <c r="B130" t="n">
-        <v>97358</v>
+        <v>97365</v>
       </c>
       <c r="C130" t="inlineStr">
         <is>

--- a/artfynd/A 12276-2023 artfynd.xlsx
+++ b/artfynd/A 12276-2023 artfynd.xlsx
@@ -14235,7 +14235,7 @@
         <v>113544517</v>
       </c>
       <c r="B130" t="n">
-        <v>97365</v>
+        <v>97370</v>
       </c>
       <c r="C130" t="inlineStr">
         <is>

--- a/artfynd/A 12276-2023 artfynd.xlsx
+++ b/artfynd/A 12276-2023 artfynd.xlsx
@@ -14235,7 +14235,7 @@
         <v>113544517</v>
       </c>
       <c r="B130" t="n">
-        <v>97370</v>
+        <v>97398</v>
       </c>
       <c r="C130" t="inlineStr">
         <is>

--- a/artfynd/A 12276-2023 artfynd.xlsx
+++ b/artfynd/A 12276-2023 artfynd.xlsx
@@ -14235,7 +14235,7 @@
         <v>113544517</v>
       </c>
       <c r="B130" t="n">
-        <v>97398</v>
+        <v>97402</v>
       </c>
       <c r="C130" t="inlineStr">
         <is>

--- a/artfynd/A 12276-2023 artfynd.xlsx
+++ b/artfynd/A 12276-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 12276-2023 artfynd.xlsx
+++ b/artfynd/A 12276-2023 artfynd.xlsx
@@ -14464,10 +14464,10 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>118387596</v>
+        <v>118387607</v>
       </c>
       <c r="B132" t="n">
-        <v>90469</v>
+        <v>97846</v>
       </c>
       <c r="C132" t="inlineStr">
         <is>
@@ -14476,25 +14476,25 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
@@ -14504,10 +14504,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>572354</v>
+        <v>572604</v>
       </c>
       <c r="R132" t="n">
-        <v>6635135</v>
+        <v>6635128</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -14554,11 +14554,6 @@
       <c r="AI132" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AO132" t="inlineStr">
-        <is>
-          <t>Granlåga</t>
         </is>
       </c>
       <c r="AT132" t="inlineStr"/>
@@ -14580,10 +14575,10 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>118387598</v>
+        <v>118387596</v>
       </c>
       <c r="B133" t="n">
-        <v>90504</v>
+        <v>90469</v>
       </c>
       <c r="C133" t="inlineStr">
         <is>
@@ -14592,25 +14587,25 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E133" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
@@ -14620,10 +14615,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>572333</v>
+        <v>572354</v>
       </c>
       <c r="R133" t="n">
-        <v>6635088</v>
+        <v>6635135</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -14696,10 +14691,10 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>118387591</v>
+        <v>118387610</v>
       </c>
       <c r="B134" t="n">
-        <v>95394</v>
+        <v>97846</v>
       </c>
       <c r="C134" t="inlineStr">
         <is>
@@ -14708,25 +14703,25 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E134" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
@@ -14736,10 +14731,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>572434</v>
+        <v>572447</v>
       </c>
       <c r="R134" t="n">
-        <v>6634862</v>
+        <v>6634879</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -14786,11 +14781,6 @@
       <c r="AI134" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AO134" t="inlineStr">
-        <is>
-          <t>Murken granlåga</t>
         </is>
       </c>
       <c r="AT134" t="inlineStr"/>
@@ -14928,10 +14918,10 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>118387612</v>
+        <v>118387592</v>
       </c>
       <c r="B136" t="n">
-        <v>12239</v>
+        <v>95394</v>
       </c>
       <c r="C136" t="inlineStr">
         <is>
@@ -14940,43 +14930,38 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E136" t="n">
-        <v>100499</v>
+        <v>53</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Smal skuggbagge</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Boros schneideri</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(Panzer, 1795)</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
-      <c r="J136" t="inlineStr"/>
-      <c r="K136" t="inlineStr"/>
-      <c r="L136" t="inlineStr"/>
-      <c r="M136" t="inlineStr"/>
-      <c r="N136" t="inlineStr"/>
       <c r="P136" t="inlineStr">
         <is>
           <t>Norrby, Vstm</t>
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>572309</v>
+        <v>572311</v>
       </c>
       <c r="R136" t="n">
-        <v>6634968</v>
+        <v>6634833</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -15017,7 +15002,6 @@
       <c r="AE136" t="b">
         <v>0</v>
       </c>
-      <c r="AF136" t="inlineStr"/>
       <c r="AG136" t="b">
         <v>0</v>
       </c>
@@ -15028,7 +15012,7 @@
       </c>
       <c r="AO136" t="inlineStr">
         <is>
-          <t>Under bark av en död tall med mestadels barkfallen stam</t>
+          <t>Murken granlåga</t>
         </is>
       </c>
       <c r="AT136" t="inlineStr"/>
@@ -15050,10 +15034,10 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>118387610</v>
+        <v>118387601</v>
       </c>
       <c r="B137" t="n">
-        <v>97846</v>
+        <v>94349</v>
       </c>
       <c r="C137" t="inlineStr">
         <is>
@@ -15062,25 +15046,25 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E137" t="n">
-        <v>220787</v>
+        <v>2667</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
@@ -15090,10 +15074,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>572447</v>
+        <v>572382</v>
       </c>
       <c r="R137" t="n">
-        <v>6634879</v>
+        <v>6635300</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -15140,6 +15124,11 @@
       <c r="AI137" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AO137" t="inlineStr">
+        <is>
+          <t>Stenblock</t>
         </is>
       </c>
       <c r="AT137" t="inlineStr"/>
@@ -15161,10 +15150,10 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>118387606</v>
+        <v>118387595</v>
       </c>
       <c r="B138" t="n">
-        <v>97846</v>
+        <v>90469</v>
       </c>
       <c r="C138" t="inlineStr">
         <is>
@@ -15173,25 +15162,25 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E138" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
@@ -15201,10 +15190,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>572493</v>
+        <v>572335</v>
       </c>
       <c r="R138" t="n">
-        <v>6635206</v>
+        <v>6635076</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -15251,6 +15240,11 @@
       <c r="AI138" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AO138" t="inlineStr">
+        <is>
+          <t>Granlåga</t>
         </is>
       </c>
       <c r="AT138" t="inlineStr"/>
@@ -15272,10 +15266,10 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>118387609</v>
+        <v>118387598</v>
       </c>
       <c r="B139" t="n">
-        <v>97846</v>
+        <v>90504</v>
       </c>
       <c r="C139" t="inlineStr">
         <is>
@@ -15284,25 +15278,25 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E139" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
@@ -15312,10 +15306,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>572438</v>
+        <v>572333</v>
       </c>
       <c r="R139" t="n">
-        <v>6634886</v>
+        <v>6635088</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -15362,6 +15356,11 @@
       <c r="AI139" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AO139" t="inlineStr">
+        <is>
+          <t>Granlåga</t>
         </is>
       </c>
       <c r="AT139" t="inlineStr"/>
@@ -15383,10 +15382,10 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>118387592</v>
+        <v>118387597</v>
       </c>
       <c r="B140" t="n">
-        <v>95394</v>
+        <v>90469</v>
       </c>
       <c r="C140" t="inlineStr">
         <is>
@@ -15395,25 +15394,25 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E140" t="n">
-        <v>53</v>
+        <v>5447</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
@@ -15423,10 +15422,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>572311</v>
+        <v>572377</v>
       </c>
       <c r="R140" t="n">
-        <v>6634833</v>
+        <v>6635188</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -15477,7 +15476,7 @@
       </c>
       <c r="AO140" t="inlineStr">
         <is>
-          <t>Murken granlåga</t>
+          <t>Granlåga</t>
         </is>
       </c>
       <c r="AT140" t="inlineStr"/>
@@ -15499,10 +15498,10 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>118387595</v>
+        <v>118387612</v>
       </c>
       <c r="B141" t="n">
-        <v>90469</v>
+        <v>12239</v>
       </c>
       <c r="C141" t="inlineStr">
         <is>
@@ -15511,38 +15510,43 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E141" t="n">
-        <v>5447</v>
+        <v>100499</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Smal skuggbagge</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Boros schneideri</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Panzer, 1795)</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
+      <c r="J141" t="inlineStr"/>
+      <c r="K141" t="inlineStr"/>
+      <c r="L141" t="inlineStr"/>
+      <c r="M141" t="inlineStr"/>
+      <c r="N141" t="inlineStr"/>
       <c r="P141" t="inlineStr">
         <is>
           <t>Norrby, Vstm</t>
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>572335</v>
+        <v>572309</v>
       </c>
       <c r="R141" t="n">
-        <v>6635076</v>
+        <v>6634968</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -15583,6 +15587,7 @@
       <c r="AE141" t="b">
         <v>0</v>
       </c>
+      <c r="AF141" t="inlineStr"/>
       <c r="AG141" t="b">
         <v>0</v>
       </c>
@@ -15593,7 +15598,7 @@
       </c>
       <c r="AO141" t="inlineStr">
         <is>
-          <t>Granlåga</t>
+          <t>Under bark av en död tall med mestadels barkfallen stam</t>
         </is>
       </c>
       <c r="AT141" t="inlineStr"/>
@@ -15615,7 +15620,7 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>118387607</v>
+        <v>118387609</v>
       </c>
       <c r="B142" t="n">
         <v>97846</v>
@@ -15655,10 +15660,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>572604</v>
+        <v>572438</v>
       </c>
       <c r="R142" t="n">
-        <v>6635128</v>
+        <v>6634886</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -15726,7 +15731,7 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>118387597</v>
+        <v>118387593</v>
       </c>
       <c r="B143" t="n">
         <v>90469</v>
@@ -15766,10 +15771,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>572377</v>
+        <v>572414</v>
       </c>
       <c r="R143" t="n">
-        <v>6635188</v>
+        <v>6635048</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -15953,10 +15958,10 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>118387601</v>
+        <v>118387599</v>
       </c>
       <c r="B145" t="n">
-        <v>94349</v>
+        <v>90504</v>
       </c>
       <c r="C145" t="inlineStr">
         <is>
@@ -15965,25 +15970,25 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E145" t="n">
-        <v>2667</v>
+        <v>1202</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
@@ -15993,10 +15998,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>572382</v>
+        <v>572630</v>
       </c>
       <c r="R145" t="n">
-        <v>6635300</v>
+        <v>6635283</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -16047,7 +16052,7 @@
       </c>
       <c r="AO145" t="inlineStr">
         <is>
-          <t>Stenblock</t>
+          <t>Granlåga</t>
         </is>
       </c>
       <c r="AT145" t="inlineStr"/>
@@ -16069,10 +16074,10 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>118387599</v>
+        <v>118387591</v>
       </c>
       <c r="B146" t="n">
-        <v>90504</v>
+        <v>95394</v>
       </c>
       <c r="C146" t="inlineStr">
         <is>
@@ -16085,21 +16090,21 @@
         </is>
       </c>
       <c r="E146" t="n">
-        <v>1202</v>
+        <v>53</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I146" t="inlineStr"/>
@@ -16109,10 +16114,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>572630</v>
+        <v>572434</v>
       </c>
       <c r="R146" t="n">
-        <v>6635283</v>
+        <v>6634862</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -16163,7 +16168,7 @@
       </c>
       <c r="AO146" t="inlineStr">
         <is>
-          <t>Granlåga</t>
+          <t>Murken granlåga</t>
         </is>
       </c>
       <c r="AT146" t="inlineStr"/>
@@ -16185,10 +16190,10 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>118387593</v>
+        <v>118387606</v>
       </c>
       <c r="B147" t="n">
-        <v>90469</v>
+        <v>97846</v>
       </c>
       <c r="C147" t="inlineStr">
         <is>
@@ -16197,25 +16202,25 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E147" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I147" t="inlineStr"/>
@@ -16225,10 +16230,10 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>572414</v>
+        <v>572493</v>
       </c>
       <c r="R147" t="n">
-        <v>6635048</v>
+        <v>6635206</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -16275,11 +16280,6 @@
       <c r="AI147" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AO147" t="inlineStr">
-        <is>
-          <t>Granlåga</t>
         </is>
       </c>
       <c r="AT147" t="inlineStr"/>

--- a/artfynd/A 12276-2023 artfynd.xlsx
+++ b/artfynd/A 12276-2023 artfynd.xlsx
@@ -15498,10 +15498,10 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>118387612</v>
+        <v>118387609</v>
       </c>
       <c r="B141" t="n">
-        <v>12239</v>
+        <v>97846</v>
       </c>
       <c r="C141" t="inlineStr">
         <is>
@@ -15514,39 +15514,34 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>100499</v>
+        <v>220787</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Smal skuggbagge</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Boros schneideri</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(Panzer, 1795)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
-      <c r="J141" t="inlineStr"/>
-      <c r="K141" t="inlineStr"/>
-      <c r="L141" t="inlineStr"/>
-      <c r="M141" t="inlineStr"/>
-      <c r="N141" t="inlineStr"/>
       <c r="P141" t="inlineStr">
         <is>
           <t>Norrby, Vstm</t>
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>572309</v>
+        <v>572438</v>
       </c>
       <c r="R141" t="n">
-        <v>6634968</v>
+        <v>6634886</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -15587,18 +15582,12 @@
       <c r="AE141" t="b">
         <v>0</v>
       </c>
-      <c r="AF141" t="inlineStr"/>
       <c r="AG141" t="b">
         <v>0</v>
       </c>
       <c r="AI141" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AO141" t="inlineStr">
-        <is>
-          <t>Under bark av en död tall med mestadels barkfallen stam</t>
         </is>
       </c>
       <c r="AT141" t="inlineStr"/>
@@ -15620,10 +15609,10 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>118387609</v>
+        <v>118387612</v>
       </c>
       <c r="B142" t="n">
-        <v>97846</v>
+        <v>12239</v>
       </c>
       <c r="C142" t="inlineStr">
         <is>
@@ -15636,34 +15625,39 @@
         </is>
       </c>
       <c r="E142" t="n">
-        <v>220787</v>
+        <v>100499</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Smal skuggbagge</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Boros schneideri</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Panzer, 1795)</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
+      <c r="J142" t="inlineStr"/>
+      <c r="K142" t="inlineStr"/>
+      <c r="L142" t="inlineStr"/>
+      <c r="M142" t="inlineStr"/>
+      <c r="N142" t="inlineStr"/>
       <c r="P142" t="inlineStr">
         <is>
           <t>Norrby, Vstm</t>
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>572438</v>
+        <v>572309</v>
       </c>
       <c r="R142" t="n">
-        <v>6634886</v>
+        <v>6634968</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -15704,12 +15698,18 @@
       <c r="AE142" t="b">
         <v>0</v>
       </c>
+      <c r="AF142" t="inlineStr"/>
       <c r="AG142" t="b">
         <v>0</v>
       </c>
       <c r="AI142" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AO142" t="inlineStr">
+        <is>
+          <t>Under bark av en död tall med mestadels barkfallen stam</t>
         </is>
       </c>
       <c r="AT142" t="inlineStr"/>

--- a/artfynd/A 12276-2023 artfynd.xlsx
+++ b/artfynd/A 12276-2023 artfynd.xlsx
@@ -14464,7 +14464,7 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>118387607</v>
+        <v>118387606</v>
       </c>
       <c r="B132" t="n">
         <v>97846</v>
@@ -14504,10 +14504,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>572604</v>
+        <v>572493</v>
       </c>
       <c r="R132" t="n">
-        <v>6635128</v>
+        <v>6635206</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -14575,7 +14575,7 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>118387596</v>
+        <v>118387595</v>
       </c>
       <c r="B133" t="n">
         <v>90469</v>
@@ -14615,10 +14615,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>572354</v>
+        <v>572335</v>
       </c>
       <c r="R133" t="n">
-        <v>6635135</v>
+        <v>6635076</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -14802,10 +14802,10 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>118387600</v>
+        <v>118387597</v>
       </c>
       <c r="B135" t="n">
-        <v>90504</v>
+        <v>90469</v>
       </c>
       <c r="C135" t="inlineStr">
         <is>
@@ -14814,25 +14814,25 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E135" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
@@ -14842,10 +14842,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>572427</v>
+        <v>572377</v>
       </c>
       <c r="R135" t="n">
-        <v>6634850</v>
+        <v>6635188</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -14918,10 +14918,10 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>118387592</v>
+        <v>118387593</v>
       </c>
       <c r="B136" t="n">
-        <v>95394</v>
+        <v>90469</v>
       </c>
       <c r="C136" t="inlineStr">
         <is>
@@ -14930,25 +14930,25 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E136" t="n">
-        <v>53</v>
+        <v>5447</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
@@ -14958,10 +14958,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>572311</v>
+        <v>572414</v>
       </c>
       <c r="R136" t="n">
-        <v>6634833</v>
+        <v>6635048</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -15012,7 +15012,7 @@
       </c>
       <c r="AO136" t="inlineStr">
         <is>
-          <t>Murken granlåga</t>
+          <t>Granlåga</t>
         </is>
       </c>
       <c r="AT136" t="inlineStr"/>
@@ -15034,10 +15034,10 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>118387601</v>
+        <v>118387599</v>
       </c>
       <c r="B137" t="n">
-        <v>94349</v>
+        <v>90504</v>
       </c>
       <c r="C137" t="inlineStr">
         <is>
@@ -15046,25 +15046,25 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E137" t="n">
-        <v>2667</v>
+        <v>1202</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
@@ -15074,10 +15074,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>572382</v>
+        <v>572630</v>
       </c>
       <c r="R137" t="n">
-        <v>6635300</v>
+        <v>6635283</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -15128,7 +15128,7 @@
       </c>
       <c r="AO137" t="inlineStr">
         <is>
-          <t>Stenblock</t>
+          <t>Granlåga</t>
         </is>
       </c>
       <c r="AT137" t="inlineStr"/>
@@ -15150,10 +15150,10 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>118387595</v>
+        <v>118387598</v>
       </c>
       <c r="B138" t="n">
-        <v>90469</v>
+        <v>90504</v>
       </c>
       <c r="C138" t="inlineStr">
         <is>
@@ -15162,25 +15162,25 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E138" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
@@ -15190,10 +15190,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>572335</v>
+        <v>572333</v>
       </c>
       <c r="R138" t="n">
-        <v>6635076</v>
+        <v>6635088</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -15266,10 +15266,10 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>118387598</v>
+        <v>118387608</v>
       </c>
       <c r="B139" t="n">
-        <v>90504</v>
+        <v>97846</v>
       </c>
       <c r="C139" t="inlineStr">
         <is>
@@ -15278,25 +15278,25 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E139" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
@@ -15306,10 +15306,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>572333</v>
+        <v>572483</v>
       </c>
       <c r="R139" t="n">
-        <v>6635088</v>
+        <v>6635026</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -15356,11 +15356,6 @@
       <c r="AI139" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AO139" t="inlineStr">
-        <is>
-          <t>Granlåga</t>
         </is>
       </c>
       <c r="AT139" t="inlineStr"/>
@@ -15382,10 +15377,10 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>118387597</v>
+        <v>118387609</v>
       </c>
       <c r="B140" t="n">
-        <v>90469</v>
+        <v>97846</v>
       </c>
       <c r="C140" t="inlineStr">
         <is>
@@ -15394,25 +15389,25 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E140" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
@@ -15422,10 +15417,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>572377</v>
+        <v>572438</v>
       </c>
       <c r="R140" t="n">
-        <v>6635188</v>
+        <v>6634886</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -15472,11 +15467,6 @@
       <c r="AI140" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AO140" t="inlineStr">
-        <is>
-          <t>Granlåga</t>
         </is>
       </c>
       <c r="AT140" t="inlineStr"/>
@@ -15498,10 +15488,10 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>118387609</v>
+        <v>118387601</v>
       </c>
       <c r="B141" t="n">
-        <v>97846</v>
+        <v>94349</v>
       </c>
       <c r="C141" t="inlineStr">
         <is>
@@ -15510,25 +15500,25 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E141" t="n">
-        <v>220787</v>
+        <v>2667</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
@@ -15538,10 +15528,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>572438</v>
+        <v>572382</v>
       </c>
       <c r="R141" t="n">
-        <v>6634886</v>
+        <v>6635300</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -15588,6 +15578,11 @@
       <c r="AI141" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AO141" t="inlineStr">
+        <is>
+          <t>Stenblock</t>
         </is>
       </c>
       <c r="AT141" t="inlineStr"/>
@@ -15731,7 +15726,7 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>118387593</v>
+        <v>118387596</v>
       </c>
       <c r="B143" t="n">
         <v>90469</v>
@@ -15771,10 +15766,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>572414</v>
+        <v>572354</v>
       </c>
       <c r="R143" t="n">
-        <v>6635048</v>
+        <v>6635135</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -15847,10 +15842,10 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>118387608</v>
+        <v>118387592</v>
       </c>
       <c r="B144" t="n">
-        <v>97846</v>
+        <v>95394</v>
       </c>
       <c r="C144" t="inlineStr">
         <is>
@@ -15859,25 +15854,25 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E144" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I144" t="inlineStr"/>
@@ -15887,10 +15882,10 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>572483</v>
+        <v>572311</v>
       </c>
       <c r="R144" t="n">
-        <v>6635026</v>
+        <v>6634833</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -15937,6 +15932,11 @@
       <c r="AI144" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AO144" t="inlineStr">
+        <is>
+          <t>Murken granlåga</t>
         </is>
       </c>
       <c r="AT144" t="inlineStr"/>
@@ -15958,7 +15958,7 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>118387599</v>
+        <v>118387600</v>
       </c>
       <c r="B145" t="n">
         <v>90504</v>
@@ -15998,10 +15998,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>572630</v>
+        <v>572427</v>
       </c>
       <c r="R145" t="n">
-        <v>6635283</v>
+        <v>6634850</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -16190,7 +16190,7 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>118387606</v>
+        <v>118387607</v>
       </c>
       <c r="B147" t="n">
         <v>97846</v>
@@ -16230,10 +16230,10 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>572493</v>
+        <v>572604</v>
       </c>
       <c r="R147" t="n">
-        <v>6635206</v>
+        <v>6635128</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>

--- a/artfynd/A 12276-2023 artfynd.xlsx
+++ b/artfynd/A 12276-2023 artfynd.xlsx
@@ -14464,10 +14464,10 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>118387606</v>
+        <v>118387609</v>
       </c>
       <c r="B132" t="n">
-        <v>97846</v>
+        <v>97853</v>
       </c>
       <c r="C132" t="inlineStr">
         <is>
@@ -14504,10 +14504,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>572493</v>
+        <v>572438</v>
       </c>
       <c r="R132" t="n">
-        <v>6635206</v>
+        <v>6634886</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -14575,10 +14575,10 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>118387595</v>
+        <v>118387610</v>
       </c>
       <c r="B133" t="n">
-        <v>90469</v>
+        <v>97853</v>
       </c>
       <c r="C133" t="inlineStr">
         <is>
@@ -14587,25 +14587,25 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E133" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
@@ -14615,10 +14615,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>572335</v>
+        <v>572447</v>
       </c>
       <c r="R133" t="n">
-        <v>6635076</v>
+        <v>6634879</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -14665,11 +14665,6 @@
       <c r="AI133" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AO133" t="inlineStr">
-        <is>
-          <t>Granlåga</t>
         </is>
       </c>
       <c r="AT133" t="inlineStr"/>
@@ -14691,10 +14686,10 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>118387610</v>
+        <v>118387593</v>
       </c>
       <c r="B134" t="n">
-        <v>97846</v>
+        <v>90476</v>
       </c>
       <c r="C134" t="inlineStr">
         <is>
@@ -14703,25 +14698,25 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E134" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
@@ -14731,10 +14726,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>572447</v>
+        <v>572414</v>
       </c>
       <c r="R134" t="n">
-        <v>6634879</v>
+        <v>6635048</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -14781,6 +14776,11 @@
       <c r="AI134" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AO134" t="inlineStr">
+        <is>
+          <t>Granlåga</t>
         </is>
       </c>
       <c r="AT134" t="inlineStr"/>
@@ -14802,10 +14802,10 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>118387597</v>
+        <v>118387596</v>
       </c>
       <c r="B135" t="n">
-        <v>90469</v>
+        <v>90476</v>
       </c>
       <c r="C135" t="inlineStr">
         <is>
@@ -14842,10 +14842,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>572377</v>
+        <v>572354</v>
       </c>
       <c r="R135" t="n">
-        <v>6635188</v>
+        <v>6635135</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -14918,10 +14918,10 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>118387593</v>
+        <v>118387612</v>
       </c>
       <c r="B136" t="n">
-        <v>90469</v>
+        <v>12239</v>
       </c>
       <c r="C136" t="inlineStr">
         <is>
@@ -14930,38 +14930,43 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E136" t="n">
-        <v>5447</v>
+        <v>100499</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Smal skuggbagge</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Boros schneideri</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Panzer, 1795)</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
+      <c r="J136" t="inlineStr"/>
+      <c r="K136" t="inlineStr"/>
+      <c r="L136" t="inlineStr"/>
+      <c r="M136" t="inlineStr"/>
+      <c r="N136" t="inlineStr"/>
       <c r="P136" t="inlineStr">
         <is>
           <t>Norrby, Vstm</t>
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>572414</v>
+        <v>572309</v>
       </c>
       <c r="R136" t="n">
-        <v>6635048</v>
+        <v>6634968</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -15002,6 +15007,7 @@
       <c r="AE136" t="b">
         <v>0</v>
       </c>
+      <c r="AF136" t="inlineStr"/>
       <c r="AG136" t="b">
         <v>0</v>
       </c>
@@ -15012,7 +15018,7 @@
       </c>
       <c r="AO136" t="inlineStr">
         <is>
-          <t>Granlåga</t>
+          <t>Under bark av en död tall med mestadels barkfallen stam</t>
         </is>
       </c>
       <c r="AT136" t="inlineStr"/>
@@ -15037,7 +15043,7 @@
         <v>118387599</v>
       </c>
       <c r="B137" t="n">
-        <v>90504</v>
+        <v>90511</v>
       </c>
       <c r="C137" t="inlineStr">
         <is>
@@ -15150,10 +15156,10 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>118387598</v>
+        <v>118387600</v>
       </c>
       <c r="B138" t="n">
-        <v>90504</v>
+        <v>90511</v>
       </c>
       <c r="C138" t="inlineStr">
         <is>
@@ -15190,10 +15196,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>572333</v>
+        <v>572427</v>
       </c>
       <c r="R138" t="n">
-        <v>6635088</v>
+        <v>6634850</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -15266,10 +15272,10 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>118387608</v>
+        <v>118387597</v>
       </c>
       <c r="B139" t="n">
-        <v>97846</v>
+        <v>90476</v>
       </c>
       <c r="C139" t="inlineStr">
         <is>
@@ -15278,25 +15284,25 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E139" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
@@ -15306,10 +15312,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>572483</v>
+        <v>572377</v>
       </c>
       <c r="R139" t="n">
-        <v>6635026</v>
+        <v>6635188</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -15356,6 +15362,11 @@
       <c r="AI139" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AO139" t="inlineStr">
+        <is>
+          <t>Granlåga</t>
         </is>
       </c>
       <c r="AT139" t="inlineStr"/>
@@ -15377,10 +15388,10 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>118387609</v>
+        <v>118387608</v>
       </c>
       <c r="B140" t="n">
-        <v>97846</v>
+        <v>97853</v>
       </c>
       <c r="C140" t="inlineStr">
         <is>
@@ -15417,10 +15428,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>572438</v>
+        <v>572483</v>
       </c>
       <c r="R140" t="n">
-        <v>6634886</v>
+        <v>6635026</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -15488,10 +15499,10 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>118387601</v>
+        <v>118387592</v>
       </c>
       <c r="B141" t="n">
-        <v>94349</v>
+        <v>95401</v>
       </c>
       <c r="C141" t="inlineStr">
         <is>
@@ -15500,25 +15511,25 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E141" t="n">
-        <v>2667</v>
+        <v>53</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
@@ -15528,10 +15539,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>572382</v>
+        <v>572311</v>
       </c>
       <c r="R141" t="n">
-        <v>6635300</v>
+        <v>6634833</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -15582,7 +15593,7 @@
       </c>
       <c r="AO141" t="inlineStr">
         <is>
-          <t>Stenblock</t>
+          <t>Murken granlåga</t>
         </is>
       </c>
       <c r="AT141" t="inlineStr"/>
@@ -15604,10 +15615,10 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>118387612</v>
+        <v>118387601</v>
       </c>
       <c r="B142" t="n">
-        <v>12239</v>
+        <v>94356</v>
       </c>
       <c r="C142" t="inlineStr">
         <is>
@@ -15616,43 +15627,38 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E142" t="n">
-        <v>100499</v>
+        <v>2667</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Smal skuggbagge</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Boros schneideri</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(Panzer, 1795)</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
-      <c r="J142" t="inlineStr"/>
-      <c r="K142" t="inlineStr"/>
-      <c r="L142" t="inlineStr"/>
-      <c r="M142" t="inlineStr"/>
-      <c r="N142" t="inlineStr"/>
       <c r="P142" t="inlineStr">
         <is>
           <t>Norrby, Vstm</t>
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>572309</v>
+        <v>572382</v>
       </c>
       <c r="R142" t="n">
-        <v>6634968</v>
+        <v>6635300</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -15693,7 +15699,6 @@
       <c r="AE142" t="b">
         <v>0</v>
       </c>
-      <c r="AF142" t="inlineStr"/>
       <c r="AG142" t="b">
         <v>0</v>
       </c>
@@ -15704,7 +15709,7 @@
       </c>
       <c r="AO142" t="inlineStr">
         <is>
-          <t>Under bark av en död tall med mestadels barkfallen stam</t>
+          <t>Stenblock</t>
         </is>
       </c>
       <c r="AT142" t="inlineStr"/>
@@ -15726,10 +15731,10 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>118387596</v>
+        <v>118387595</v>
       </c>
       <c r="B143" t="n">
-        <v>90469</v>
+        <v>90476</v>
       </c>
       <c r="C143" t="inlineStr">
         <is>
@@ -15766,10 +15771,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>572354</v>
+        <v>572335</v>
       </c>
       <c r="R143" t="n">
-        <v>6635135</v>
+        <v>6635076</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -15842,10 +15847,10 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>118387592</v>
+        <v>118387607</v>
       </c>
       <c r="B144" t="n">
-        <v>95394</v>
+        <v>97853</v>
       </c>
       <c r="C144" t="inlineStr">
         <is>
@@ -15854,25 +15859,25 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E144" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I144" t="inlineStr"/>
@@ -15882,10 +15887,10 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>572311</v>
+        <v>572604</v>
       </c>
       <c r="R144" t="n">
-        <v>6634833</v>
+        <v>6635128</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -15932,11 +15937,6 @@
       <c r="AI144" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AO144" t="inlineStr">
-        <is>
-          <t>Murken granlåga</t>
         </is>
       </c>
       <c r="AT144" t="inlineStr"/>
@@ -15958,10 +15958,10 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>118387600</v>
+        <v>118387598</v>
       </c>
       <c r="B145" t="n">
-        <v>90504</v>
+        <v>90511</v>
       </c>
       <c r="C145" t="inlineStr">
         <is>
@@ -15998,10 +15998,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>572427</v>
+        <v>572333</v>
       </c>
       <c r="R145" t="n">
-        <v>6634850</v>
+        <v>6635088</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -16074,10 +16074,10 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>118387591</v>
+        <v>118387606</v>
       </c>
       <c r="B146" t="n">
-        <v>95394</v>
+        <v>97853</v>
       </c>
       <c r="C146" t="inlineStr">
         <is>
@@ -16086,25 +16086,25 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E146" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I146" t="inlineStr"/>
@@ -16114,10 +16114,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>572434</v>
+        <v>572493</v>
       </c>
       <c r="R146" t="n">
-        <v>6634862</v>
+        <v>6635206</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -16164,11 +16164,6 @@
       <c r="AI146" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AO146" t="inlineStr">
-        <is>
-          <t>Murken granlåga</t>
         </is>
       </c>
       <c r="AT146" t="inlineStr"/>
@@ -16190,10 +16185,10 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>118387607</v>
+        <v>118387591</v>
       </c>
       <c r="B147" t="n">
-        <v>97846</v>
+        <v>95401</v>
       </c>
       <c r="C147" t="inlineStr">
         <is>
@@ -16202,25 +16197,25 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E147" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I147" t="inlineStr"/>
@@ -16230,10 +16225,10 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>572604</v>
+        <v>572434</v>
       </c>
       <c r="R147" t="n">
-        <v>6635128</v>
+        <v>6634862</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -16280,6 +16275,11 @@
       <c r="AI147" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AO147" t="inlineStr">
+        <is>
+          <t>Murken granlåga</t>
         </is>
       </c>
       <c r="AT147" t="inlineStr"/>

--- a/artfynd/A 12276-2023 artfynd.xlsx
+++ b/artfynd/A 12276-2023 artfynd.xlsx
@@ -14464,10 +14464,10 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>118387609</v>
+        <v>118387595</v>
       </c>
       <c r="B132" t="n">
-        <v>97853</v>
+        <v>90476</v>
       </c>
       <c r="C132" t="inlineStr">
         <is>
@@ -14476,25 +14476,25 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
@@ -14504,10 +14504,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>572438</v>
+        <v>572335</v>
       </c>
       <c r="R132" t="n">
-        <v>6634886</v>
+        <v>6635076</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -14554,6 +14554,11 @@
       <c r="AI132" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AO132" t="inlineStr">
+        <is>
+          <t>Granlåga</t>
         </is>
       </c>
       <c r="AT132" t="inlineStr"/>
@@ -14575,10 +14580,10 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>118387610</v>
+        <v>118387596</v>
       </c>
       <c r="B133" t="n">
-        <v>97853</v>
+        <v>90476</v>
       </c>
       <c r="C133" t="inlineStr">
         <is>
@@ -14587,25 +14592,25 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E133" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
@@ -14615,10 +14620,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>572447</v>
+        <v>572354</v>
       </c>
       <c r="R133" t="n">
-        <v>6634879</v>
+        <v>6635135</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -14665,6 +14670,11 @@
       <c r="AI133" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AO133" t="inlineStr">
+        <is>
+          <t>Granlåga</t>
         </is>
       </c>
       <c r="AT133" t="inlineStr"/>
@@ -14686,10 +14696,10 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>118387593</v>
+        <v>118387591</v>
       </c>
       <c r="B134" t="n">
-        <v>90476</v>
+        <v>95401</v>
       </c>
       <c r="C134" t="inlineStr">
         <is>
@@ -14698,25 +14708,25 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E134" t="n">
-        <v>5447</v>
+        <v>53</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
@@ -14726,10 +14736,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>572414</v>
+        <v>572434</v>
       </c>
       <c r="R134" t="n">
-        <v>6635048</v>
+        <v>6634862</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -14780,7 +14790,7 @@
       </c>
       <c r="AO134" t="inlineStr">
         <is>
-          <t>Granlåga</t>
+          <t>Murken granlåga</t>
         </is>
       </c>
       <c r="AT134" t="inlineStr"/>
@@ -14802,10 +14812,10 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>118387596</v>
+        <v>118387601</v>
       </c>
       <c r="B135" t="n">
-        <v>90476</v>
+        <v>94356</v>
       </c>
       <c r="C135" t="inlineStr">
         <is>
@@ -14818,21 +14828,21 @@
         </is>
       </c>
       <c r="E135" t="n">
-        <v>5447</v>
+        <v>2667</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
@@ -14842,10 +14852,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>572354</v>
+        <v>572382</v>
       </c>
       <c r="R135" t="n">
-        <v>6635135</v>
+        <v>6635300</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -14896,7 +14906,7 @@
       </c>
       <c r="AO135" t="inlineStr">
         <is>
-          <t>Granlåga</t>
+          <t>Stenblock</t>
         </is>
       </c>
       <c r="AT135" t="inlineStr"/>
@@ -15040,7 +15050,7 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>118387599</v>
+        <v>118387598</v>
       </c>
       <c r="B137" t="n">
         <v>90511</v>
@@ -15080,10 +15090,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>572630</v>
+        <v>572333</v>
       </c>
       <c r="R137" t="n">
-        <v>6635283</v>
+        <v>6635088</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -15156,10 +15166,10 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>118387600</v>
+        <v>118387597</v>
       </c>
       <c r="B138" t="n">
-        <v>90511</v>
+        <v>90476</v>
       </c>
       <c r="C138" t="inlineStr">
         <is>
@@ -15168,25 +15178,25 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E138" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
@@ -15196,10 +15206,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>572427</v>
+        <v>572377</v>
       </c>
       <c r="R138" t="n">
-        <v>6634850</v>
+        <v>6635188</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -15272,10 +15282,10 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>118387597</v>
+        <v>118387592</v>
       </c>
       <c r="B139" t="n">
-        <v>90476</v>
+        <v>95401</v>
       </c>
       <c r="C139" t="inlineStr">
         <is>
@@ -15284,25 +15294,25 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E139" t="n">
-        <v>5447</v>
+        <v>53</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
@@ -15312,10 +15322,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>572377</v>
+        <v>572311</v>
       </c>
       <c r="R139" t="n">
-        <v>6635188</v>
+        <v>6634833</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -15366,7 +15376,7 @@
       </c>
       <c r="AO139" t="inlineStr">
         <is>
-          <t>Granlåga</t>
+          <t>Murken granlåga</t>
         </is>
       </c>
       <c r="AT139" t="inlineStr"/>
@@ -15499,10 +15509,10 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>118387592</v>
+        <v>118387593</v>
       </c>
       <c r="B141" t="n">
-        <v>95401</v>
+        <v>90476</v>
       </c>
       <c r="C141" t="inlineStr">
         <is>
@@ -15511,25 +15521,25 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E141" t="n">
-        <v>53</v>
+        <v>5447</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
@@ -15539,10 +15549,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>572311</v>
+        <v>572414</v>
       </c>
       <c r="R141" t="n">
-        <v>6634833</v>
+        <v>6635048</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -15593,7 +15603,7 @@
       </c>
       <c r="AO141" t="inlineStr">
         <is>
-          <t>Murken granlåga</t>
+          <t>Granlåga</t>
         </is>
       </c>
       <c r="AT141" t="inlineStr"/>
@@ -15615,10 +15625,10 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>118387601</v>
+        <v>118387610</v>
       </c>
       <c r="B142" t="n">
-        <v>94356</v>
+        <v>97853</v>
       </c>
       <c r="C142" t="inlineStr">
         <is>
@@ -15627,25 +15637,25 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E142" t="n">
-        <v>2667</v>
+        <v>220787</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
@@ -15655,10 +15665,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>572382</v>
+        <v>572447</v>
       </c>
       <c r="R142" t="n">
-        <v>6635300</v>
+        <v>6634879</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -15705,11 +15715,6 @@
       <c r="AI142" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AO142" t="inlineStr">
-        <is>
-          <t>Stenblock</t>
         </is>
       </c>
       <c r="AT142" t="inlineStr"/>
@@ -15731,10 +15736,10 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>118387595</v>
+        <v>118387606</v>
       </c>
       <c r="B143" t="n">
-        <v>90476</v>
+        <v>97853</v>
       </c>
       <c r="C143" t="inlineStr">
         <is>
@@ -15743,25 +15748,25 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E143" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
@@ -15771,10 +15776,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>572335</v>
+        <v>572493</v>
       </c>
       <c r="R143" t="n">
-        <v>6635076</v>
+        <v>6635206</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -15821,11 +15826,6 @@
       <c r="AI143" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AO143" t="inlineStr">
-        <is>
-          <t>Granlåga</t>
         </is>
       </c>
       <c r="AT143" t="inlineStr"/>
@@ -15847,10 +15847,10 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>118387607</v>
+        <v>118387600</v>
       </c>
       <c r="B144" t="n">
-        <v>97853</v>
+        <v>90511</v>
       </c>
       <c r="C144" t="inlineStr">
         <is>
@@ -15859,25 +15859,25 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E144" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I144" t="inlineStr"/>
@@ -15887,10 +15887,10 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>572604</v>
+        <v>572427</v>
       </c>
       <c r="R144" t="n">
-        <v>6635128</v>
+        <v>6634850</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -15937,6 +15937,11 @@
       <c r="AI144" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AO144" t="inlineStr">
+        <is>
+          <t>Granlåga</t>
         </is>
       </c>
       <c r="AT144" t="inlineStr"/>
@@ -15958,7 +15963,7 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>118387598</v>
+        <v>118387599</v>
       </c>
       <c r="B145" t="n">
         <v>90511</v>
@@ -15998,10 +16003,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>572333</v>
+        <v>572630</v>
       </c>
       <c r="R145" t="n">
-        <v>6635088</v>
+        <v>6635283</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -16074,7 +16079,7 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>118387606</v>
+        <v>118387607</v>
       </c>
       <c r="B146" t="n">
         <v>97853</v>
@@ -16114,10 +16119,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>572493</v>
+        <v>572604</v>
       </c>
       <c r="R146" t="n">
-        <v>6635206</v>
+        <v>6635128</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -16185,10 +16190,10 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>118387591</v>
+        <v>118387609</v>
       </c>
       <c r="B147" t="n">
-        <v>95401</v>
+        <v>97853</v>
       </c>
       <c r="C147" t="inlineStr">
         <is>
@@ -16197,25 +16202,25 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E147" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I147" t="inlineStr"/>
@@ -16225,10 +16230,10 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>572434</v>
+        <v>572438</v>
       </c>
       <c r="R147" t="n">
-        <v>6634862</v>
+        <v>6634886</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -16275,11 +16280,6 @@
       <c r="AI147" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AO147" t="inlineStr">
-        <is>
-          <t>Murken granlåga</t>
         </is>
       </c>
       <c r="AT147" t="inlineStr"/>

--- a/artfynd/A 12276-2023 artfynd.xlsx
+++ b/artfynd/A 12276-2023 artfynd.xlsx
@@ -16408,10 +16408,10 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>119807129</v>
+        <v>119806746</v>
       </c>
       <c r="B149" t="n">
-        <v>25571</v>
+        <v>97907</v>
       </c>
       <c r="C149" t="inlineStr">
         <is>
@@ -16420,47 +16420,47 @@
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E149" t="n">
-        <v>100659</v>
+        <v>220787</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Ljus vedstrit</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Cixidia lapponica</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(Zetterstedt, 1838)</t>
-        </is>
-      </c>
-      <c r="I149" t="inlineStr"/>
-      <c r="J149" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I149" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K149" t="inlineStr">
         <is>
-          <t>larv/nymf</t>
-        </is>
-      </c>
-      <c r="L149" t="inlineStr"/>
-      <c r="M149" t="inlineStr"/>
-      <c r="N149" t="inlineStr"/>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P149" t="inlineStr">
         <is>
-          <t>Sala-Norrby 1:10, Vstm</t>
+          <t>Sala-Norrby 1:4, Vstm</t>
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>572435</v>
+        <v>572446</v>
       </c>
       <c r="R149" t="n">
-        <v>6634933</v>
+        <v>6635218</v>
       </c>
       <c r="S149" t="n">
         <v>15</v>
@@ -16501,7 +16501,6 @@
       <c r="AE149" t="b">
         <v>0</v>
       </c>
-      <c r="AF149" t="inlineStr"/>
       <c r="AG149" t="b">
         <v>0</v>
       </c>
@@ -16520,10 +16519,10 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>119806746</v>
+        <v>119807129</v>
       </c>
       <c r="B150" t="n">
-        <v>97907</v>
+        <v>25571</v>
       </c>
       <c r="C150" t="inlineStr">
         <is>
@@ -16532,47 +16531,47 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E150" t="n">
-        <v>220787</v>
+        <v>100659</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ljus vedstrit</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Cixidia lapponica</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I150" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Zetterstedt, 1838)</t>
+        </is>
+      </c>
+      <c r="I150" t="inlineStr"/>
+      <c r="J150" t="inlineStr"/>
       <c r="K150" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>larv/nymf</t>
+        </is>
+      </c>
+      <c r="L150" t="inlineStr"/>
+      <c r="M150" t="inlineStr"/>
+      <c r="N150" t="inlineStr"/>
       <c r="P150" t="inlineStr">
         <is>
-          <t>Sala-Norrby 1:4, Vstm</t>
+          <t>Sala-Norrby 1:10, Vstm</t>
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>572446</v>
+        <v>572435</v>
       </c>
       <c r="R150" t="n">
-        <v>6635218</v>
+        <v>6634933</v>
       </c>
       <c r="S150" t="n">
         <v>15</v>
@@ -16613,6 +16612,7 @@
       <c r="AE150" t="b">
         <v>0</v>
       </c>
+      <c r="AF150" t="inlineStr"/>
       <c r="AG150" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 12276-2023 artfynd.xlsx
+++ b/artfynd/A 12276-2023 artfynd.xlsx
@@ -16301,10 +16301,10 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>119806739</v>
+        <v>119806746</v>
       </c>
       <c r="B148" t="n">
-        <v>57326</v>
+        <v>97907</v>
       </c>
       <c r="C148" t="inlineStr">
         <is>
@@ -16313,43 +16313,47 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E148" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I148" t="inlineStr"/>
-      <c r="M148" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I148" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K148" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P148" t="inlineStr">
         <is>
-          <t>Sala-Norrby 1:11, Vstm</t>
+          <t>Sala-Norrby 1:4, Vstm</t>
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>572434</v>
+        <v>572446</v>
       </c>
       <c r="R148" t="n">
-        <v>6634940</v>
+        <v>6635218</v>
       </c>
       <c r="S148" t="n">
         <v>15</v>
@@ -16408,10 +16412,10 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>119806746</v>
+        <v>119806739</v>
       </c>
       <c r="B149" t="n">
-        <v>97907</v>
+        <v>57326</v>
       </c>
       <c r="C149" t="inlineStr">
         <is>
@@ -16420,47 +16424,43 @@
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E149" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I149" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K149" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I149" t="inlineStr"/>
+      <c r="M149" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P149" t="inlineStr">
         <is>
-          <t>Sala-Norrby 1:4, Vstm</t>
+          <t>Sala-Norrby 1:11, Vstm</t>
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>572446</v>
+        <v>572434</v>
       </c>
       <c r="R149" t="n">
-        <v>6635218</v>
+        <v>6634940</v>
       </c>
       <c r="S149" t="n">
         <v>15</v>
@@ -16519,10 +16519,10 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>119807129</v>
+        <v>119806745</v>
       </c>
       <c r="B150" t="n">
-        <v>25571</v>
+        <v>97907</v>
       </c>
       <c r="C150" t="inlineStr">
         <is>
@@ -16531,47 +16531,47 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E150" t="n">
-        <v>100659</v>
+        <v>220787</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Ljus vedstrit</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Cixidia lapponica</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(Zetterstedt, 1838)</t>
-        </is>
-      </c>
-      <c r="I150" t="inlineStr"/>
-      <c r="J150" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I150" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K150" t="inlineStr">
         <is>
-          <t>larv/nymf</t>
-        </is>
-      </c>
-      <c r="L150" t="inlineStr"/>
-      <c r="M150" t="inlineStr"/>
-      <c r="N150" t="inlineStr"/>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P150" t="inlineStr">
         <is>
-          <t>Sala-Norrby 1:10, Vstm</t>
+          <t>Sala-Norrby 1:5, Vstm</t>
         </is>
       </c>
       <c r="Q150" t="n">
         <v>572435</v>
       </c>
       <c r="R150" t="n">
-        <v>6634933</v>
+        <v>6635219</v>
       </c>
       <c r="S150" t="n">
         <v>15</v>
@@ -16612,7 +16612,6 @@
       <c r="AE150" t="b">
         <v>0</v>
       </c>
-      <c r="AF150" t="inlineStr"/>
       <c r="AG150" t="b">
         <v>0</v>
       </c>
@@ -16631,10 +16630,10 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>119806745</v>
+        <v>119807129</v>
       </c>
       <c r="B151" t="n">
-        <v>97907</v>
+        <v>25571</v>
       </c>
       <c r="C151" t="inlineStr">
         <is>
@@ -16643,47 +16642,47 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E151" t="n">
-        <v>220787</v>
+        <v>100659</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ljus vedstrit</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Cixidia lapponica</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I151" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Zetterstedt, 1838)</t>
+        </is>
+      </c>
+      <c r="I151" t="inlineStr"/>
+      <c r="J151" t="inlineStr"/>
       <c r="K151" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>larv/nymf</t>
+        </is>
+      </c>
+      <c r="L151" t="inlineStr"/>
+      <c r="M151" t="inlineStr"/>
+      <c r="N151" t="inlineStr"/>
       <c r="P151" t="inlineStr">
         <is>
-          <t>Sala-Norrby 1:5, Vstm</t>
+          <t>Sala-Norrby 1:10, Vstm</t>
         </is>
       </c>
       <c r="Q151" t="n">
         <v>572435</v>
       </c>
       <c r="R151" t="n">
-        <v>6635219</v>
+        <v>6634933</v>
       </c>
       <c r="S151" t="n">
         <v>15</v>
@@ -16724,6 +16723,7 @@
       <c r="AE151" t="b">
         <v>0</v>
       </c>
+      <c r="AF151" t="inlineStr"/>
       <c r="AG151" t="b">
         <v>0</v>
       </c>
@@ -16742,10 +16742,10 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>119806744</v>
+        <v>119806742</v>
       </c>
       <c r="B152" t="n">
-        <v>8243</v>
+        <v>90582</v>
       </c>
       <c r="C152" t="inlineStr">
         <is>
@@ -16758,43 +16758,34 @@
         </is>
       </c>
       <c r="E152" t="n">
-        <v>106456</v>
+        <v>5442</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Granvivel</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Pissodes harcyniae</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>(Herbst, 1795)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
-      <c r="J152" t="inlineStr"/>
-      <c r="K152" t="inlineStr"/>
-      <c r="L152" t="inlineStr"/>
-      <c r="M152" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N152" t="inlineStr"/>
       <c r="P152" t="inlineStr">
         <is>
-          <t>Sala-Norrby 1:6, Vstm</t>
+          <t>Sala-Norrby 1:8, Vstm</t>
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>572354</v>
+        <v>572407</v>
       </c>
       <c r="R152" t="n">
-        <v>6635074</v>
+        <v>6634973</v>
       </c>
       <c r="S152" t="n">
         <v>15</v>
@@ -16835,7 +16826,6 @@
       <c r="AE152" t="b">
         <v>0</v>
       </c>
-      <c r="AF152" t="inlineStr"/>
       <c r="AG152" t="b">
         <v>0</v>
       </c>
@@ -16854,10 +16844,10 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>119806742</v>
+        <v>119806747</v>
       </c>
       <c r="B153" t="n">
-        <v>90582</v>
+        <v>90562</v>
       </c>
       <c r="C153" t="inlineStr">
         <is>
@@ -16870,34 +16860,34 @@
         </is>
       </c>
       <c r="E153" t="n">
-        <v>5442</v>
+        <v>1202</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I153" t="inlineStr"/>
       <c r="P153" t="inlineStr">
         <is>
-          <t>Sala-Norrby 1:8, Vstm</t>
+          <t>Sala-Norrby 1:3, Vstm</t>
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>572407</v>
+        <v>572528</v>
       </c>
       <c r="R153" t="n">
-        <v>6634973</v>
+        <v>6635097</v>
       </c>
       <c r="S153" t="n">
         <v>15</v>
@@ -16956,10 +16946,10 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>119806747</v>
+        <v>119806744</v>
       </c>
       <c r="B154" t="n">
-        <v>90562</v>
+        <v>8243</v>
       </c>
       <c r="C154" t="inlineStr">
         <is>
@@ -16972,34 +16962,43 @@
         </is>
       </c>
       <c r="E154" t="n">
-        <v>1202</v>
+        <v>106456</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granvivel</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pissodes harcyniae</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Herbst, 1795)</t>
         </is>
       </c>
       <c r="I154" t="inlineStr"/>
+      <c r="J154" t="inlineStr"/>
+      <c r="K154" t="inlineStr"/>
+      <c r="L154" t="inlineStr"/>
+      <c r="M154" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N154" t="inlineStr"/>
       <c r="P154" t="inlineStr">
         <is>
-          <t>Sala-Norrby 1:3, Vstm</t>
+          <t>Sala-Norrby 1:6, Vstm</t>
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>572528</v>
+        <v>572354</v>
       </c>
       <c r="R154" t="n">
-        <v>6635097</v>
+        <v>6635074</v>
       </c>
       <c r="S154" t="n">
         <v>15</v>
@@ -17040,6 +17039,7 @@
       <c r="AE154" t="b">
         <v>0</v>
       </c>
+      <c r="AF154" t="inlineStr"/>
       <c r="AG154" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 12276-2023 artfynd.xlsx
+++ b/artfynd/A 12276-2023 artfynd.xlsx
@@ -16301,10 +16301,10 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>119806746</v>
+        <v>119806742</v>
       </c>
       <c r="B148" t="n">
-        <v>97907</v>
+        <v>90582</v>
       </c>
       <c r="C148" t="inlineStr">
         <is>
@@ -16313,47 +16313,38 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E148" t="n">
-        <v>220787</v>
+        <v>5442</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I148" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K148" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I148" t="inlineStr"/>
       <c r="P148" t="inlineStr">
         <is>
-          <t>Sala-Norrby 1:4, Vstm</t>
+          <t>Sala-Norrby 1:8, Vstm</t>
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>572446</v>
+        <v>572407</v>
       </c>
       <c r="R148" t="n">
-        <v>6635218</v>
+        <v>6634973</v>
       </c>
       <c r="S148" t="n">
         <v>15</v>
@@ -16519,10 +16510,10 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>119806745</v>
+        <v>119807129</v>
       </c>
       <c r="B150" t="n">
-        <v>97907</v>
+        <v>25571</v>
       </c>
       <c r="C150" t="inlineStr">
         <is>
@@ -16531,47 +16522,47 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E150" t="n">
-        <v>220787</v>
+        <v>100659</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ljus vedstrit</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Cixidia lapponica</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I150" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Zetterstedt, 1838)</t>
+        </is>
+      </c>
+      <c r="I150" t="inlineStr"/>
+      <c r="J150" t="inlineStr"/>
       <c r="K150" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>larv/nymf</t>
+        </is>
+      </c>
+      <c r="L150" t="inlineStr"/>
+      <c r="M150" t="inlineStr"/>
+      <c r="N150" t="inlineStr"/>
       <c r="P150" t="inlineStr">
         <is>
-          <t>Sala-Norrby 1:5, Vstm</t>
+          <t>Sala-Norrby 1:10, Vstm</t>
         </is>
       </c>
       <c r="Q150" t="n">
         <v>572435</v>
       </c>
       <c r="R150" t="n">
-        <v>6635219</v>
+        <v>6634933</v>
       </c>
       <c r="S150" t="n">
         <v>15</v>
@@ -16612,6 +16603,7 @@
       <c r="AE150" t="b">
         <v>0</v>
       </c>
+      <c r="AF150" t="inlineStr"/>
       <c r="AG150" t="b">
         <v>0</v>
       </c>
@@ -16630,10 +16622,10 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>119807129</v>
+        <v>119806744</v>
       </c>
       <c r="B151" t="n">
-        <v>25571</v>
+        <v>8243</v>
       </c>
       <c r="C151" t="inlineStr">
         <is>
@@ -16642,47 +16634,47 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E151" t="n">
-        <v>100659</v>
+        <v>106456</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Ljus vedstrit</t>
+          <t>Granvivel</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Cixidia lapponica</t>
+          <t>Pissodes harcyniae</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(Zetterstedt, 1838)</t>
+          <t>(Herbst, 1795)</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
       <c r="J151" t="inlineStr"/>
-      <c r="K151" t="inlineStr">
-        <is>
-          <t>larv/nymf</t>
-        </is>
-      </c>
+      <c r="K151" t="inlineStr"/>
       <c r="L151" t="inlineStr"/>
-      <c r="M151" t="inlineStr"/>
+      <c r="M151" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="N151" t="inlineStr"/>
       <c r="P151" t="inlineStr">
         <is>
-          <t>Sala-Norrby 1:10, Vstm</t>
+          <t>Sala-Norrby 1:6, Vstm</t>
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>572435</v>
+        <v>572354</v>
       </c>
       <c r="R151" t="n">
-        <v>6634933</v>
+        <v>6635074</v>
       </c>
       <c r="S151" t="n">
         <v>15</v>
@@ -16742,10 +16734,10 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>119806742</v>
+        <v>119806746</v>
       </c>
       <c r="B152" t="n">
-        <v>90582</v>
+        <v>97907</v>
       </c>
       <c r="C152" t="inlineStr">
         <is>
@@ -16754,38 +16746,47 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E152" t="n">
-        <v>5442</v>
+        <v>220787</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I152" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I152" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K152" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P152" t="inlineStr">
         <is>
-          <t>Sala-Norrby 1:8, Vstm</t>
+          <t>Sala-Norrby 1:4, Vstm</t>
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>572407</v>
+        <v>572446</v>
       </c>
       <c r="R152" t="n">
-        <v>6634973</v>
+        <v>6635218</v>
       </c>
       <c r="S152" t="n">
         <v>15</v>
@@ -16844,10 +16845,10 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>119806747</v>
+        <v>119806745</v>
       </c>
       <c r="B153" t="n">
-        <v>90562</v>
+        <v>97907</v>
       </c>
       <c r="C153" t="inlineStr">
         <is>
@@ -16856,38 +16857,47 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E153" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I153" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I153" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K153" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P153" t="inlineStr">
         <is>
-          <t>Sala-Norrby 1:3, Vstm</t>
+          <t>Sala-Norrby 1:5, Vstm</t>
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>572528</v>
+        <v>572435</v>
       </c>
       <c r="R153" t="n">
-        <v>6635097</v>
+        <v>6635219</v>
       </c>
       <c r="S153" t="n">
         <v>15</v>
@@ -16946,10 +16956,10 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>119806744</v>
+        <v>119806747</v>
       </c>
       <c r="B154" t="n">
-        <v>8243</v>
+        <v>90562</v>
       </c>
       <c r="C154" t="inlineStr">
         <is>
@@ -16962,43 +16972,34 @@
         </is>
       </c>
       <c r="E154" t="n">
-        <v>106456</v>
+        <v>1202</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Granvivel</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Pissodes harcyniae</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>(Herbst, 1795)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I154" t="inlineStr"/>
-      <c r="J154" t="inlineStr"/>
-      <c r="K154" t="inlineStr"/>
-      <c r="L154" t="inlineStr"/>
-      <c r="M154" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N154" t="inlineStr"/>
       <c r="P154" t="inlineStr">
         <is>
-          <t>Sala-Norrby 1:6, Vstm</t>
+          <t>Sala-Norrby 1:3, Vstm</t>
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>572354</v>
+        <v>572528</v>
       </c>
       <c r="R154" t="n">
-        <v>6635074</v>
+        <v>6635097</v>
       </c>
       <c r="S154" t="n">
         <v>15</v>
@@ -17039,7 +17040,6 @@
       <c r="AE154" t="b">
         <v>0</v>
       </c>
-      <c r="AF154" t="inlineStr"/>
       <c r="AG154" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 12276-2023 artfynd.xlsx
+++ b/artfynd/A 12276-2023 artfynd.xlsx
@@ -16403,10 +16403,10 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>119806739</v>
+        <v>119806744</v>
       </c>
       <c r="B149" t="n">
-        <v>57326</v>
+        <v>8243</v>
       </c>
       <c r="C149" t="inlineStr">
         <is>
@@ -16419,39 +16419,43 @@
         </is>
       </c>
       <c r="E149" t="n">
-        <v>100049</v>
+        <v>106456</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Granvivel</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pissodes harcyniae</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Herbst, 1795)</t>
         </is>
       </c>
       <c r="I149" t="inlineStr"/>
+      <c r="J149" t="inlineStr"/>
+      <c r="K149" t="inlineStr"/>
+      <c r="L149" t="inlineStr"/>
       <c r="M149" t="inlineStr">
         <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N149" t="inlineStr"/>
       <c r="P149" t="inlineStr">
         <is>
-          <t>Sala-Norrby 1:11, Vstm</t>
+          <t>Sala-Norrby 1:6, Vstm</t>
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>572434</v>
+        <v>572354</v>
       </c>
       <c r="R149" t="n">
-        <v>6634940</v>
+        <v>6635074</v>
       </c>
       <c r="S149" t="n">
         <v>15</v>
@@ -16492,6 +16496,7 @@
       <c r="AE149" t="b">
         <v>0</v>
       </c>
+      <c r="AF149" t="inlineStr"/>
       <c r="AG149" t="b">
         <v>0</v>
       </c>
@@ -16622,10 +16627,10 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>119806744</v>
+        <v>119806739</v>
       </c>
       <c r="B151" t="n">
-        <v>8243</v>
+        <v>57326</v>
       </c>
       <c r="C151" t="inlineStr">
         <is>
@@ -16638,43 +16643,39 @@
         </is>
       </c>
       <c r="E151" t="n">
-        <v>106456</v>
+        <v>100049</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Granvivel</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Pissodes harcyniae</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(Herbst, 1795)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
-      <c r="J151" t="inlineStr"/>
-      <c r="K151" t="inlineStr"/>
-      <c r="L151" t="inlineStr"/>
       <c r="M151" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N151" t="inlineStr"/>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P151" t="inlineStr">
         <is>
-          <t>Sala-Norrby 1:6, Vstm</t>
+          <t>Sala-Norrby 1:11, Vstm</t>
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>572354</v>
+        <v>572434</v>
       </c>
       <c r="R151" t="n">
-        <v>6635074</v>
+        <v>6634940</v>
       </c>
       <c r="S151" t="n">
         <v>15</v>
@@ -16715,7 +16716,6 @@
       <c r="AE151" t="b">
         <v>0</v>
       </c>
-      <c r="AF151" t="inlineStr"/>
       <c r="AG151" t="b">
         <v>0</v>
       </c>
@@ -16845,10 +16845,10 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>119806745</v>
+        <v>119806747</v>
       </c>
       <c r="B153" t="n">
-        <v>97907</v>
+        <v>90562</v>
       </c>
       <c r="C153" t="inlineStr">
         <is>
@@ -16857,47 +16857,38 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E153" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I153" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K153" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I153" t="inlineStr"/>
       <c r="P153" t="inlineStr">
         <is>
-          <t>Sala-Norrby 1:5, Vstm</t>
+          <t>Sala-Norrby 1:3, Vstm</t>
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>572435</v>
+        <v>572528</v>
       </c>
       <c r="R153" t="n">
-        <v>6635219</v>
+        <v>6635097</v>
       </c>
       <c r="S153" t="n">
         <v>15</v>
@@ -16956,10 +16947,10 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>119806747</v>
+        <v>119806745</v>
       </c>
       <c r="B154" t="n">
-        <v>90562</v>
+        <v>97907</v>
       </c>
       <c r="C154" t="inlineStr">
         <is>
@@ -16968,38 +16959,47 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E154" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I154" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I154" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K154" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P154" t="inlineStr">
         <is>
-          <t>Sala-Norrby 1:3, Vstm</t>
+          <t>Sala-Norrby 1:5, Vstm</t>
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>572528</v>
+        <v>572435</v>
       </c>
       <c r="R154" t="n">
-        <v>6635097</v>
+        <v>6635219</v>
       </c>
       <c r="S154" t="n">
         <v>15</v>

--- a/artfynd/A 12276-2023 artfynd.xlsx
+++ b/artfynd/A 12276-2023 artfynd.xlsx
@@ -16301,10 +16301,10 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>119806742</v>
+        <v>119806747</v>
       </c>
       <c r="B148" t="n">
-        <v>90582</v>
+        <v>90562</v>
       </c>
       <c r="C148" t="inlineStr">
         <is>
@@ -16317,34 +16317,34 @@
         </is>
       </c>
       <c r="E148" t="n">
-        <v>5442</v>
+        <v>1202</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I148" t="inlineStr"/>
       <c r="P148" t="inlineStr">
         <is>
-          <t>Sala-Norrby 1:8, Vstm</t>
+          <t>Sala-Norrby 1:3, Vstm</t>
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>572407</v>
+        <v>572528</v>
       </c>
       <c r="R148" t="n">
-        <v>6634973</v>
+        <v>6635097</v>
       </c>
       <c r="S148" t="n">
         <v>15</v>
@@ -16403,10 +16403,10 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>119806744</v>
+        <v>119806742</v>
       </c>
       <c r="B149" t="n">
-        <v>8243</v>
+        <v>90582</v>
       </c>
       <c r="C149" t="inlineStr">
         <is>
@@ -16419,43 +16419,34 @@
         </is>
       </c>
       <c r="E149" t="n">
-        <v>106456</v>
+        <v>5442</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Granvivel</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Pissodes harcyniae</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(Herbst, 1795)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I149" t="inlineStr"/>
-      <c r="J149" t="inlineStr"/>
-      <c r="K149" t="inlineStr"/>
-      <c r="L149" t="inlineStr"/>
-      <c r="M149" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N149" t="inlineStr"/>
       <c r="P149" t="inlineStr">
         <is>
-          <t>Sala-Norrby 1:6, Vstm</t>
+          <t>Sala-Norrby 1:8, Vstm</t>
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>572354</v>
+        <v>572407</v>
       </c>
       <c r="R149" t="n">
-        <v>6635074</v>
+        <v>6634973</v>
       </c>
       <c r="S149" t="n">
         <v>15</v>
@@ -16496,7 +16487,6 @@
       <c r="AE149" t="b">
         <v>0</v>
       </c>
-      <c r="AF149" t="inlineStr"/>
       <c r="AG149" t="b">
         <v>0</v>
       </c>
@@ -16515,10 +16505,10 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>119807129</v>
+        <v>119806745</v>
       </c>
       <c r="B150" t="n">
-        <v>25571</v>
+        <v>97907</v>
       </c>
       <c r="C150" t="inlineStr">
         <is>
@@ -16527,47 +16517,47 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E150" t="n">
-        <v>100659</v>
+        <v>220787</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Ljus vedstrit</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Cixidia lapponica</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(Zetterstedt, 1838)</t>
-        </is>
-      </c>
-      <c r="I150" t="inlineStr"/>
-      <c r="J150" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I150" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K150" t="inlineStr">
         <is>
-          <t>larv/nymf</t>
-        </is>
-      </c>
-      <c r="L150" t="inlineStr"/>
-      <c r="M150" t="inlineStr"/>
-      <c r="N150" t="inlineStr"/>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P150" t="inlineStr">
         <is>
-          <t>Sala-Norrby 1:10, Vstm</t>
+          <t>Sala-Norrby 1:5, Vstm</t>
         </is>
       </c>
       <c r="Q150" t="n">
         <v>572435</v>
       </c>
       <c r="R150" t="n">
-        <v>6634933</v>
+        <v>6635219</v>
       </c>
       <c r="S150" t="n">
         <v>15</v>
@@ -16608,7 +16598,6 @@
       <c r="AE150" t="b">
         <v>0</v>
       </c>
-      <c r="AF150" t="inlineStr"/>
       <c r="AG150" t="b">
         <v>0</v>
       </c>
@@ -16627,10 +16616,10 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>119806739</v>
+        <v>119806746</v>
       </c>
       <c r="B151" t="n">
-        <v>57326</v>
+        <v>97907</v>
       </c>
       <c r="C151" t="inlineStr">
         <is>
@@ -16639,43 +16628,47 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E151" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I151" t="inlineStr"/>
-      <c r="M151" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I151" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K151" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P151" t="inlineStr">
         <is>
-          <t>Sala-Norrby 1:11, Vstm</t>
+          <t>Sala-Norrby 1:4, Vstm</t>
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>572434</v>
+        <v>572446</v>
       </c>
       <c r="R151" t="n">
-        <v>6634940</v>
+        <v>6635218</v>
       </c>
       <c r="S151" t="n">
         <v>15</v>
@@ -16734,10 +16727,10 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>119806746</v>
+        <v>119806744</v>
       </c>
       <c r="B152" t="n">
-        <v>97907</v>
+        <v>8243</v>
       </c>
       <c r="C152" t="inlineStr">
         <is>
@@ -16746,47 +16739,47 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E152" t="n">
-        <v>220787</v>
+        <v>106456</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Granvivel</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pissodes harcyniae</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I152" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K152" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Herbst, 1795)</t>
+        </is>
+      </c>
+      <c r="I152" t="inlineStr"/>
+      <c r="J152" t="inlineStr"/>
+      <c r="K152" t="inlineStr"/>
+      <c r="L152" t="inlineStr"/>
+      <c r="M152" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N152" t="inlineStr"/>
       <c r="P152" t="inlineStr">
         <is>
-          <t>Sala-Norrby 1:4, Vstm</t>
+          <t>Sala-Norrby 1:6, Vstm</t>
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>572446</v>
+        <v>572354</v>
       </c>
       <c r="R152" t="n">
-        <v>6635218</v>
+        <v>6635074</v>
       </c>
       <c r="S152" t="n">
         <v>15</v>
@@ -16827,6 +16820,7 @@
       <c r="AE152" t="b">
         <v>0</v>
       </c>
+      <c r="AF152" t="inlineStr"/>
       <c r="AG152" t="b">
         <v>0</v>
       </c>
@@ -16845,10 +16839,10 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>119806747</v>
+        <v>119806739</v>
       </c>
       <c r="B153" t="n">
-        <v>90562</v>
+        <v>57326</v>
       </c>
       <c r="C153" t="inlineStr">
         <is>
@@ -16861,34 +16855,39 @@
         </is>
       </c>
       <c r="E153" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I153" t="inlineStr"/>
+      <c r="M153" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P153" t="inlineStr">
         <is>
-          <t>Sala-Norrby 1:3, Vstm</t>
+          <t>Sala-Norrby 1:11, Vstm</t>
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>572528</v>
+        <v>572434</v>
       </c>
       <c r="R153" t="n">
-        <v>6635097</v>
+        <v>6634940</v>
       </c>
       <c r="S153" t="n">
         <v>15</v>
@@ -16947,10 +16946,10 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>119806745</v>
+        <v>119807129</v>
       </c>
       <c r="B154" t="n">
-        <v>97907</v>
+        <v>25571</v>
       </c>
       <c r="C154" t="inlineStr">
         <is>
@@ -16959,47 +16958,47 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E154" t="n">
-        <v>220787</v>
+        <v>100659</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ljus vedstrit</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Cixidia lapponica</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I154" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Zetterstedt, 1838)</t>
+        </is>
+      </c>
+      <c r="I154" t="inlineStr"/>
+      <c r="J154" t="inlineStr"/>
       <c r="K154" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>larv/nymf</t>
+        </is>
+      </c>
+      <c r="L154" t="inlineStr"/>
+      <c r="M154" t="inlineStr"/>
+      <c r="N154" t="inlineStr"/>
       <c r="P154" t="inlineStr">
         <is>
-          <t>Sala-Norrby 1:5, Vstm</t>
+          <t>Sala-Norrby 1:10, Vstm</t>
         </is>
       </c>
       <c r="Q154" t="n">
         <v>572435</v>
       </c>
       <c r="R154" t="n">
-        <v>6635219</v>
+        <v>6634933</v>
       </c>
       <c r="S154" t="n">
         <v>15</v>
@@ -17040,6 +17039,7 @@
       <c r="AE154" t="b">
         <v>0</v>
       </c>
+      <c r="AF154" t="inlineStr"/>
       <c r="AG154" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 12276-2023 artfynd.xlsx
+++ b/artfynd/A 12276-2023 artfynd.xlsx
@@ -16727,10 +16727,10 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>119806744</v>
+        <v>119806739</v>
       </c>
       <c r="B152" t="n">
-        <v>8243</v>
+        <v>57326</v>
       </c>
       <c r="C152" t="inlineStr">
         <is>
@@ -16743,43 +16743,39 @@
         </is>
       </c>
       <c r="E152" t="n">
-        <v>106456</v>
+        <v>100049</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Granvivel</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Pissodes harcyniae</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>(Herbst, 1795)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
-      <c r="J152" t="inlineStr"/>
-      <c r="K152" t="inlineStr"/>
-      <c r="L152" t="inlineStr"/>
       <c r="M152" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N152" t="inlineStr"/>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P152" t="inlineStr">
         <is>
-          <t>Sala-Norrby 1:6, Vstm</t>
+          <t>Sala-Norrby 1:11, Vstm</t>
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>572354</v>
+        <v>572434</v>
       </c>
       <c r="R152" t="n">
-        <v>6635074</v>
+        <v>6634940</v>
       </c>
       <c r="S152" t="n">
         <v>15</v>
@@ -16820,7 +16816,6 @@
       <c r="AE152" t="b">
         <v>0</v>
       </c>
-      <c r="AF152" t="inlineStr"/>
       <c r="AG152" t="b">
         <v>0</v>
       </c>
@@ -16839,10 +16834,10 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>119806739</v>
+        <v>119806744</v>
       </c>
       <c r="B153" t="n">
-        <v>57326</v>
+        <v>8243</v>
       </c>
       <c r="C153" t="inlineStr">
         <is>
@@ -16855,39 +16850,43 @@
         </is>
       </c>
       <c r="E153" t="n">
-        <v>100049</v>
+        <v>106456</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Granvivel</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pissodes harcyniae</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Herbst, 1795)</t>
         </is>
       </c>
       <c r="I153" t="inlineStr"/>
+      <c r="J153" t="inlineStr"/>
+      <c r="K153" t="inlineStr"/>
+      <c r="L153" t="inlineStr"/>
       <c r="M153" t="inlineStr">
         <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N153" t="inlineStr"/>
       <c r="P153" t="inlineStr">
         <is>
-          <t>Sala-Norrby 1:11, Vstm</t>
+          <t>Sala-Norrby 1:6, Vstm</t>
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>572434</v>
+        <v>572354</v>
       </c>
       <c r="R153" t="n">
-        <v>6634940</v>
+        <v>6635074</v>
       </c>
       <c r="S153" t="n">
         <v>15</v>
@@ -16928,6 +16927,7 @@
       <c r="AE153" t="b">
         <v>0</v>
       </c>
+      <c r="AF153" t="inlineStr"/>
       <c r="AG153" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 12276-2023 artfynd.xlsx
+++ b/artfynd/A 12276-2023 artfynd.xlsx
@@ -16301,10 +16301,10 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>119806747</v>
+        <v>119806745</v>
       </c>
       <c r="B148" t="n">
-        <v>90562</v>
+        <v>97930</v>
       </c>
       <c r="C148" t="inlineStr">
         <is>
@@ -16313,38 +16313,47 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E148" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I148" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I148" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K148" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P148" t="inlineStr">
         <is>
-          <t>Sala-Norrby 1:3, Vstm</t>
+          <t>Sala-Norrby 1:5, Vstm</t>
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>572528</v>
+        <v>572435</v>
       </c>
       <c r="R148" t="n">
-        <v>6635097</v>
+        <v>6635219</v>
       </c>
       <c r="S148" t="n">
         <v>15</v>
@@ -16403,10 +16412,10 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>119806742</v>
+        <v>119806746</v>
       </c>
       <c r="B149" t="n">
-        <v>90582</v>
+        <v>97930</v>
       </c>
       <c r="C149" t="inlineStr">
         <is>
@@ -16415,38 +16424,47 @@
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E149" t="n">
-        <v>5442</v>
+        <v>220787</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I149" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I149" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K149" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P149" t="inlineStr">
         <is>
-          <t>Sala-Norrby 1:8, Vstm</t>
+          <t>Sala-Norrby 1:4, Vstm</t>
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>572407</v>
+        <v>572446</v>
       </c>
       <c r="R149" t="n">
-        <v>6634973</v>
+        <v>6635218</v>
       </c>
       <c r="S149" t="n">
         <v>15</v>
@@ -16505,10 +16523,10 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>119806745</v>
+        <v>119806744</v>
       </c>
       <c r="B150" t="n">
-        <v>97907</v>
+        <v>8243</v>
       </c>
       <c r="C150" t="inlineStr">
         <is>
@@ -16517,47 +16535,47 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E150" t="n">
-        <v>220787</v>
+        <v>106456</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Granvivel</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pissodes harcyniae</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I150" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K150" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Herbst, 1795)</t>
+        </is>
+      </c>
+      <c r="I150" t="inlineStr"/>
+      <c r="J150" t="inlineStr"/>
+      <c r="K150" t="inlineStr"/>
+      <c r="L150" t="inlineStr"/>
+      <c r="M150" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N150" t="inlineStr"/>
       <c r="P150" t="inlineStr">
         <is>
-          <t>Sala-Norrby 1:5, Vstm</t>
+          <t>Sala-Norrby 1:6, Vstm</t>
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>572435</v>
+        <v>572354</v>
       </c>
       <c r="R150" t="n">
-        <v>6635219</v>
+        <v>6635074</v>
       </c>
       <c r="S150" t="n">
         <v>15</v>
@@ -16598,6 +16616,7 @@
       <c r="AE150" t="b">
         <v>0</v>
       </c>
+      <c r="AF150" t="inlineStr"/>
       <c r="AG150" t="b">
         <v>0</v>
       </c>
@@ -16616,10 +16635,10 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>119806746</v>
+        <v>119806742</v>
       </c>
       <c r="B151" t="n">
-        <v>97907</v>
+        <v>90600</v>
       </c>
       <c r="C151" t="inlineStr">
         <is>
@@ -16628,47 +16647,38 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E151" t="n">
-        <v>220787</v>
+        <v>5442</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I151" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K151" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I151" t="inlineStr"/>
       <c r="P151" t="inlineStr">
         <is>
-          <t>Sala-Norrby 1:4, Vstm</t>
+          <t>Sala-Norrby 1:8, Vstm</t>
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>572446</v>
+        <v>572407</v>
       </c>
       <c r="R151" t="n">
-        <v>6635218</v>
+        <v>6634973</v>
       </c>
       <c r="S151" t="n">
         <v>15</v>
@@ -16727,10 +16737,10 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>119806739</v>
+        <v>119806747</v>
       </c>
       <c r="B152" t="n">
-        <v>57326</v>
+        <v>90580</v>
       </c>
       <c r="C152" t="inlineStr">
         <is>
@@ -16743,39 +16753,34 @@
         </is>
       </c>
       <c r="E152" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
-      <c r="M152" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P152" t="inlineStr">
         <is>
-          <t>Sala-Norrby 1:11, Vstm</t>
+          <t>Sala-Norrby 1:3, Vstm</t>
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>572434</v>
+        <v>572528</v>
       </c>
       <c r="R152" t="n">
-        <v>6634940</v>
+        <v>6635097</v>
       </c>
       <c r="S152" t="n">
         <v>15</v>
@@ -16834,10 +16839,10 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>119806744</v>
+        <v>119807129</v>
       </c>
       <c r="B153" t="n">
-        <v>8243</v>
+        <v>25578</v>
       </c>
       <c r="C153" t="inlineStr">
         <is>
@@ -16846,47 +16851,47 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E153" t="n">
-        <v>106456</v>
+        <v>100659</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Granvivel</t>
+          <t>Ljus vedstrit</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Pissodes harcyniae</t>
+          <t>Cixidia lapponica</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>(Herbst, 1795)</t>
+          <t>(Zetterstedt, 1838)</t>
         </is>
       </c>
       <c r="I153" t="inlineStr"/>
       <c r="J153" t="inlineStr"/>
-      <c r="K153" t="inlineStr"/>
+      <c r="K153" t="inlineStr">
+        <is>
+          <t>larv/nymf</t>
+        </is>
+      </c>
       <c r="L153" t="inlineStr"/>
-      <c r="M153" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
+      <c r="M153" t="inlineStr"/>
       <c r="N153" t="inlineStr"/>
       <c r="P153" t="inlineStr">
         <is>
-          <t>Sala-Norrby 1:6, Vstm</t>
+          <t>Sala-Norrby 1:10, Vstm</t>
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>572354</v>
+        <v>572435</v>
       </c>
       <c r="R153" t="n">
-        <v>6635074</v>
+        <v>6634933</v>
       </c>
       <c r="S153" t="n">
         <v>15</v>
@@ -16946,10 +16951,10 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>119807129</v>
+        <v>119806739</v>
       </c>
       <c r="B154" t="n">
-        <v>25571</v>
+        <v>57336</v>
       </c>
       <c r="C154" t="inlineStr">
         <is>
@@ -16958,47 +16963,43 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E154" t="n">
-        <v>100659</v>
+        <v>100049</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Ljus vedstrit</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Cixidia lapponica</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>(Zetterstedt, 1838)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I154" t="inlineStr"/>
-      <c r="J154" t="inlineStr"/>
-      <c r="K154" t="inlineStr">
-        <is>
-          <t>larv/nymf</t>
-        </is>
-      </c>
-      <c r="L154" t="inlineStr"/>
-      <c r="M154" t="inlineStr"/>
-      <c r="N154" t="inlineStr"/>
+      <c r="M154" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P154" t="inlineStr">
         <is>
-          <t>Sala-Norrby 1:10, Vstm</t>
+          <t>Sala-Norrby 1:11, Vstm</t>
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>572435</v>
+        <v>572434</v>
       </c>
       <c r="R154" t="n">
-        <v>6634933</v>
+        <v>6634940</v>
       </c>
       <c r="S154" t="n">
         <v>15</v>
@@ -17039,7 +17040,6 @@
       <c r="AE154" t="b">
         <v>0</v>
       </c>
-      <c r="AF154" t="inlineStr"/>
       <c r="AG154" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 12276-2023 artfynd.xlsx
+++ b/artfynd/A 12276-2023 artfynd.xlsx
@@ -16301,10 +16301,10 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>119806745</v>
+        <v>119807129</v>
       </c>
       <c r="B148" t="n">
-        <v>97930</v>
+        <v>25578</v>
       </c>
       <c r="C148" t="inlineStr">
         <is>
@@ -16313,47 +16313,47 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E148" t="n">
-        <v>220787</v>
+        <v>100659</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ljus vedstrit</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Cixidia lapponica</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I148" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Zetterstedt, 1838)</t>
+        </is>
+      </c>
+      <c r="I148" t="inlineStr"/>
+      <c r="J148" t="inlineStr"/>
       <c r="K148" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>larv/nymf</t>
+        </is>
+      </c>
+      <c r="L148" t="inlineStr"/>
+      <c r="M148" t="inlineStr"/>
+      <c r="N148" t="inlineStr"/>
       <c r="P148" t="inlineStr">
         <is>
-          <t>Sala-Norrby 1:5, Vstm</t>
+          <t>Sala-Norrby 1:10, Vstm</t>
         </is>
       </c>
       <c r="Q148" t="n">
         <v>572435</v>
       </c>
       <c r="R148" t="n">
-        <v>6635219</v>
+        <v>6634933</v>
       </c>
       <c r="S148" t="n">
         <v>15</v>
@@ -16394,6 +16394,7 @@
       <c r="AE148" t="b">
         <v>0</v>
       </c>
+      <c r="AF148" t="inlineStr"/>
       <c r="AG148" t="b">
         <v>0</v>
       </c>
@@ -16412,10 +16413,10 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>119806746</v>
+        <v>119806739</v>
       </c>
       <c r="B149" t="n">
-        <v>97930</v>
+        <v>57336</v>
       </c>
       <c r="C149" t="inlineStr">
         <is>
@@ -16424,47 +16425,43 @@
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E149" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I149" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K149" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I149" t="inlineStr"/>
+      <c r="M149" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P149" t="inlineStr">
         <is>
-          <t>Sala-Norrby 1:4, Vstm</t>
+          <t>Sala-Norrby 1:11, Vstm</t>
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>572446</v>
+        <v>572434</v>
       </c>
       <c r="R149" t="n">
-        <v>6635218</v>
+        <v>6634940</v>
       </c>
       <c r="S149" t="n">
         <v>15</v>
@@ -16523,10 +16520,10 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>119806744</v>
+        <v>119806745</v>
       </c>
       <c r="B150" t="n">
-        <v>8243</v>
+        <v>97930</v>
       </c>
       <c r="C150" t="inlineStr">
         <is>
@@ -16535,47 +16532,47 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E150" t="n">
-        <v>106456</v>
+        <v>220787</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Granvivel</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Pissodes harcyniae</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(Herbst, 1795)</t>
-        </is>
-      </c>
-      <c r="I150" t="inlineStr"/>
-      <c r="J150" t="inlineStr"/>
-      <c r="K150" t="inlineStr"/>
-      <c r="L150" t="inlineStr"/>
-      <c r="M150" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N150" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I150" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K150" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P150" t="inlineStr">
         <is>
-          <t>Sala-Norrby 1:6, Vstm</t>
+          <t>Sala-Norrby 1:5, Vstm</t>
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>572354</v>
+        <v>572435</v>
       </c>
       <c r="R150" t="n">
-        <v>6635074</v>
+        <v>6635219</v>
       </c>
       <c r="S150" t="n">
         <v>15</v>
@@ -16616,7 +16613,6 @@
       <c r="AE150" t="b">
         <v>0</v>
       </c>
-      <c r="AF150" t="inlineStr"/>
       <c r="AG150" t="b">
         <v>0</v>
       </c>
@@ -16839,10 +16835,10 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>119807129</v>
+        <v>119806744</v>
       </c>
       <c r="B153" t="n">
-        <v>25578</v>
+        <v>8243</v>
       </c>
       <c r="C153" t="inlineStr">
         <is>
@@ -16851,47 +16847,47 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E153" t="n">
-        <v>100659</v>
+        <v>106456</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Ljus vedstrit</t>
+          <t>Granvivel</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Cixidia lapponica</t>
+          <t>Pissodes harcyniae</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>(Zetterstedt, 1838)</t>
+          <t>(Herbst, 1795)</t>
         </is>
       </c>
       <c r="I153" t="inlineStr"/>
       <c r="J153" t="inlineStr"/>
-      <c r="K153" t="inlineStr">
-        <is>
-          <t>larv/nymf</t>
-        </is>
-      </c>
+      <c r="K153" t="inlineStr"/>
       <c r="L153" t="inlineStr"/>
-      <c r="M153" t="inlineStr"/>
+      <c r="M153" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="N153" t="inlineStr"/>
       <c r="P153" t="inlineStr">
         <is>
-          <t>Sala-Norrby 1:10, Vstm</t>
+          <t>Sala-Norrby 1:6, Vstm</t>
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>572435</v>
+        <v>572354</v>
       </c>
       <c r="R153" t="n">
-        <v>6634933</v>
+        <v>6635074</v>
       </c>
       <c r="S153" t="n">
         <v>15</v>
@@ -16951,10 +16947,10 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>119806739</v>
+        <v>119806746</v>
       </c>
       <c r="B154" t="n">
-        <v>57336</v>
+        <v>97930</v>
       </c>
       <c r="C154" t="inlineStr">
         <is>
@@ -16963,43 +16959,47 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E154" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I154" t="inlineStr"/>
-      <c r="M154" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I154" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K154" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P154" t="inlineStr">
         <is>
-          <t>Sala-Norrby 1:11, Vstm</t>
+          <t>Sala-Norrby 1:4, Vstm</t>
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>572434</v>
+        <v>572446</v>
       </c>
       <c r="R154" t="n">
-        <v>6634940</v>
+        <v>6635218</v>
       </c>
       <c r="S154" t="n">
         <v>15</v>

--- a/artfynd/A 12276-2023 artfynd.xlsx
+++ b/artfynd/A 12276-2023 artfynd.xlsx
@@ -16416,11 +16416,11 @@
         <v>119806739</v>
       </c>
       <c r="B149" t="n">
-        <v>57336</v>
+        <v>57381</v>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Behöver inte valideras</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">

--- a/artfynd/A 12276-2023 artfynd.xlsx
+++ b/artfynd/A 12276-2023 artfynd.xlsx
@@ -16416,7 +16416,7 @@
         <v>119806739</v>
       </c>
       <c r="B149" t="n">
-        <v>57381</v>
+        <v>57385</v>
       </c>
       <c r="C149" t="inlineStr">
         <is>

--- a/artfynd/A 12276-2023 artfynd.xlsx
+++ b/artfynd/A 12276-2023 artfynd.xlsx
@@ -16416,7 +16416,7 @@
         <v>119806739</v>
       </c>
       <c r="B149" t="n">
-        <v>57385</v>
+        <v>57388</v>
       </c>
       <c r="C149" t="inlineStr">
         <is>

--- a/artfynd/A 12276-2023 artfynd.xlsx
+++ b/artfynd/A 12276-2023 artfynd.xlsx
@@ -16416,7 +16416,7 @@
         <v>119806739</v>
       </c>
       <c r="B149" t="n">
-        <v>57388</v>
+        <v>57390</v>
       </c>
       <c r="C149" t="inlineStr">
         <is>

--- a/artfynd/A 12276-2023 artfynd.xlsx
+++ b/artfynd/A 12276-2023 artfynd.xlsx
@@ -16416,7 +16416,7 @@
         <v>119806739</v>
       </c>
       <c r="B149" t="n">
-        <v>57390</v>
+        <v>57395</v>
       </c>
       <c r="C149" t="inlineStr">
         <is>

--- a/artfynd/A 12276-2023 artfynd.xlsx
+++ b/artfynd/A 12276-2023 artfynd.xlsx
@@ -16431,11 +16431,6 @@
       <c r="E149" t="n">
         <v>100049</v>
       </c>
-      <c r="F149" t="inlineStr">
-        <is>
-          <t>Spillkråka</t>
-        </is>
-      </c>
       <c r="G149" t="inlineStr">
         <is>
           <t>Dryocopus martius</t>

--- a/artfynd/A 12276-2023 artfynd.xlsx
+++ b/artfynd/A 12276-2023 artfynd.xlsx
@@ -16416,7 +16416,7 @@
         <v>119806739</v>
       </c>
       <c r="B149" t="n">
-        <v>57395</v>
+        <v>57399</v>
       </c>
       <c r="C149" t="inlineStr">
         <is>
@@ -16430,6 +16430,11 @@
       </c>
       <c r="E149" t="n">
         <v>100049</v>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>

--- a/artfynd/A 12276-2023 artfynd.xlsx
+++ b/artfynd/A 12276-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY154"/>
+  <dimension ref="A1:AY179"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17056,6 +17056,2446 @@
       </c>
       <c r="AY154" t="inlineStr"/>
     </row>
+    <row r="155">
+      <c r="A155" t="n">
+        <v>129419047</v>
+      </c>
+      <c r="B155" t="n">
+        <v>92814</v>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E155" t="n">
+        <v>4361</v>
+      </c>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>Orange taggsvamp</t>
+        </is>
+      </c>
+      <c r="G155" t="inlineStr">
+        <is>
+          <t>Hydnellum aurantiacum</t>
+        </is>
+      </c>
+      <c r="H155" t="inlineStr">
+        <is>
+          <t>(Batsch:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I155" t="inlineStr"/>
+      <c r="P155" t="inlineStr">
+        <is>
+          <t>Väst Norrby gamla tomt, Vstm</t>
+        </is>
+      </c>
+      <c r="Q155" t="n">
+        <v>572518</v>
+      </c>
+      <c r="R155" t="n">
+        <v>6635261</v>
+      </c>
+      <c r="S155" t="n">
+        <v>10</v>
+      </c>
+      <c r="T155" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U155" t="inlineStr">
+        <is>
+          <t>Sala</t>
+        </is>
+      </c>
+      <c r="V155" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W155" t="inlineStr">
+        <is>
+          <t>Fläckebo</t>
+        </is>
+      </c>
+      <c r="Y155" t="inlineStr">
+        <is>
+          <t>2025-09-05</t>
+        </is>
+      </c>
+      <c r="AA155" t="inlineStr">
+        <is>
+          <t>2025-09-05</t>
+        </is>
+      </c>
+      <c r="AD155" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE155" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG155" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT155" t="inlineStr"/>
+      <c r="AW155" t="inlineStr">
+        <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AX155" t="inlineStr">
+        <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AY155" t="inlineStr"/>
+    </row>
+    <row r="156">
+      <c r="A156" t="n">
+        <v>129419026</v>
+      </c>
+      <c r="B156" t="n">
+        <v>91504</v>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E156" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G156" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H156" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I156" t="inlineStr"/>
+      <c r="P156" t="inlineStr">
+        <is>
+          <t>Väst Norrby gamla tomt, Vstm</t>
+        </is>
+      </c>
+      <c r="Q156" t="n">
+        <v>572557</v>
+      </c>
+      <c r="R156" t="n">
+        <v>6635008</v>
+      </c>
+      <c r="S156" t="n">
+        <v>10</v>
+      </c>
+      <c r="T156" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U156" t="inlineStr">
+        <is>
+          <t>Sala</t>
+        </is>
+      </c>
+      <c r="V156" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W156" t="inlineStr">
+        <is>
+          <t>Fläckebo</t>
+        </is>
+      </c>
+      <c r="Y156" t="inlineStr">
+        <is>
+          <t>2025-09-05</t>
+        </is>
+      </c>
+      <c r="AA156" t="inlineStr">
+        <is>
+          <t>2025-09-05</t>
+        </is>
+      </c>
+      <c r="AD156" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE156" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG156" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT156" t="inlineStr"/>
+      <c r="AW156" t="inlineStr">
+        <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AX156" t="inlineStr">
+        <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AY156" t="inlineStr"/>
+    </row>
+    <row r="157">
+      <c r="A157" t="n">
+        <v>129419048</v>
+      </c>
+      <c r="B157" t="n">
+        <v>98706</v>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E157" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G157" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H157" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I157" t="inlineStr"/>
+      <c r="P157" t="inlineStr">
+        <is>
+          <t>Väst Norrby gamla tomt, Vstm</t>
+        </is>
+      </c>
+      <c r="Q157" t="n">
+        <v>572387</v>
+      </c>
+      <c r="R157" t="n">
+        <v>6635335</v>
+      </c>
+      <c r="S157" t="n">
+        <v>10</v>
+      </c>
+      <c r="T157" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U157" t="inlineStr">
+        <is>
+          <t>Sala</t>
+        </is>
+      </c>
+      <c r="V157" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W157" t="inlineStr">
+        <is>
+          <t>Fläckebo</t>
+        </is>
+      </c>
+      <c r="Y157" t="inlineStr">
+        <is>
+          <t>2025-09-05</t>
+        </is>
+      </c>
+      <c r="AA157" t="inlineStr">
+        <is>
+          <t>2025-09-05</t>
+        </is>
+      </c>
+      <c r="AD157" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE157" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG157" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT157" t="inlineStr"/>
+      <c r="AW157" t="inlineStr">
+        <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AX157" t="inlineStr">
+        <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AY157" t="inlineStr"/>
+    </row>
+    <row r="158">
+      <c r="A158" t="n">
+        <v>129419028</v>
+      </c>
+      <c r="B158" t="n">
+        <v>91540</v>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E158" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G158" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H158" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I158" t="inlineStr"/>
+      <c r="P158" t="inlineStr">
+        <is>
+          <t>Väst Norrby gamla tomt, Vstm</t>
+        </is>
+      </c>
+      <c r="Q158" t="n">
+        <v>572482</v>
+      </c>
+      <c r="R158" t="n">
+        <v>6635208</v>
+      </c>
+      <c r="S158" t="n">
+        <v>10</v>
+      </c>
+      <c r="T158" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U158" t="inlineStr">
+        <is>
+          <t>Sala</t>
+        </is>
+      </c>
+      <c r="V158" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W158" t="inlineStr">
+        <is>
+          <t>Fläckebo</t>
+        </is>
+      </c>
+      <c r="Y158" t="inlineStr">
+        <is>
+          <t>2025-09-05</t>
+        </is>
+      </c>
+      <c r="AA158" t="inlineStr">
+        <is>
+          <t>2025-09-05</t>
+        </is>
+      </c>
+      <c r="AD158" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE158" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG158" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT158" t="inlineStr"/>
+      <c r="AW158" t="inlineStr">
+        <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AX158" t="inlineStr">
+        <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AY158" t="inlineStr"/>
+    </row>
+    <row r="159">
+      <c r="A159" t="n">
+        <v>129419032</v>
+      </c>
+      <c r="B159" t="n">
+        <v>91540</v>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E159" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G159" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H159" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I159" t="inlineStr"/>
+      <c r="P159" t="inlineStr">
+        <is>
+          <t>Väst Norrby gamla tomt, Vstm</t>
+        </is>
+      </c>
+      <c r="Q159" t="n">
+        <v>572369</v>
+      </c>
+      <c r="R159" t="n">
+        <v>6635093</v>
+      </c>
+      <c r="S159" t="n">
+        <v>10</v>
+      </c>
+      <c r="T159" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U159" t="inlineStr">
+        <is>
+          <t>Sala</t>
+        </is>
+      </c>
+      <c r="V159" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W159" t="inlineStr">
+        <is>
+          <t>Fläckebo</t>
+        </is>
+      </c>
+      <c r="Y159" t="inlineStr">
+        <is>
+          <t>2025-09-05</t>
+        </is>
+      </c>
+      <c r="AA159" t="inlineStr">
+        <is>
+          <t>2025-09-05</t>
+        </is>
+      </c>
+      <c r="AD159" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE159" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG159" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT159" t="inlineStr"/>
+      <c r="AW159" t="inlineStr">
+        <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AX159" t="inlineStr">
+        <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AY159" t="inlineStr"/>
+    </row>
+    <row r="160">
+      <c r="A160" t="n">
+        <v>129419034</v>
+      </c>
+      <c r="B160" t="n">
+        <v>91540</v>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E160" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G160" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H160" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I160" t="inlineStr"/>
+      <c r="P160" t="inlineStr">
+        <is>
+          <t>Väst Norrby gamla tomt, Vstm</t>
+        </is>
+      </c>
+      <c r="Q160" t="n">
+        <v>572518</v>
+      </c>
+      <c r="R160" t="n">
+        <v>6635088</v>
+      </c>
+      <c r="S160" t="n">
+        <v>10</v>
+      </c>
+      <c r="T160" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U160" t="inlineStr">
+        <is>
+          <t>Sala</t>
+        </is>
+      </c>
+      <c r="V160" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W160" t="inlineStr">
+        <is>
+          <t>Fläckebo</t>
+        </is>
+      </c>
+      <c r="Y160" t="inlineStr">
+        <is>
+          <t>2025-09-05</t>
+        </is>
+      </c>
+      <c r="AA160" t="inlineStr">
+        <is>
+          <t>2025-09-05</t>
+        </is>
+      </c>
+      <c r="AD160" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE160" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG160" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT160" t="inlineStr"/>
+      <c r="AW160" t="inlineStr">
+        <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AX160" t="inlineStr">
+        <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AY160" t="inlineStr"/>
+    </row>
+    <row r="161">
+      <c r="A161" t="n">
+        <v>129419027</v>
+      </c>
+      <c r="B161" t="n">
+        <v>91504</v>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E161" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F161" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G161" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H161" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I161" t="inlineStr"/>
+      <c r="P161" t="inlineStr">
+        <is>
+          <t>Väst Norrby gamla tomt, Vstm</t>
+        </is>
+      </c>
+      <c r="Q161" t="n">
+        <v>572637</v>
+      </c>
+      <c r="R161" t="n">
+        <v>6635268</v>
+      </c>
+      <c r="S161" t="n">
+        <v>10</v>
+      </c>
+      <c r="T161" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U161" t="inlineStr">
+        <is>
+          <t>Sala</t>
+        </is>
+      </c>
+      <c r="V161" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W161" t="inlineStr">
+        <is>
+          <t>Fläckebo</t>
+        </is>
+      </c>
+      <c r="Y161" t="inlineStr">
+        <is>
+          <t>2025-09-05</t>
+        </is>
+      </c>
+      <c r="AA161" t="inlineStr">
+        <is>
+          <t>2025-09-05</t>
+        </is>
+      </c>
+      <c r="AD161" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE161" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG161" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT161" t="inlineStr"/>
+      <c r="AW161" t="inlineStr">
+        <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AX161" t="inlineStr">
+        <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AY161" t="inlineStr"/>
+    </row>
+    <row r="162">
+      <c r="A162" t="n">
+        <v>129419029</v>
+      </c>
+      <c r="B162" t="n">
+        <v>91540</v>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E162" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F162" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G162" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H162" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I162" t="inlineStr"/>
+      <c r="P162" t="inlineStr">
+        <is>
+          <t>Väst Norrby gamla tomt, Vstm</t>
+        </is>
+      </c>
+      <c r="Q162" t="n">
+        <v>572434</v>
+      </c>
+      <c r="R162" t="n">
+        <v>6635240</v>
+      </c>
+      <c r="S162" t="n">
+        <v>10</v>
+      </c>
+      <c r="T162" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U162" t="inlineStr">
+        <is>
+          <t>Sala</t>
+        </is>
+      </c>
+      <c r="V162" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W162" t="inlineStr">
+        <is>
+          <t>Fläckebo</t>
+        </is>
+      </c>
+      <c r="Y162" t="inlineStr">
+        <is>
+          <t>2025-09-05</t>
+        </is>
+      </c>
+      <c r="AA162" t="inlineStr">
+        <is>
+          <t>2025-09-05</t>
+        </is>
+      </c>
+      <c r="AD162" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE162" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG162" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT162" t="inlineStr"/>
+      <c r="AW162" t="inlineStr">
+        <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AX162" t="inlineStr">
+        <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AY162" t="inlineStr"/>
+    </row>
+    <row r="163">
+      <c r="A163" t="n">
+        <v>129419052</v>
+      </c>
+      <c r="B163" t="n">
+        <v>90922</v>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E163" t="n">
+        <v>5685</v>
+      </c>
+      <c r="F163" t="inlineStr">
+        <is>
+          <t>Gullgröppa</t>
+        </is>
+      </c>
+      <c r="G163" t="inlineStr">
+        <is>
+          <t>Pseudomerulius aureus</t>
+        </is>
+      </c>
+      <c r="H163" t="inlineStr">
+        <is>
+          <t>(Fr.) Jülich</t>
+        </is>
+      </c>
+      <c r="I163" t="inlineStr"/>
+      <c r="P163" t="inlineStr">
+        <is>
+          <t>Väst Norrby gamla tomt, Vstm</t>
+        </is>
+      </c>
+      <c r="Q163" t="n">
+        <v>572365</v>
+      </c>
+      <c r="R163" t="n">
+        <v>6635062</v>
+      </c>
+      <c r="S163" t="n">
+        <v>10</v>
+      </c>
+      <c r="T163" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U163" t="inlineStr">
+        <is>
+          <t>Sala</t>
+        </is>
+      </c>
+      <c r="V163" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W163" t="inlineStr">
+        <is>
+          <t>Fläckebo</t>
+        </is>
+      </c>
+      <c r="Y163" t="inlineStr">
+        <is>
+          <t>2025-09-05</t>
+        </is>
+      </c>
+      <c r="AA163" t="inlineStr">
+        <is>
+          <t>2025-09-05</t>
+        </is>
+      </c>
+      <c r="AD163" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE163" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG163" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT163" t="inlineStr"/>
+      <c r="AW163" t="inlineStr">
+        <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AX163" t="inlineStr">
+        <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AY163" t="inlineStr"/>
+    </row>
+    <row r="164">
+      <c r="A164" t="n">
+        <v>129419063</v>
+      </c>
+      <c r="B164" t="n">
+        <v>91410</v>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E164" t="n">
+        <v>3290</v>
+      </c>
+      <c r="F164" t="inlineStr">
+        <is>
+          <t>Gaffelskinn</t>
+        </is>
+      </c>
+      <c r="G164" t="inlineStr">
+        <is>
+          <t>Clavulicium macounii</t>
+        </is>
+      </c>
+      <c r="H164" t="inlineStr">
+        <is>
+          <t>(Burt) J.Erikss. &amp; Boidin ex Parmasto</t>
+        </is>
+      </c>
+      <c r="I164" t="inlineStr"/>
+      <c r="P164" t="inlineStr">
+        <is>
+          <t>Väst Norrby gamla tomt, Vstm</t>
+        </is>
+      </c>
+      <c r="Q164" t="n">
+        <v>572505</v>
+      </c>
+      <c r="R164" t="n">
+        <v>6635049</v>
+      </c>
+      <c r="S164" t="n">
+        <v>10</v>
+      </c>
+      <c r="T164" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U164" t="inlineStr">
+        <is>
+          <t>Sala</t>
+        </is>
+      </c>
+      <c r="V164" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W164" t="inlineStr">
+        <is>
+          <t>Fläckebo</t>
+        </is>
+      </c>
+      <c r="Y164" t="inlineStr">
+        <is>
+          <t>2025-09-05</t>
+        </is>
+      </c>
+      <c r="AA164" t="inlineStr">
+        <is>
+          <t>2025-09-05</t>
+        </is>
+      </c>
+      <c r="AD164" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE164" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG164" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT164" t="inlineStr"/>
+      <c r="AW164" t="inlineStr">
+        <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AX164" t="inlineStr">
+        <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AY164" t="inlineStr"/>
+    </row>
+    <row r="165">
+      <c r="A165" t="n">
+        <v>129419035</v>
+      </c>
+      <c r="B165" t="n">
+        <v>91540</v>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E165" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F165" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G165" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H165" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I165" t="inlineStr"/>
+      <c r="P165" t="inlineStr">
+        <is>
+          <t>Väst Norrby gamla tomt, Vstm</t>
+        </is>
+      </c>
+      <c r="Q165" t="n">
+        <v>572625</v>
+      </c>
+      <c r="R165" t="n">
+        <v>6635270</v>
+      </c>
+      <c r="S165" t="n">
+        <v>10</v>
+      </c>
+      <c r="T165" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U165" t="inlineStr">
+        <is>
+          <t>Sala</t>
+        </is>
+      </c>
+      <c r="V165" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W165" t="inlineStr">
+        <is>
+          <t>Fläckebo</t>
+        </is>
+      </c>
+      <c r="Y165" t="inlineStr">
+        <is>
+          <t>2025-09-05</t>
+        </is>
+      </c>
+      <c r="AA165" t="inlineStr">
+        <is>
+          <t>2025-09-05</t>
+        </is>
+      </c>
+      <c r="AD165" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE165" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG165" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT165" t="inlineStr"/>
+      <c r="AW165" t="inlineStr">
+        <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AX165" t="inlineStr">
+        <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AY165" t="inlineStr"/>
+    </row>
+    <row r="166">
+      <c r="A166" t="n">
+        <v>129419024</v>
+      </c>
+      <c r="B166" t="n">
+        <v>91504</v>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E166" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F166" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G166" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H166" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I166" t="inlineStr"/>
+      <c r="P166" t="inlineStr">
+        <is>
+          <t>Väst Norrby gamla tomt, Vstm</t>
+        </is>
+      </c>
+      <c r="Q166" t="n">
+        <v>572501</v>
+      </c>
+      <c r="R166" t="n">
+        <v>6635056</v>
+      </c>
+      <c r="S166" t="n">
+        <v>10</v>
+      </c>
+      <c r="T166" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U166" t="inlineStr">
+        <is>
+          <t>Sala</t>
+        </is>
+      </c>
+      <c r="V166" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W166" t="inlineStr">
+        <is>
+          <t>Fläckebo</t>
+        </is>
+      </c>
+      <c r="Y166" t="inlineStr">
+        <is>
+          <t>2025-09-05</t>
+        </is>
+      </c>
+      <c r="AA166" t="inlineStr">
+        <is>
+          <t>2025-09-05</t>
+        </is>
+      </c>
+      <c r="AD166" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE166" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG166" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT166" t="inlineStr"/>
+      <c r="AW166" t="inlineStr">
+        <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AX166" t="inlineStr">
+        <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AY166" t="inlineStr"/>
+    </row>
+    <row r="167">
+      <c r="A167" t="n">
+        <v>129419041</v>
+      </c>
+      <c r="B167" t="n">
+        <v>92462</v>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E167" t="n">
+        <v>4740</v>
+      </c>
+      <c r="F167" t="inlineStr">
+        <is>
+          <t>Sotriska</t>
+        </is>
+      </c>
+      <c r="G167" t="inlineStr">
+        <is>
+          <t>Lactarius lignyotus</t>
+        </is>
+      </c>
+      <c r="H167" t="inlineStr">
+        <is>
+          <t>Fr.</t>
+        </is>
+      </c>
+      <c r="I167" t="inlineStr"/>
+      <c r="P167" t="inlineStr">
+        <is>
+          <t>Väst Norrby gamla tomt, Vstm</t>
+        </is>
+      </c>
+      <c r="Q167" t="n">
+        <v>572441</v>
+      </c>
+      <c r="R167" t="n">
+        <v>6634990</v>
+      </c>
+      <c r="S167" t="n">
+        <v>10</v>
+      </c>
+      <c r="T167" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U167" t="inlineStr">
+        <is>
+          <t>Sala</t>
+        </is>
+      </c>
+      <c r="V167" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W167" t="inlineStr">
+        <is>
+          <t>Fläckebo</t>
+        </is>
+      </c>
+      <c r="Y167" t="inlineStr">
+        <is>
+          <t>2025-09-05</t>
+        </is>
+      </c>
+      <c r="AA167" t="inlineStr">
+        <is>
+          <t>2025-09-05</t>
+        </is>
+      </c>
+      <c r="AD167" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE167" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG167" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO167" t="inlineStr">
+        <is>
+          <t>tallåga</t>
+        </is>
+      </c>
+      <c r="AT167" t="inlineStr"/>
+      <c r="AW167" t="inlineStr">
+        <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AX167" t="inlineStr">
+        <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AY167" t="inlineStr"/>
+    </row>
+    <row r="168">
+      <c r="A168" t="n">
+        <v>129419031</v>
+      </c>
+      <c r="B168" t="n">
+        <v>91540</v>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E168" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F168" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G168" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H168" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I168" t="inlineStr"/>
+      <c r="P168" t="inlineStr">
+        <is>
+          <t>Väst Norrby gamla tomt, Vstm</t>
+        </is>
+      </c>
+      <c r="Q168" t="n">
+        <v>572381</v>
+      </c>
+      <c r="R168" t="n">
+        <v>6635179</v>
+      </c>
+      <c r="S168" t="n">
+        <v>10</v>
+      </c>
+      <c r="T168" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U168" t="inlineStr">
+        <is>
+          <t>Sala</t>
+        </is>
+      </c>
+      <c r="V168" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W168" t="inlineStr">
+        <is>
+          <t>Fläckebo</t>
+        </is>
+      </c>
+      <c r="Y168" t="inlineStr">
+        <is>
+          <t>2025-09-05</t>
+        </is>
+      </c>
+      <c r="AA168" t="inlineStr">
+        <is>
+          <t>2025-09-05</t>
+        </is>
+      </c>
+      <c r="AD168" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE168" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG168" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT168" t="inlineStr"/>
+      <c r="AW168" t="inlineStr">
+        <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AX168" t="inlineStr">
+        <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AY168" t="inlineStr"/>
+    </row>
+    <row r="169">
+      <c r="A169" t="n">
+        <v>129419036</v>
+      </c>
+      <c r="B169" t="n">
+        <v>90376</v>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E169" t="n">
+        <v>6292</v>
+      </c>
+      <c r="F169" t="inlineStr">
+        <is>
+          <t>Gulgrön kantmusseron</t>
+        </is>
+      </c>
+      <c r="G169" t="inlineStr">
+        <is>
+          <t>Tricholoma viridilutescens</t>
+        </is>
+      </c>
+      <c r="H169" t="inlineStr">
+        <is>
+          <t>M. M. Moser</t>
+        </is>
+      </c>
+      <c r="I169" t="inlineStr"/>
+      <c r="P169" t="inlineStr">
+        <is>
+          <t>Väst Norrby gamla tomt, Vstm</t>
+        </is>
+      </c>
+      <c r="Q169" t="n">
+        <v>572641</v>
+      </c>
+      <c r="R169" t="n">
+        <v>6635207</v>
+      </c>
+      <c r="S169" t="n">
+        <v>10</v>
+      </c>
+      <c r="T169" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U169" t="inlineStr">
+        <is>
+          <t>Sala</t>
+        </is>
+      </c>
+      <c r="V169" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W169" t="inlineStr">
+        <is>
+          <t>Fläckebo</t>
+        </is>
+      </c>
+      <c r="Y169" t="inlineStr">
+        <is>
+          <t>2025-09-05</t>
+        </is>
+      </c>
+      <c r="AA169" t="inlineStr">
+        <is>
+          <t>2025-09-05</t>
+        </is>
+      </c>
+      <c r="AD169" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE169" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG169" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT169" t="inlineStr"/>
+      <c r="AW169" t="inlineStr">
+        <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AX169" t="inlineStr">
+        <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AY169" t="inlineStr"/>
+    </row>
+    <row r="170">
+      <c r="A170" t="n">
+        <v>129419064</v>
+      </c>
+      <c r="B170" t="n">
+        <v>92190</v>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E170" t="n">
+        <v>1339</v>
+      </c>
+      <c r="F170" t="inlineStr">
+        <is>
+          <t>Brandticka</t>
+        </is>
+      </c>
+      <c r="G170" t="inlineStr">
+        <is>
+          <t>Pycnoporellus fulgens</t>
+        </is>
+      </c>
+      <c r="H170" t="inlineStr">
+        <is>
+          <t>(Fr.) Donk</t>
+        </is>
+      </c>
+      <c r="I170" t="inlineStr"/>
+      <c r="P170" t="inlineStr">
+        <is>
+          <t>Väst Norrby gamla tomt, Vstm</t>
+        </is>
+      </c>
+      <c r="Q170" t="n">
+        <v>572450</v>
+      </c>
+      <c r="R170" t="n">
+        <v>6635232</v>
+      </c>
+      <c r="S170" t="n">
+        <v>10</v>
+      </c>
+      <c r="T170" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U170" t="inlineStr">
+        <is>
+          <t>Sala</t>
+        </is>
+      </c>
+      <c r="V170" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W170" t="inlineStr">
+        <is>
+          <t>Fläckebo</t>
+        </is>
+      </c>
+      <c r="Y170" t="inlineStr">
+        <is>
+          <t>2025-09-05</t>
+        </is>
+      </c>
+      <c r="AA170" t="inlineStr">
+        <is>
+          <t>2025-09-05</t>
+        </is>
+      </c>
+      <c r="AD170" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE170" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG170" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT170" t="inlineStr"/>
+      <c r="AW170" t="inlineStr">
+        <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AX170" t="inlineStr">
+        <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AY170" t="inlineStr"/>
+    </row>
+    <row r="171">
+      <c r="A171" t="n">
+        <v>129419044</v>
+      </c>
+      <c r="B171" t="n">
+        <v>90327</v>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E171" t="n">
+        <v>6268</v>
+      </c>
+      <c r="F171" t="inlineStr">
+        <is>
+          <t>Rökmusseron</t>
+        </is>
+      </c>
+      <c r="G171" t="inlineStr">
+        <is>
+          <t>Tricholoma fucatum</t>
+        </is>
+      </c>
+      <c r="H171" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Kumm.</t>
+        </is>
+      </c>
+      <c r="I171" t="inlineStr"/>
+      <c r="P171" t="inlineStr">
+        <is>
+          <t>Väst Norrby gamla tomt, Vstm</t>
+        </is>
+      </c>
+      <c r="Q171" t="n">
+        <v>572651</v>
+      </c>
+      <c r="R171" t="n">
+        <v>6635193</v>
+      </c>
+      <c r="S171" t="n">
+        <v>10</v>
+      </c>
+      <c r="T171" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U171" t="inlineStr">
+        <is>
+          <t>Sala</t>
+        </is>
+      </c>
+      <c r="V171" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W171" t="inlineStr">
+        <is>
+          <t>Fläckebo</t>
+        </is>
+      </c>
+      <c r="Y171" t="inlineStr">
+        <is>
+          <t>2025-09-05</t>
+        </is>
+      </c>
+      <c r="AA171" t="inlineStr">
+        <is>
+          <t>2025-09-05</t>
+        </is>
+      </c>
+      <c r="AD171" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE171" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG171" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT171" t="inlineStr"/>
+      <c r="AW171" t="inlineStr">
+        <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AX171" t="inlineStr">
+        <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AY171" t="inlineStr"/>
+    </row>
+    <row r="172">
+      <c r="A172" t="n">
+        <v>129419043</v>
+      </c>
+      <c r="B172" t="n">
+        <v>91064</v>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E172" t="n">
+        <v>5733</v>
+      </c>
+      <c r="F172" t="inlineStr">
+        <is>
+          <t>Såpfingersvamp</t>
+        </is>
+      </c>
+      <c r="G172" t="inlineStr">
+        <is>
+          <t>Ramaria lutea</t>
+        </is>
+      </c>
+      <c r="H172" t="inlineStr">
+        <is>
+          <t>(Vent.) Schild</t>
+        </is>
+      </c>
+      <c r="I172" t="inlineStr"/>
+      <c r="P172" t="inlineStr">
+        <is>
+          <t>Väst Norrby gamla tomt, Vstm</t>
+        </is>
+      </c>
+      <c r="Q172" t="n">
+        <v>572574</v>
+      </c>
+      <c r="R172" t="n">
+        <v>6634982</v>
+      </c>
+      <c r="S172" t="n">
+        <v>10</v>
+      </c>
+      <c r="T172" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U172" t="inlineStr">
+        <is>
+          <t>Sala</t>
+        </is>
+      </c>
+      <c r="V172" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W172" t="inlineStr">
+        <is>
+          <t>Fläckebo</t>
+        </is>
+      </c>
+      <c r="Y172" t="inlineStr">
+        <is>
+          <t>2025-09-05</t>
+        </is>
+      </c>
+      <c r="AA172" t="inlineStr">
+        <is>
+          <t>2025-09-05</t>
+        </is>
+      </c>
+      <c r="AD172" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE172" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF172" t="inlineStr"/>
+      <c r="AG172" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT172" t="inlineStr"/>
+      <c r="AW172" t="inlineStr">
+        <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AX172" t="inlineStr">
+        <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AY172" t="inlineStr"/>
+    </row>
+    <row r="173">
+      <c r="A173" t="n">
+        <v>129419033</v>
+      </c>
+      <c r="B173" t="n">
+        <v>91540</v>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E173" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F173" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G173" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H173" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I173" t="inlineStr"/>
+      <c r="P173" t="inlineStr">
+        <is>
+          <t>Väst Norrby gamla tomt, Vstm</t>
+        </is>
+      </c>
+      <c r="Q173" t="n">
+        <v>572416</v>
+      </c>
+      <c r="R173" t="n">
+        <v>6634855</v>
+      </c>
+      <c r="S173" t="n">
+        <v>10</v>
+      </c>
+      <c r="T173" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U173" t="inlineStr">
+        <is>
+          <t>Sala</t>
+        </is>
+      </c>
+      <c r="V173" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W173" t="inlineStr">
+        <is>
+          <t>Fläckebo</t>
+        </is>
+      </c>
+      <c r="Y173" t="inlineStr">
+        <is>
+          <t>2025-09-05</t>
+        </is>
+      </c>
+      <c r="AA173" t="inlineStr">
+        <is>
+          <t>2025-09-05</t>
+        </is>
+      </c>
+      <c r="AD173" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE173" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG173" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT173" t="inlineStr"/>
+      <c r="AW173" t="inlineStr">
+        <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AX173" t="inlineStr">
+        <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AY173" t="inlineStr"/>
+    </row>
+    <row r="174">
+      <c r="A174" t="n">
+        <v>129419023</v>
+      </c>
+      <c r="B174" t="n">
+        <v>91504</v>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E174" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F174" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G174" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H174" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I174" t="inlineStr"/>
+      <c r="P174" t="inlineStr">
+        <is>
+          <t>Väst Norrby gamla tomt, Vstm</t>
+        </is>
+      </c>
+      <c r="Q174" t="n">
+        <v>572375</v>
+      </c>
+      <c r="R174" t="n">
+        <v>6635185</v>
+      </c>
+      <c r="S174" t="n">
+        <v>10</v>
+      </c>
+      <c r="T174" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U174" t="inlineStr">
+        <is>
+          <t>Sala</t>
+        </is>
+      </c>
+      <c r="V174" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W174" t="inlineStr">
+        <is>
+          <t>Fläckebo</t>
+        </is>
+      </c>
+      <c r="Y174" t="inlineStr">
+        <is>
+          <t>2025-09-05</t>
+        </is>
+      </c>
+      <c r="AA174" t="inlineStr">
+        <is>
+          <t>2025-09-05</t>
+        </is>
+      </c>
+      <c r="AD174" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE174" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG174" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT174" t="inlineStr"/>
+      <c r="AW174" t="inlineStr">
+        <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AX174" t="inlineStr">
+        <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AY174" t="inlineStr"/>
+    </row>
+    <row r="175">
+      <c r="A175" t="n">
+        <v>129419049</v>
+      </c>
+      <c r="B175" t="n">
+        <v>95907</v>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E175" t="n">
+        <v>530</v>
+      </c>
+      <c r="F175" t="inlineStr">
+        <is>
+          <t>Hårklomossa</t>
+        </is>
+      </c>
+      <c r="G175" t="inlineStr">
+        <is>
+          <t>Dichelyma capillaceum</t>
+        </is>
+      </c>
+      <c r="H175" t="inlineStr">
+        <is>
+          <t>(L. ex Dicks.) Myrin</t>
+        </is>
+      </c>
+      <c r="I175" t="inlineStr"/>
+      <c r="P175" t="inlineStr">
+        <is>
+          <t>Väst Norrby gamla tomt, Vstm</t>
+        </is>
+      </c>
+      <c r="Q175" t="n">
+        <v>572565</v>
+      </c>
+      <c r="R175" t="n">
+        <v>6634984</v>
+      </c>
+      <c r="S175" t="n">
+        <v>10</v>
+      </c>
+      <c r="T175" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U175" t="inlineStr">
+        <is>
+          <t>Sala</t>
+        </is>
+      </c>
+      <c r="V175" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W175" t="inlineStr">
+        <is>
+          <t>Fläckebo</t>
+        </is>
+      </c>
+      <c r="Y175" t="inlineStr">
+        <is>
+          <t>2025-09-05</t>
+        </is>
+      </c>
+      <c r="AA175" t="inlineStr">
+        <is>
+          <t>2025-09-05</t>
+        </is>
+      </c>
+      <c r="AD175" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE175" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG175" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO175" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AT175" t="inlineStr"/>
+      <c r="AW175" t="inlineStr">
+        <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AX175" t="inlineStr">
+        <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AY175" t="inlineStr"/>
+    </row>
+    <row r="176">
+      <c r="A176" t="n">
+        <v>129419025</v>
+      </c>
+      <c r="B176" t="n">
+        <v>91504</v>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E176" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F176" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G176" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H176" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I176" t="inlineStr"/>
+      <c r="P176" t="inlineStr">
+        <is>
+          <t>Väst Norrby gamla tomt, Vstm</t>
+        </is>
+      </c>
+      <c r="Q176" t="n">
+        <v>572492</v>
+      </c>
+      <c r="R176" t="n">
+        <v>6634998</v>
+      </c>
+      <c r="S176" t="n">
+        <v>10</v>
+      </c>
+      <c r="T176" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U176" t="inlineStr">
+        <is>
+          <t>Sala</t>
+        </is>
+      </c>
+      <c r="V176" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W176" t="inlineStr">
+        <is>
+          <t>Fläckebo</t>
+        </is>
+      </c>
+      <c r="Y176" t="inlineStr">
+        <is>
+          <t>2025-09-05</t>
+        </is>
+      </c>
+      <c r="AA176" t="inlineStr">
+        <is>
+          <t>2025-09-05</t>
+        </is>
+      </c>
+      <c r="AD176" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE176" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG176" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT176" t="inlineStr"/>
+      <c r="AW176" t="inlineStr">
+        <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AX176" t="inlineStr">
+        <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AY176" t="inlineStr"/>
+    </row>
+    <row r="177">
+      <c r="A177" t="n">
+        <v>129419022</v>
+      </c>
+      <c r="B177" t="n">
+        <v>96952</v>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E177" t="n">
+        <v>53</v>
+      </c>
+      <c r="F177" t="inlineStr">
+        <is>
+          <t>Vedtrappmossa</t>
+        </is>
+      </c>
+      <c r="G177" t="inlineStr">
+        <is>
+          <t>Crossocalyx hellerianus</t>
+        </is>
+      </c>
+      <c r="H177" t="inlineStr">
+        <is>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I177" t="inlineStr"/>
+      <c r="P177" t="inlineStr">
+        <is>
+          <t>Väst Norrby gamla tomt, Vstm</t>
+        </is>
+      </c>
+      <c r="Q177" t="n">
+        <v>572437</v>
+      </c>
+      <c r="R177" t="n">
+        <v>6634991</v>
+      </c>
+      <c r="S177" t="n">
+        <v>10</v>
+      </c>
+      <c r="T177" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U177" t="inlineStr">
+        <is>
+          <t>Sala</t>
+        </is>
+      </c>
+      <c r="V177" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W177" t="inlineStr">
+        <is>
+          <t>Fläckebo</t>
+        </is>
+      </c>
+      <c r="Y177" t="inlineStr">
+        <is>
+          <t>2025-09-05</t>
+        </is>
+      </c>
+      <c r="AA177" t="inlineStr">
+        <is>
+          <t>2025-09-05</t>
+        </is>
+      </c>
+      <c r="AD177" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE177" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG177" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT177" t="inlineStr"/>
+      <c r="AW177" t="inlineStr">
+        <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AX177" t="inlineStr">
+        <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AY177" t="inlineStr"/>
+    </row>
+    <row r="178">
+      <c r="A178" t="n">
+        <v>129419030</v>
+      </c>
+      <c r="B178" t="n">
+        <v>91540</v>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E178" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F178" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G178" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H178" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I178" t="inlineStr"/>
+      <c r="P178" t="inlineStr">
+        <is>
+          <t>Väst Norrby gamla tomt, Vstm</t>
+        </is>
+      </c>
+      <c r="Q178" t="n">
+        <v>572414</v>
+      </c>
+      <c r="R178" t="n">
+        <v>6635279</v>
+      </c>
+      <c r="S178" t="n">
+        <v>10</v>
+      </c>
+      <c r="T178" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U178" t="inlineStr">
+        <is>
+          <t>Sala</t>
+        </is>
+      </c>
+      <c r="V178" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W178" t="inlineStr">
+        <is>
+          <t>Fläckebo</t>
+        </is>
+      </c>
+      <c r="Y178" t="inlineStr">
+        <is>
+          <t>2025-09-05</t>
+        </is>
+      </c>
+      <c r="AA178" t="inlineStr">
+        <is>
+          <t>2025-09-05</t>
+        </is>
+      </c>
+      <c r="AD178" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE178" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG178" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT178" t="inlineStr"/>
+      <c r="AW178" t="inlineStr">
+        <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AX178" t="inlineStr">
+        <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AY178" t="inlineStr"/>
+    </row>
+    <row r="179">
+      <c r="A179" t="n">
+        <v>129419062</v>
+      </c>
+      <c r="B179" t="n">
+        <v>91962</v>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E179" t="n">
+        <v>298</v>
+      </c>
+      <c r="F179" t="inlineStr">
+        <is>
+          <t>Laxgröppa</t>
+        </is>
+      </c>
+      <c r="G179" t="inlineStr">
+        <is>
+          <t>Meruliopsis rubicunda</t>
+        </is>
+      </c>
+      <c r="H179" t="inlineStr">
+        <is>
+          <t>(Litsch.) Spirin &amp; K.H.Larss.</t>
+        </is>
+      </c>
+      <c r="I179" t="inlineStr"/>
+      <c r="J179" t="inlineStr"/>
+      <c r="K179" t="inlineStr"/>
+      <c r="N179" t="inlineStr"/>
+      <c r="P179" t="inlineStr">
+        <is>
+          <t>Väst Norrby gamla tomt, Vstm</t>
+        </is>
+      </c>
+      <c r="Q179" t="n">
+        <v>572637</v>
+      </c>
+      <c r="R179" t="n">
+        <v>6635268</v>
+      </c>
+      <c r="S179" t="n">
+        <v>10</v>
+      </c>
+      <c r="T179" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U179" t="inlineStr">
+        <is>
+          <t>Sala</t>
+        </is>
+      </c>
+      <c r="V179" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W179" t="inlineStr">
+        <is>
+          <t>Fläckebo</t>
+        </is>
+      </c>
+      <c r="Y179" t="inlineStr">
+        <is>
+          <t>2025-09-05</t>
+        </is>
+      </c>
+      <c r="AA179" t="inlineStr">
+        <is>
+          <t>2025-09-05</t>
+        </is>
+      </c>
+      <c r="AD179" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE179" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF179" t="inlineStr"/>
+      <c r="AG179" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT179" t="inlineStr"/>
+      <c r="AW179" t="inlineStr">
+        <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AX179" t="inlineStr">
+        <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AY179" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 12276-2023 artfynd.xlsx
+++ b/artfynd/A 12276-2023 artfynd.xlsx
@@ -17061,7 +17061,7 @@
         <v>129419047</v>
       </c>
       <c r="B155" t="n">
-        <v>92814</v>
+        <v>92817</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -17158,7 +17158,7 @@
         <v>129419026</v>
       </c>
       <c r="B156" t="n">
-        <v>91504</v>
+        <v>91507</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -17255,7 +17255,7 @@
         <v>129419048</v>
       </c>
       <c r="B157" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -17352,7 +17352,7 @@
         <v>129419028</v>
       </c>
       <c r="B158" t="n">
-        <v>91540</v>
+        <v>91543</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -17449,7 +17449,7 @@
         <v>129419032</v>
       </c>
       <c r="B159" t="n">
-        <v>91540</v>
+        <v>91543</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -17546,7 +17546,7 @@
         <v>129419034</v>
       </c>
       <c r="B160" t="n">
-        <v>91540</v>
+        <v>91543</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -17640,32 +17640,32 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>129419027</v>
+        <v>129419029</v>
       </c>
       <c r="B161" t="n">
-        <v>91504</v>
+        <v>91543</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E161" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I161" t="inlineStr"/>
@@ -17675,10 +17675,10 @@
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>572637</v>
+        <v>572434</v>
       </c>
       <c r="R161" t="n">
-        <v>6635268</v>
+        <v>6635240</v>
       </c>
       <c r="S161" t="n">
         <v>10</v>
@@ -17737,32 +17737,32 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>129419029</v>
+        <v>129419027</v>
       </c>
       <c r="B162" t="n">
-        <v>91540</v>
+        <v>91507</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E162" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I162" t="inlineStr"/>
@@ -17772,10 +17772,10 @@
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>572434</v>
+        <v>572637</v>
       </c>
       <c r="R162" t="n">
-        <v>6635240</v>
+        <v>6635268</v>
       </c>
       <c r="S162" t="n">
         <v>10</v>
@@ -17834,32 +17834,32 @@
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>129419052</v>
+        <v>129419063</v>
       </c>
       <c r="B163" t="n">
-        <v>90922</v>
+        <v>91413</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E163" t="n">
-        <v>5685</v>
+        <v>3290</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Gullgröppa</t>
+          <t>Gaffelskinn</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Pseudomerulius aureus</t>
+          <t>Clavulicium macounii</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>(Fr.) Jülich</t>
+          <t>(Burt) J.Erikss. &amp; Boidin ex Parmasto</t>
         </is>
       </c>
       <c r="I163" t="inlineStr"/>
@@ -17869,10 +17869,10 @@
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>572365</v>
+        <v>572505</v>
       </c>
       <c r="R163" t="n">
-        <v>6635062</v>
+        <v>6635049</v>
       </c>
       <c r="S163" t="n">
         <v>10</v>
@@ -17931,32 +17931,32 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>129419063</v>
+        <v>129419052</v>
       </c>
       <c r="B164" t="n">
-        <v>91410</v>
+        <v>90925</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E164" t="n">
-        <v>3290</v>
+        <v>5685</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Gaffelskinn</t>
+          <t>Gullgröppa</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Clavulicium macounii</t>
+          <t>Pseudomerulius aureus</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>(Burt) J.Erikss. &amp; Boidin ex Parmasto</t>
+          <t>(Fr.) Jülich</t>
         </is>
       </c>
       <c r="I164" t="inlineStr"/>
@@ -17966,10 +17966,10 @@
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>572505</v>
+        <v>572365</v>
       </c>
       <c r="R164" t="n">
-        <v>6635049</v>
+        <v>6635062</v>
       </c>
       <c r="S164" t="n">
         <v>10</v>
@@ -18028,32 +18028,32 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>129419035</v>
+        <v>129419024</v>
       </c>
       <c r="B165" t="n">
-        <v>91540</v>
+        <v>91507</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E165" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I165" t="inlineStr"/>
@@ -18063,10 +18063,10 @@
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>572625</v>
+        <v>572501</v>
       </c>
       <c r="R165" t="n">
-        <v>6635270</v>
+        <v>6635056</v>
       </c>
       <c r="S165" t="n">
         <v>10</v>
@@ -18125,32 +18125,32 @@
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>129419024</v>
+        <v>129419035</v>
       </c>
       <c r="B166" t="n">
-        <v>91504</v>
+        <v>91543</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E166" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I166" t="inlineStr"/>
@@ -18160,10 +18160,10 @@
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>572501</v>
+        <v>572625</v>
       </c>
       <c r="R166" t="n">
-        <v>6635056</v>
+        <v>6635270</v>
       </c>
       <c r="S166" t="n">
         <v>10</v>
@@ -18222,32 +18222,32 @@
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>129419041</v>
+        <v>129419031</v>
       </c>
       <c r="B167" t="n">
-        <v>92462</v>
+        <v>91543</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E167" t="n">
-        <v>4740</v>
+        <v>1202</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Sotriska</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Lactarius lignyotus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I167" t="inlineStr"/>
@@ -18257,10 +18257,10 @@
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>572441</v>
+        <v>572381</v>
       </c>
       <c r="R167" t="n">
-        <v>6634990</v>
+        <v>6635179</v>
       </c>
       <c r="S167" t="n">
         <v>10</v>
@@ -18303,11 +18303,6 @@
       </c>
       <c r="AG167" t="b">
         <v>0</v>
-      </c>
-      <c r="AO167" t="inlineStr">
-        <is>
-          <t>tallåga</t>
-        </is>
       </c>
       <c r="AT167" t="inlineStr"/>
       <c r="AW167" t="inlineStr">
@@ -18324,32 +18319,32 @@
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>129419031</v>
+        <v>129419041</v>
       </c>
       <c r="B168" t="n">
-        <v>91540</v>
+        <v>92465</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E168" t="n">
-        <v>1202</v>
+        <v>4740</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Sotriska</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lactarius lignyotus</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I168" t="inlineStr"/>
@@ -18359,10 +18354,10 @@
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>572381</v>
+        <v>572441</v>
       </c>
       <c r="R168" t="n">
-        <v>6635179</v>
+        <v>6634990</v>
       </c>
       <c r="S168" t="n">
         <v>10</v>
@@ -18405,6 +18400,11 @@
       </c>
       <c r="AG168" t="b">
         <v>0</v>
+      </c>
+      <c r="AO168" t="inlineStr">
+        <is>
+          <t>tallåga</t>
+        </is>
       </c>
       <c r="AT168" t="inlineStr"/>
       <c r="AW168" t="inlineStr">
@@ -18424,7 +18424,7 @@
         <v>129419036</v>
       </c>
       <c r="B169" t="n">
-        <v>90376</v>
+        <v>90379</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -18521,7 +18521,7 @@
         <v>129419064</v>
       </c>
       <c r="B170" t="n">
-        <v>92190</v>
+        <v>92193</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -18615,32 +18615,32 @@
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>129419044</v>
+        <v>129419033</v>
       </c>
       <c r="B171" t="n">
-        <v>90327</v>
+        <v>91543</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E171" t="n">
-        <v>6268</v>
+        <v>1202</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Rökmusseron</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Tricholoma fucatum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Kumm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I171" t="inlineStr"/>
@@ -18650,10 +18650,10 @@
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>572651</v>
+        <v>572416</v>
       </c>
       <c r="R171" t="n">
-        <v>6635193</v>
+        <v>6634855</v>
       </c>
       <c r="S171" t="n">
         <v>10</v>
@@ -18715,7 +18715,7 @@
         <v>129419043</v>
       </c>
       <c r="B172" t="n">
-        <v>91064</v>
+        <v>91067</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -18810,32 +18810,32 @@
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>129419033</v>
+        <v>129419023</v>
       </c>
       <c r="B173" t="n">
-        <v>91540</v>
+        <v>91507</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E173" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I173" t="inlineStr"/>
@@ -18845,10 +18845,10 @@
         </is>
       </c>
       <c r="Q173" t="n">
-        <v>572416</v>
+        <v>572375</v>
       </c>
       <c r="R173" t="n">
-        <v>6634855</v>
+        <v>6635185</v>
       </c>
       <c r="S173" t="n">
         <v>10</v>
@@ -18907,10 +18907,10 @@
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>129419023</v>
+        <v>129419044</v>
       </c>
       <c r="B174" t="n">
-        <v>91504</v>
+        <v>90330</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -18918,21 +18918,21 @@
         </is>
       </c>
       <c r="E174" t="n">
-        <v>5447</v>
+        <v>6268</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Rökmusseron</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Tricholoma fucatum</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.:Fr.) P. Kumm.</t>
         </is>
       </c>
       <c r="I174" t="inlineStr"/>
@@ -18942,10 +18942,10 @@
         </is>
       </c>
       <c r="Q174" t="n">
-        <v>572375</v>
+        <v>572651</v>
       </c>
       <c r="R174" t="n">
-        <v>6635185</v>
+        <v>6635193</v>
       </c>
       <c r="S174" t="n">
         <v>10</v>
@@ -19007,7 +19007,7 @@
         <v>129419049</v>
       </c>
       <c r="B175" t="n">
-        <v>95907</v>
+        <v>95911</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -19106,32 +19106,32 @@
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>129419025</v>
+        <v>129419022</v>
       </c>
       <c r="B176" t="n">
-        <v>91504</v>
+        <v>96956</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E176" t="n">
-        <v>5447</v>
+        <v>53</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I176" t="inlineStr"/>
@@ -19141,10 +19141,10 @@
         </is>
       </c>
       <c r="Q176" t="n">
-        <v>572492</v>
+        <v>572437</v>
       </c>
       <c r="R176" t="n">
-        <v>6634998</v>
+        <v>6634991</v>
       </c>
       <c r="S176" t="n">
         <v>10</v>
@@ -19203,32 +19203,32 @@
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>129419022</v>
+        <v>129419025</v>
       </c>
       <c r="B177" t="n">
-        <v>96952</v>
+        <v>91507</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E177" t="n">
-        <v>53</v>
+        <v>5447</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I177" t="inlineStr"/>
@@ -19238,10 +19238,10 @@
         </is>
       </c>
       <c r="Q177" t="n">
-        <v>572437</v>
+        <v>572492</v>
       </c>
       <c r="R177" t="n">
-        <v>6634991</v>
+        <v>6634998</v>
       </c>
       <c r="S177" t="n">
         <v>10</v>
@@ -19300,45 +19300,48 @@
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>129419030</v>
+        <v>129419062</v>
       </c>
       <c r="B178" t="n">
-        <v>91540</v>
+        <v>91965</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E178" t="n">
-        <v>1202</v>
+        <v>298</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Laxgröppa</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Meruliopsis rubicunda</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Litsch.) Spirin &amp; K.H.Larss.</t>
         </is>
       </c>
       <c r="I178" t="inlineStr"/>
+      <c r="J178" t="inlineStr"/>
+      <c r="K178" t="inlineStr"/>
+      <c r="N178" t="inlineStr"/>
       <c r="P178" t="inlineStr">
         <is>
           <t>Väst Norrby gamla tomt, Vstm</t>
         </is>
       </c>
       <c r="Q178" t="n">
-        <v>572414</v>
+        <v>572637</v>
       </c>
       <c r="R178" t="n">
-        <v>6635279</v>
+        <v>6635268</v>
       </c>
       <c r="S178" t="n">
         <v>10</v>
@@ -19379,6 +19382,7 @@
       <c r="AE178" t="b">
         <v>0</v>
       </c>
+      <c r="AF178" t="inlineStr"/>
       <c r="AG178" t="b">
         <v>0</v>
       </c>
@@ -19397,48 +19401,45 @@
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>129419062</v>
+        <v>129419030</v>
       </c>
       <c r="B179" t="n">
-        <v>91962</v>
+        <v>91543</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E179" t="n">
-        <v>298</v>
+        <v>1202</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Laxgröppa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>Meruliopsis rubicunda</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>(Litsch.) Spirin &amp; K.H.Larss.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I179" t="inlineStr"/>
-      <c r="J179" t="inlineStr"/>
-      <c r="K179" t="inlineStr"/>
-      <c r="N179" t="inlineStr"/>
       <c r="P179" t="inlineStr">
         <is>
           <t>Väst Norrby gamla tomt, Vstm</t>
         </is>
       </c>
       <c r="Q179" t="n">
-        <v>572637</v>
+        <v>572414</v>
       </c>
       <c r="R179" t="n">
-        <v>6635268</v>
+        <v>6635279</v>
       </c>
       <c r="S179" t="n">
         <v>10</v>
@@ -19479,7 +19480,6 @@
       <c r="AE179" t="b">
         <v>0</v>
       </c>
-      <c r="AF179" t="inlineStr"/>
       <c r="AG179" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 12276-2023 artfynd.xlsx
+++ b/artfynd/A 12276-2023 artfynd.xlsx
@@ -17061,7 +17061,7 @@
         <v>129419047</v>
       </c>
       <c r="B155" t="n">
-        <v>92855</v>
+        <v>92861</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -17162,7 +17162,7 @@
         <v>129419026</v>
       </c>
       <c r="B156" t="n">
-        <v>91545</v>
+        <v>91551</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -17263,7 +17263,7 @@
         <v>129419048</v>
       </c>
       <c r="B157" t="n">
-        <v>98756</v>
+        <v>98768</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -17364,7 +17364,7 @@
         <v>129419028</v>
       </c>
       <c r="B158" t="n">
-        <v>91581</v>
+        <v>91587</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -17465,7 +17465,7 @@
         <v>129419032</v>
       </c>
       <c r="B159" t="n">
-        <v>91581</v>
+        <v>91587</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -17566,7 +17566,7 @@
         <v>129419034</v>
       </c>
       <c r="B160" t="n">
-        <v>91581</v>
+        <v>91587</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -17667,7 +17667,7 @@
         <v>129419029</v>
       </c>
       <c r="B161" t="n">
-        <v>91581</v>
+        <v>91587</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -17768,7 +17768,7 @@
         <v>129419027</v>
       </c>
       <c r="B162" t="n">
-        <v>91545</v>
+        <v>91551</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -17866,32 +17866,32 @@
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>129419052</v>
+        <v>129419063</v>
       </c>
       <c r="B163" t="n">
-        <v>90963</v>
+        <v>91457</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E163" t="n">
-        <v>5685</v>
+        <v>3290</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Gullgröppa</t>
+          <t>Gaffelskinn</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Pseudomerulius aureus</t>
+          <t>Clavulicium macounii</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>(Fr.) Jülich</t>
+          <t>(Burt) J.Erikss. &amp; Boidin ex Parmasto</t>
         </is>
       </c>
       <c r="I163" t="inlineStr"/>
@@ -17901,10 +17901,10 @@
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>572365</v>
+        <v>572505</v>
       </c>
       <c r="R163" t="n">
-        <v>6635062</v>
+        <v>6635049</v>
       </c>
       <c r="S163" t="n">
         <v>10</v>
@@ -17967,32 +17967,32 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>129419063</v>
+        <v>129419052</v>
       </c>
       <c r="B164" t="n">
-        <v>91451</v>
+        <v>90969</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E164" t="n">
-        <v>3290</v>
+        <v>5685</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Gaffelskinn</t>
+          <t>Gullgröppa</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Clavulicium macounii</t>
+          <t>Pseudomerulius aureus</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>(Burt) J.Erikss. &amp; Boidin ex Parmasto</t>
+          <t>(Fr.) Jülich</t>
         </is>
       </c>
       <c r="I164" t="inlineStr"/>
@@ -18002,10 +18002,10 @@
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>572505</v>
+        <v>572365</v>
       </c>
       <c r="R164" t="n">
-        <v>6635049</v>
+        <v>6635062</v>
       </c>
       <c r="S164" t="n">
         <v>10</v>
@@ -18071,7 +18071,7 @@
         <v>129419035</v>
       </c>
       <c r="B165" t="n">
-        <v>91581</v>
+        <v>91587</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -18172,7 +18172,7 @@
         <v>129419024</v>
       </c>
       <c r="B166" t="n">
-        <v>91545</v>
+        <v>91551</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -18270,32 +18270,32 @@
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>129419031</v>
+        <v>129419041</v>
       </c>
       <c r="B167" t="n">
-        <v>91581</v>
+        <v>92509</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E167" t="n">
-        <v>1202</v>
+        <v>4740</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Sotriska</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lactarius lignyotus</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I167" t="inlineStr"/>
@@ -18305,10 +18305,10 @@
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>572381</v>
+        <v>572441</v>
       </c>
       <c r="R167" t="n">
-        <v>6635179</v>
+        <v>6634990</v>
       </c>
       <c r="S167" t="n">
         <v>10</v>
@@ -18351,6 +18351,11 @@
       </c>
       <c r="AG167" t="b">
         <v>0</v>
+      </c>
+      <c r="AO167" t="inlineStr">
+        <is>
+          <t>tallåga</t>
+        </is>
       </c>
       <c r="AT167" t="inlineStr"/>
       <c r="AW167" t="inlineStr">
@@ -18371,32 +18376,32 @@
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>129419041</v>
+        <v>129419031</v>
       </c>
       <c r="B168" t="n">
-        <v>92503</v>
+        <v>91587</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E168" t="n">
-        <v>4740</v>
+        <v>1202</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Sotriska</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Lactarius lignyotus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I168" t="inlineStr"/>
@@ -18406,10 +18411,10 @@
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>572441</v>
+        <v>572381</v>
       </c>
       <c r="R168" t="n">
-        <v>6634990</v>
+        <v>6635179</v>
       </c>
       <c r="S168" t="n">
         <v>10</v>
@@ -18452,11 +18457,6 @@
       </c>
       <c r="AG168" t="b">
         <v>0</v>
-      </c>
-      <c r="AO168" t="inlineStr">
-        <is>
-          <t>tallåga</t>
-        </is>
       </c>
       <c r="AT168" t="inlineStr"/>
       <c r="AW168" t="inlineStr">
@@ -18480,7 +18480,7 @@
         <v>129419036</v>
       </c>
       <c r="B169" t="n">
-        <v>90417</v>
+        <v>90423</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -18578,32 +18578,32 @@
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>129419043</v>
+        <v>129419064</v>
       </c>
       <c r="B170" t="n">
-        <v>91105</v>
+        <v>92237</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E170" t="n">
-        <v>5733</v>
+        <v>1339</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Såpfingersvamp</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Ramaria lutea</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>(Vent.) Schild</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I170" t="inlineStr"/>
@@ -18613,10 +18613,10 @@
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>572574</v>
+        <v>572450</v>
       </c>
       <c r="R170" t="n">
-        <v>6634982</v>
+        <v>6635232</v>
       </c>
       <c r="S170" t="n">
         <v>10</v>
@@ -18657,7 +18657,6 @@
       <c r="AE170" t="b">
         <v>0</v>
       </c>
-      <c r="AF170" t="inlineStr"/>
       <c r="AG170" t="b">
         <v>0</v>
       </c>
@@ -18680,10 +18679,10 @@
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>129419023</v>
+        <v>129419044</v>
       </c>
       <c r="B171" t="n">
-        <v>91545</v>
+        <v>90374</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -18691,21 +18690,21 @@
         </is>
       </c>
       <c r="E171" t="n">
-        <v>5447</v>
+        <v>6268</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Rökmusseron</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Tricholoma fucatum</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.:Fr.) P. Kumm.</t>
         </is>
       </c>
       <c r="I171" t="inlineStr"/>
@@ -18715,10 +18714,10 @@
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>572375</v>
+        <v>572651</v>
       </c>
       <c r="R171" t="n">
-        <v>6635185</v>
+        <v>6635193</v>
       </c>
       <c r="S171" t="n">
         <v>10</v>
@@ -18781,32 +18780,32 @@
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>129419064</v>
+        <v>129419043</v>
       </c>
       <c r="B172" t="n">
-        <v>92231</v>
+        <v>91111</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E172" t="n">
-        <v>1339</v>
+        <v>5733</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Såpfingersvamp</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Ramaria lutea</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>(Vent.) Schild</t>
         </is>
       </c>
       <c r="I172" t="inlineStr"/>
@@ -18816,10 +18815,10 @@
         </is>
       </c>
       <c r="Q172" t="n">
-        <v>572450</v>
+        <v>572574</v>
       </c>
       <c r="R172" t="n">
-        <v>6635232</v>
+        <v>6634982</v>
       </c>
       <c r="S172" t="n">
         <v>10</v>
@@ -18860,6 +18859,7 @@
       <c r="AE172" t="b">
         <v>0</v>
       </c>
+      <c r="AF172" t="inlineStr"/>
       <c r="AG172" t="b">
         <v>0</v>
       </c>
@@ -18882,32 +18882,32 @@
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>129419033</v>
+        <v>129419023</v>
       </c>
       <c r="B173" t="n">
-        <v>91581</v>
+        <v>91551</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E173" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I173" t="inlineStr"/>
@@ -18917,10 +18917,10 @@
         </is>
       </c>
       <c r="Q173" t="n">
-        <v>572416</v>
+        <v>572375</v>
       </c>
       <c r="R173" t="n">
-        <v>6634855</v>
+        <v>6635185</v>
       </c>
       <c r="S173" t="n">
         <v>10</v>
@@ -18983,32 +18983,32 @@
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>129419044</v>
+        <v>129419033</v>
       </c>
       <c r="B174" t="n">
-        <v>90368</v>
+        <v>91587</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E174" t="n">
-        <v>6268</v>
+        <v>1202</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Rökmusseron</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>Tricholoma fucatum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Kumm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I174" t="inlineStr"/>
@@ -19018,10 +19018,10 @@
         </is>
       </c>
       <c r="Q174" t="n">
-        <v>572651</v>
+        <v>572416</v>
       </c>
       <c r="R174" t="n">
-        <v>6635193</v>
+        <v>6634855</v>
       </c>
       <c r="S174" t="n">
         <v>10</v>
@@ -19087,7 +19087,7 @@
         <v>129419049</v>
       </c>
       <c r="B175" t="n">
-        <v>95957</v>
+        <v>95969</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -19190,32 +19190,32 @@
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>129419022</v>
+        <v>129419025</v>
       </c>
       <c r="B176" t="n">
-        <v>97002</v>
+        <v>91551</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E176" t="n">
-        <v>53</v>
+        <v>5447</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I176" t="inlineStr"/>
@@ -19225,10 +19225,10 @@
         </is>
       </c>
       <c r="Q176" t="n">
-        <v>572437</v>
+        <v>572492</v>
       </c>
       <c r="R176" t="n">
-        <v>6634991</v>
+        <v>6634998</v>
       </c>
       <c r="S176" t="n">
         <v>10</v>
@@ -19291,32 +19291,32 @@
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>129419025</v>
+        <v>129419022</v>
       </c>
       <c r="B177" t="n">
-        <v>91545</v>
+        <v>97014</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E177" t="n">
-        <v>5447</v>
+        <v>53</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I177" t="inlineStr"/>
@@ -19326,10 +19326,10 @@
         </is>
       </c>
       <c r="Q177" t="n">
-        <v>572492</v>
+        <v>572437</v>
       </c>
       <c r="R177" t="n">
-        <v>6634998</v>
+        <v>6634991</v>
       </c>
       <c r="S177" t="n">
         <v>10</v>
@@ -19392,45 +19392,48 @@
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>129419030</v>
+        <v>129419062</v>
       </c>
       <c r="B178" t="n">
-        <v>91581</v>
+        <v>92009</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E178" t="n">
-        <v>1202</v>
+        <v>298</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Laxgröppa</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Meruliopsis rubicunda</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Litsch.) Spirin &amp; K.H.Larss.</t>
         </is>
       </c>
       <c r="I178" t="inlineStr"/>
+      <c r="J178" t="inlineStr"/>
+      <c r="K178" t="inlineStr"/>
+      <c r="N178" t="inlineStr"/>
       <c r="P178" t="inlineStr">
         <is>
           <t>Väst Norrby gamla tomt, Vstm</t>
         </is>
       </c>
       <c r="Q178" t="n">
-        <v>572414</v>
+        <v>572637</v>
       </c>
       <c r="R178" t="n">
-        <v>6635279</v>
+        <v>6635268</v>
       </c>
       <c r="S178" t="n">
         <v>10</v>
@@ -19471,6 +19474,7 @@
       <c r="AE178" t="b">
         <v>0</v>
       </c>
+      <c r="AF178" t="inlineStr"/>
       <c r="AG178" t="b">
         <v>0</v>
       </c>
@@ -19493,48 +19497,45 @@
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>129419062</v>
+        <v>129419030</v>
       </c>
       <c r="B179" t="n">
-        <v>92003</v>
+        <v>91587</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E179" t="n">
-        <v>298</v>
+        <v>1202</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Laxgröppa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>Meruliopsis rubicunda</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>(Litsch.) Spirin &amp; K.H.Larss.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I179" t="inlineStr"/>
-      <c r="J179" t="inlineStr"/>
-      <c r="K179" t="inlineStr"/>
-      <c r="N179" t="inlineStr"/>
       <c r="P179" t="inlineStr">
         <is>
           <t>Väst Norrby gamla tomt, Vstm</t>
         </is>
       </c>
       <c r="Q179" t="n">
-        <v>572637</v>
+        <v>572414</v>
       </c>
       <c r="R179" t="n">
-        <v>6635268</v>
+        <v>6635279</v>
       </c>
       <c r="S179" t="n">
         <v>10</v>
@@ -19575,7 +19576,6 @@
       <c r="AE179" t="b">
         <v>0</v>
       </c>
-      <c r="AF179" t="inlineStr"/>
       <c r="AG179" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 12276-2023 artfynd.xlsx
+++ b/artfynd/A 12276-2023 artfynd.xlsx
@@ -17061,7 +17061,7 @@
         <v>129419047</v>
       </c>
       <c r="B155" t="n">
-        <v>92861</v>
+        <v>92862</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -17162,7 +17162,7 @@
         <v>129419026</v>
       </c>
       <c r="B156" t="n">
-        <v>91551</v>
+        <v>91552</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -17263,7 +17263,7 @@
         <v>129419048</v>
       </c>
       <c r="B157" t="n">
-        <v>98768</v>
+        <v>98769</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -17364,7 +17364,7 @@
         <v>129419028</v>
       </c>
       <c r="B158" t="n">
-        <v>91587</v>
+        <v>91588</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -17465,7 +17465,7 @@
         <v>129419032</v>
       </c>
       <c r="B159" t="n">
-        <v>91587</v>
+        <v>91588</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -17563,32 +17563,32 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>129419034</v>
+        <v>129419027</v>
       </c>
       <c r="B160" t="n">
-        <v>91587</v>
+        <v>91552</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E160" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I160" t="inlineStr"/>
@@ -17598,10 +17598,10 @@
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>572518</v>
+        <v>572637</v>
       </c>
       <c r="R160" t="n">
-        <v>6635088</v>
+        <v>6635268</v>
       </c>
       <c r="S160" t="n">
         <v>10</v>
@@ -17664,10 +17664,10 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>129419029</v>
+        <v>129419034</v>
       </c>
       <c r="B161" t="n">
-        <v>91587</v>
+        <v>91588</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -17699,10 +17699,10 @@
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>572434</v>
+        <v>572518</v>
       </c>
       <c r="R161" t="n">
-        <v>6635240</v>
+        <v>6635088</v>
       </c>
       <c r="S161" t="n">
         <v>10</v>
@@ -17765,32 +17765,32 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>129419027</v>
+        <v>129419029</v>
       </c>
       <c r="B162" t="n">
-        <v>91551</v>
+        <v>91588</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E162" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I162" t="inlineStr"/>
@@ -17800,10 +17800,10 @@
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>572637</v>
+        <v>572434</v>
       </c>
       <c r="R162" t="n">
-        <v>6635268</v>
+        <v>6635240</v>
       </c>
       <c r="S162" t="n">
         <v>10</v>
@@ -17866,32 +17866,32 @@
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>129419063</v>
+        <v>129419052</v>
       </c>
       <c r="B163" t="n">
-        <v>91457</v>
+        <v>90970</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E163" t="n">
-        <v>3290</v>
+        <v>5685</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Gaffelskinn</t>
+          <t>Gullgröppa</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Clavulicium macounii</t>
+          <t>Pseudomerulius aureus</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>(Burt) J.Erikss. &amp; Boidin ex Parmasto</t>
+          <t>(Fr.) Jülich</t>
         </is>
       </c>
       <c r="I163" t="inlineStr"/>
@@ -17901,10 +17901,10 @@
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>572505</v>
+        <v>572365</v>
       </c>
       <c r="R163" t="n">
-        <v>6635049</v>
+        <v>6635062</v>
       </c>
       <c r="S163" t="n">
         <v>10</v>
@@ -17967,32 +17967,32 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>129419052</v>
+        <v>129419063</v>
       </c>
       <c r="B164" t="n">
-        <v>90969</v>
+        <v>91458</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E164" t="n">
-        <v>5685</v>
+        <v>3290</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Gullgröppa</t>
+          <t>Gaffelskinn</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Pseudomerulius aureus</t>
+          <t>Clavulicium macounii</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>(Fr.) Jülich</t>
+          <t>(Burt) J.Erikss. &amp; Boidin ex Parmasto</t>
         </is>
       </c>
       <c r="I164" t="inlineStr"/>
@@ -18002,10 +18002,10 @@
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>572365</v>
+        <v>572505</v>
       </c>
       <c r="R164" t="n">
-        <v>6635062</v>
+        <v>6635049</v>
       </c>
       <c r="S164" t="n">
         <v>10</v>
@@ -18068,32 +18068,32 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>129419035</v>
+        <v>129419024</v>
       </c>
       <c r="B165" t="n">
-        <v>91587</v>
+        <v>91552</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E165" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I165" t="inlineStr"/>
@@ -18103,10 +18103,10 @@
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>572625</v>
+        <v>572501</v>
       </c>
       <c r="R165" t="n">
-        <v>6635270</v>
+        <v>6635056</v>
       </c>
       <c r="S165" t="n">
         <v>10</v>
@@ -18169,32 +18169,32 @@
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>129419024</v>
+        <v>129419035</v>
       </c>
       <c r="B166" t="n">
-        <v>91551</v>
+        <v>91588</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E166" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I166" t="inlineStr"/>
@@ -18204,10 +18204,10 @@
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>572501</v>
+        <v>572625</v>
       </c>
       <c r="R166" t="n">
-        <v>6635056</v>
+        <v>6635270</v>
       </c>
       <c r="S166" t="n">
         <v>10</v>
@@ -18270,32 +18270,32 @@
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>129419041</v>
+        <v>129419031</v>
       </c>
       <c r="B167" t="n">
-        <v>92509</v>
+        <v>91588</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E167" t="n">
-        <v>4740</v>
+        <v>1202</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Sotriska</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Lactarius lignyotus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I167" t="inlineStr"/>
@@ -18305,10 +18305,10 @@
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>572441</v>
+        <v>572381</v>
       </c>
       <c r="R167" t="n">
-        <v>6634990</v>
+        <v>6635179</v>
       </c>
       <c r="S167" t="n">
         <v>10</v>
@@ -18351,11 +18351,6 @@
       </c>
       <c r="AG167" t="b">
         <v>0</v>
-      </c>
-      <c r="AO167" t="inlineStr">
-        <is>
-          <t>tallåga</t>
-        </is>
       </c>
       <c r="AT167" t="inlineStr"/>
       <c r="AW167" t="inlineStr">
@@ -18376,32 +18371,32 @@
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>129419031</v>
+        <v>129419041</v>
       </c>
       <c r="B168" t="n">
-        <v>91587</v>
+        <v>92510</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E168" t="n">
-        <v>1202</v>
+        <v>4740</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Sotriska</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lactarius lignyotus</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I168" t="inlineStr"/>
@@ -18411,10 +18406,10 @@
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>572381</v>
+        <v>572441</v>
       </c>
       <c r="R168" t="n">
-        <v>6635179</v>
+        <v>6634990</v>
       </c>
       <c r="S168" t="n">
         <v>10</v>
@@ -18457,6 +18452,11 @@
       </c>
       <c r="AG168" t="b">
         <v>0</v>
+      </c>
+      <c r="AO168" t="inlineStr">
+        <is>
+          <t>tallåga</t>
+        </is>
       </c>
       <c r="AT168" t="inlineStr"/>
       <c r="AW168" t="inlineStr">
@@ -18480,7 +18480,7 @@
         <v>129419036</v>
       </c>
       <c r="B169" t="n">
-        <v>90423</v>
+        <v>90424</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -18581,7 +18581,7 @@
         <v>129419064</v>
       </c>
       <c r="B170" t="n">
-        <v>92237</v>
+        <v>92238</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -18679,32 +18679,32 @@
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>129419044</v>
+        <v>129419033</v>
       </c>
       <c r="B171" t="n">
-        <v>90374</v>
+        <v>91588</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E171" t="n">
-        <v>6268</v>
+        <v>1202</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Rökmusseron</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Tricholoma fucatum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Kumm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I171" t="inlineStr"/>
@@ -18714,10 +18714,10 @@
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>572651</v>
+        <v>572416</v>
       </c>
       <c r="R171" t="n">
-        <v>6635193</v>
+        <v>6634855</v>
       </c>
       <c r="S171" t="n">
         <v>10</v>
@@ -18783,7 +18783,7 @@
         <v>129419043</v>
       </c>
       <c r="B172" t="n">
-        <v>91111</v>
+        <v>91112</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -18885,7 +18885,7 @@
         <v>129419023</v>
       </c>
       <c r="B173" t="n">
-        <v>91551</v>
+        <v>91552</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -18983,32 +18983,32 @@
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>129419033</v>
+        <v>129419044</v>
       </c>
       <c r="B174" t="n">
-        <v>91587</v>
+        <v>90375</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E174" t="n">
-        <v>1202</v>
+        <v>6268</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rökmusseron</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Tricholoma fucatum</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.:Fr.) P. Kumm.</t>
         </is>
       </c>
       <c r="I174" t="inlineStr"/>
@@ -19018,10 +19018,10 @@
         </is>
       </c>
       <c r="Q174" t="n">
-        <v>572416</v>
+        <v>572651</v>
       </c>
       <c r="R174" t="n">
-        <v>6634855</v>
+        <v>6635193</v>
       </c>
       <c r="S174" t="n">
         <v>10</v>
@@ -19087,7 +19087,7 @@
         <v>129419049</v>
       </c>
       <c r="B175" t="n">
-        <v>95969</v>
+        <v>95970</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -19190,32 +19190,32 @@
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>129419025</v>
+        <v>129419022</v>
       </c>
       <c r="B176" t="n">
-        <v>91551</v>
+        <v>97015</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E176" t="n">
-        <v>5447</v>
+        <v>53</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I176" t="inlineStr"/>
@@ -19225,10 +19225,10 @@
         </is>
       </c>
       <c r="Q176" t="n">
-        <v>572492</v>
+        <v>572437</v>
       </c>
       <c r="R176" t="n">
-        <v>6634998</v>
+        <v>6634991</v>
       </c>
       <c r="S176" t="n">
         <v>10</v>
@@ -19291,32 +19291,32 @@
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>129419022</v>
+        <v>129419025</v>
       </c>
       <c r="B177" t="n">
-        <v>97014</v>
+        <v>91552</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E177" t="n">
-        <v>53</v>
+        <v>5447</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I177" t="inlineStr"/>
@@ -19326,10 +19326,10 @@
         </is>
       </c>
       <c r="Q177" t="n">
-        <v>572437</v>
+        <v>572492</v>
       </c>
       <c r="R177" t="n">
-        <v>6634991</v>
+        <v>6634998</v>
       </c>
       <c r="S177" t="n">
         <v>10</v>
@@ -19392,48 +19392,45 @@
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>129419062</v>
+        <v>129419030</v>
       </c>
       <c r="B178" t="n">
-        <v>92009</v>
+        <v>91588</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E178" t="n">
-        <v>298</v>
+        <v>1202</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Laxgröppa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>Meruliopsis rubicunda</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>(Litsch.) Spirin &amp; K.H.Larss.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I178" t="inlineStr"/>
-      <c r="J178" t="inlineStr"/>
-      <c r="K178" t="inlineStr"/>
-      <c r="N178" t="inlineStr"/>
       <c r="P178" t="inlineStr">
         <is>
           <t>Väst Norrby gamla tomt, Vstm</t>
         </is>
       </c>
       <c r="Q178" t="n">
-        <v>572637</v>
+        <v>572414</v>
       </c>
       <c r="R178" t="n">
-        <v>6635268</v>
+        <v>6635279</v>
       </c>
       <c r="S178" t="n">
         <v>10</v>
@@ -19474,7 +19471,6 @@
       <c r="AE178" t="b">
         <v>0</v>
       </c>
-      <c r="AF178" t="inlineStr"/>
       <c r="AG178" t="b">
         <v>0</v>
       </c>
@@ -19497,45 +19493,48 @@
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>129419030</v>
+        <v>129419062</v>
       </c>
       <c r="B179" t="n">
-        <v>91587</v>
+        <v>92010</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E179" t="n">
-        <v>1202</v>
+        <v>298</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Laxgröppa</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Meruliopsis rubicunda</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Litsch.) Spirin &amp; K.H.Larss.</t>
         </is>
       </c>
       <c r="I179" t="inlineStr"/>
+      <c r="J179" t="inlineStr"/>
+      <c r="K179" t="inlineStr"/>
+      <c r="N179" t="inlineStr"/>
       <c r="P179" t="inlineStr">
         <is>
           <t>Väst Norrby gamla tomt, Vstm</t>
         </is>
       </c>
       <c r="Q179" t="n">
-        <v>572414</v>
+        <v>572637</v>
       </c>
       <c r="R179" t="n">
-        <v>6635279</v>
+        <v>6635268</v>
       </c>
       <c r="S179" t="n">
         <v>10</v>
@@ -19576,6 +19575,7 @@
       <c r="AE179" t="b">
         <v>0</v>
       </c>
+      <c r="AF179" t="inlineStr"/>
       <c r="AG179" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 12276-2023 artfynd.xlsx
+++ b/artfynd/A 12276-2023 artfynd.xlsx
@@ -18068,32 +18068,32 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>129419024</v>
+        <v>129419035</v>
       </c>
       <c r="B165" t="n">
-        <v>91552</v>
+        <v>91588</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E165" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I165" t="inlineStr"/>
@@ -18103,10 +18103,10 @@
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>572501</v>
+        <v>572625</v>
       </c>
       <c r="R165" t="n">
-        <v>6635056</v>
+        <v>6635270</v>
       </c>
       <c r="S165" t="n">
         <v>10</v>
@@ -18169,32 +18169,32 @@
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>129419035</v>
+        <v>129419024</v>
       </c>
       <c r="B166" t="n">
-        <v>91588</v>
+        <v>91552</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E166" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I166" t="inlineStr"/>
@@ -18204,10 +18204,10 @@
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>572625</v>
+        <v>572501</v>
       </c>
       <c r="R166" t="n">
-        <v>6635270</v>
+        <v>6635056</v>
       </c>
       <c r="S166" t="n">
         <v>10</v>

--- a/artfynd/A 12276-2023 artfynd.xlsx
+++ b/artfynd/A 12276-2023 artfynd.xlsx
@@ -17061,7 +17061,7 @@
         <v>129419047</v>
       </c>
       <c r="B155" t="n">
-        <v>92862</v>
+        <v>92867</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -17162,7 +17162,7 @@
         <v>129419026</v>
       </c>
       <c r="B156" t="n">
-        <v>91552</v>
+        <v>91557</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -17263,7 +17263,7 @@
         <v>129419048</v>
       </c>
       <c r="B157" t="n">
-        <v>98769</v>
+        <v>98774</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -17364,7 +17364,7 @@
         <v>129419028</v>
       </c>
       <c r="B158" t="n">
-        <v>91588</v>
+        <v>91593</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -17465,7 +17465,7 @@
         <v>129419032</v>
       </c>
       <c r="B159" t="n">
-        <v>91588</v>
+        <v>91593</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -17563,32 +17563,32 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>129419027</v>
+        <v>129419034</v>
       </c>
       <c r="B160" t="n">
-        <v>91552</v>
+        <v>91593</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E160" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I160" t="inlineStr"/>
@@ -17598,10 +17598,10 @@
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>572637</v>
+        <v>572518</v>
       </c>
       <c r="R160" t="n">
-        <v>6635268</v>
+        <v>6635088</v>
       </c>
       <c r="S160" t="n">
         <v>10</v>
@@ -17664,10 +17664,10 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>129419034</v>
+        <v>129419029</v>
       </c>
       <c r="B161" t="n">
-        <v>91588</v>
+        <v>91593</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -17699,10 +17699,10 @@
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>572518</v>
+        <v>572434</v>
       </c>
       <c r="R161" t="n">
-        <v>6635088</v>
+        <v>6635240</v>
       </c>
       <c r="S161" t="n">
         <v>10</v>
@@ -17765,32 +17765,32 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>129419029</v>
+        <v>129419027</v>
       </c>
       <c r="B162" t="n">
-        <v>91588</v>
+        <v>91557</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E162" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I162" t="inlineStr"/>
@@ -17800,10 +17800,10 @@
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>572434</v>
+        <v>572637</v>
       </c>
       <c r="R162" t="n">
-        <v>6635240</v>
+        <v>6635268</v>
       </c>
       <c r="S162" t="n">
         <v>10</v>
@@ -17866,32 +17866,32 @@
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>129419052</v>
+        <v>129419063</v>
       </c>
       <c r="B163" t="n">
-        <v>90970</v>
+        <v>91463</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E163" t="n">
-        <v>5685</v>
+        <v>3290</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Gullgröppa</t>
+          <t>Gaffelskinn</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Pseudomerulius aureus</t>
+          <t>Clavulicium macounii</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>(Fr.) Jülich</t>
+          <t>(Burt) J.Erikss. &amp; Boidin ex Parmasto</t>
         </is>
       </c>
       <c r="I163" t="inlineStr"/>
@@ -17901,10 +17901,10 @@
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>572365</v>
+        <v>572505</v>
       </c>
       <c r="R163" t="n">
-        <v>6635062</v>
+        <v>6635049</v>
       </c>
       <c r="S163" t="n">
         <v>10</v>
@@ -17967,32 +17967,32 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>129419063</v>
+        <v>129419052</v>
       </c>
       <c r="B164" t="n">
-        <v>91458</v>
+        <v>90975</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E164" t="n">
-        <v>3290</v>
+        <v>5685</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Gaffelskinn</t>
+          <t>Gullgröppa</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Clavulicium macounii</t>
+          <t>Pseudomerulius aureus</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>(Burt) J.Erikss. &amp; Boidin ex Parmasto</t>
+          <t>(Fr.) Jülich</t>
         </is>
       </c>
       <c r="I164" t="inlineStr"/>
@@ -18002,10 +18002,10 @@
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>572505</v>
+        <v>572365</v>
       </c>
       <c r="R164" t="n">
-        <v>6635049</v>
+        <v>6635062</v>
       </c>
       <c r="S164" t="n">
         <v>10</v>
@@ -18071,7 +18071,7 @@
         <v>129419035</v>
       </c>
       <c r="B165" t="n">
-        <v>91588</v>
+        <v>91593</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -18172,7 +18172,7 @@
         <v>129419024</v>
       </c>
       <c r="B166" t="n">
-        <v>91552</v>
+        <v>91557</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -18273,7 +18273,7 @@
         <v>129419031</v>
       </c>
       <c r="B167" t="n">
-        <v>91588</v>
+        <v>91593</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -18374,7 +18374,7 @@
         <v>129419041</v>
       </c>
       <c r="B168" t="n">
-        <v>92510</v>
+        <v>92515</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -18480,7 +18480,7 @@
         <v>129419036</v>
       </c>
       <c r="B169" t="n">
-        <v>90424</v>
+        <v>90429</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -18581,7 +18581,7 @@
         <v>129419064</v>
       </c>
       <c r="B170" t="n">
-        <v>92238</v>
+        <v>92243</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -18682,7 +18682,7 @@
         <v>129419033</v>
       </c>
       <c r="B171" t="n">
-        <v>91588</v>
+        <v>91593</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -18780,32 +18780,32 @@
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>129419043</v>
+        <v>129419044</v>
       </c>
       <c r="B172" t="n">
-        <v>91112</v>
+        <v>90380</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E172" t="n">
-        <v>5733</v>
+        <v>6268</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Såpfingersvamp</t>
+          <t>Rökmusseron</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>Ramaria lutea</t>
+          <t>Tricholoma fucatum</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>(Vent.) Schild</t>
+          <t>(Fr.:Fr.) P. Kumm.</t>
         </is>
       </c>
       <c r="I172" t="inlineStr"/>
@@ -18815,10 +18815,10 @@
         </is>
       </c>
       <c r="Q172" t="n">
-        <v>572574</v>
+        <v>572651</v>
       </c>
       <c r="R172" t="n">
-        <v>6634982</v>
+        <v>6635193</v>
       </c>
       <c r="S172" t="n">
         <v>10</v>
@@ -18859,7 +18859,6 @@
       <c r="AE172" t="b">
         <v>0</v>
       </c>
-      <c r="AF172" t="inlineStr"/>
       <c r="AG172" t="b">
         <v>0</v>
       </c>
@@ -18882,32 +18881,32 @@
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>129419023</v>
+        <v>129419043</v>
       </c>
       <c r="B173" t="n">
-        <v>91552</v>
+        <v>91117</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E173" t="n">
-        <v>5447</v>
+        <v>5733</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Såpfingersvamp</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Ramaria lutea</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Vent.) Schild</t>
         </is>
       </c>
       <c r="I173" t="inlineStr"/>
@@ -18917,10 +18916,10 @@
         </is>
       </c>
       <c r="Q173" t="n">
-        <v>572375</v>
+        <v>572574</v>
       </c>
       <c r="R173" t="n">
-        <v>6635185</v>
+        <v>6634982</v>
       </c>
       <c r="S173" t="n">
         <v>10</v>
@@ -18961,6 +18960,7 @@
       <c r="AE173" t="b">
         <v>0</v>
       </c>
+      <c r="AF173" t="inlineStr"/>
       <c r="AG173" t="b">
         <v>0</v>
       </c>
@@ -18983,10 +18983,10 @@
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>129419044</v>
+        <v>129419023</v>
       </c>
       <c r="B174" t="n">
-        <v>90375</v>
+        <v>91557</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -18994,21 +18994,21 @@
         </is>
       </c>
       <c r="E174" t="n">
-        <v>6268</v>
+        <v>5447</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Rökmusseron</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>Tricholoma fucatum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Kumm.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I174" t="inlineStr"/>
@@ -19018,10 +19018,10 @@
         </is>
       </c>
       <c r="Q174" t="n">
-        <v>572651</v>
+        <v>572375</v>
       </c>
       <c r="R174" t="n">
-        <v>6635193</v>
+        <v>6635185</v>
       </c>
       <c r="S174" t="n">
         <v>10</v>
@@ -19087,7 +19087,7 @@
         <v>129419049</v>
       </c>
       <c r="B175" t="n">
-        <v>95970</v>
+        <v>95975</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -19193,7 +19193,7 @@
         <v>129419022</v>
       </c>
       <c r="B176" t="n">
-        <v>97015</v>
+        <v>97020</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -19294,7 +19294,7 @@
         <v>129419025</v>
       </c>
       <c r="B177" t="n">
-        <v>91552</v>
+        <v>91557</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -19395,7 +19395,7 @@
         <v>129419030</v>
       </c>
       <c r="B178" t="n">
-        <v>91588</v>
+        <v>91593</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -19496,7 +19496,7 @@
         <v>129419062</v>
       </c>
       <c r="B179" t="n">
-        <v>92010</v>
+        <v>92015</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>

--- a/artfynd/A 12276-2023 artfynd.xlsx
+++ b/artfynd/A 12276-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY179"/>
+  <dimension ref="A1:AY180"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18578,32 +18578,32 @@
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>129419064</v>
+        <v>129419033</v>
       </c>
       <c r="B170" t="n">
-        <v>92243</v>
+        <v>91593</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E170" t="n">
-        <v>1339</v>
+        <v>1202</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I170" t="inlineStr"/>
@@ -18613,10 +18613,10 @@
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>572450</v>
+        <v>572416</v>
       </c>
       <c r="R170" t="n">
-        <v>6635232</v>
+        <v>6634855</v>
       </c>
       <c r="S170" t="n">
         <v>10</v>
@@ -18679,32 +18679,32 @@
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>129419033</v>
+        <v>129419064</v>
       </c>
       <c r="B171" t="n">
-        <v>91593</v>
+        <v>92243</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E171" t="n">
-        <v>1202</v>
+        <v>1339</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I171" t="inlineStr"/>
@@ -18714,10 +18714,10 @@
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>572416</v>
+        <v>572450</v>
       </c>
       <c r="R171" t="n">
-        <v>6634855</v>
+        <v>6635232</v>
       </c>
       <c r="S171" t="n">
         <v>10</v>
@@ -19596,6 +19596,130 @@
         </is>
       </c>
     </row>
+    <row r="180">
+      <c r="A180" t="n">
+        <v>129808810</v>
+      </c>
+      <c r="B180" t="n">
+        <v>98774</v>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E180" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F180" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G180" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H180" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I180" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J180" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K180" t="inlineStr"/>
+      <c r="L180" t="inlineStr"/>
+      <c r="N180" t="inlineStr"/>
+      <c r="P180" t="inlineStr">
+        <is>
+          <t>Norrby gamla tomt, V om (knärot), Vstm</t>
+        </is>
+      </c>
+      <c r="Q180" t="n">
+        <v>572387</v>
+      </c>
+      <c r="R180" t="n">
+        <v>6635334</v>
+      </c>
+      <c r="S180" t="n">
+        <v>10</v>
+      </c>
+      <c r="T180" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U180" t="inlineStr">
+        <is>
+          <t>Sala</t>
+        </is>
+      </c>
+      <c r="V180" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W180" t="inlineStr">
+        <is>
+          <t>Fläckebo</t>
+        </is>
+      </c>
+      <c r="X180" t="inlineStr">
+        <is>
+          <t>U-Sal-1171</t>
+        </is>
+      </c>
+      <c r="Y180" t="inlineStr">
+        <is>
+          <t>2025-09-05</t>
+        </is>
+      </c>
+      <c r="AA180" t="inlineStr">
+        <is>
+          <t>2025-09-05</t>
+        </is>
+      </c>
+      <c r="AC180" t="inlineStr">
+        <is>
+          <t>minst ("noterad")</t>
+        </is>
+      </c>
+      <c r="AD180" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE180" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF180" t="inlineStr"/>
+      <c r="AG180" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT180" t="inlineStr"/>
+      <c r="AW180" t="inlineStr">
+        <is>
+          <t>Bo Eriksson</t>
+        </is>
+      </c>
+      <c r="AX180" t="inlineStr">
+        <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AY180" t="inlineStr">
+        <is>
+          <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 12276-2023 artfynd.xlsx
+++ b/artfynd/A 12276-2023 artfynd.xlsx
@@ -18068,32 +18068,32 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>129419035</v>
+        <v>129419024</v>
       </c>
       <c r="B165" t="n">
-        <v>91593</v>
+        <v>91557</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E165" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I165" t="inlineStr"/>
@@ -18103,10 +18103,10 @@
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>572625</v>
+        <v>572501</v>
       </c>
       <c r="R165" t="n">
-        <v>6635270</v>
+        <v>6635056</v>
       </c>
       <c r="S165" t="n">
         <v>10</v>
@@ -18169,32 +18169,32 @@
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>129419024</v>
+        <v>129419035</v>
       </c>
       <c r="B166" t="n">
-        <v>91557</v>
+        <v>91593</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E166" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I166" t="inlineStr"/>
@@ -18204,10 +18204,10 @@
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>572501</v>
+        <v>572625</v>
       </c>
       <c r="R166" t="n">
-        <v>6635056</v>
+        <v>6635270</v>
       </c>
       <c r="S166" t="n">
         <v>10</v>
@@ -18270,32 +18270,32 @@
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>129419031</v>
+        <v>129419041</v>
       </c>
       <c r="B167" t="n">
-        <v>91593</v>
+        <v>92515</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E167" t="n">
-        <v>1202</v>
+        <v>4740</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Sotriska</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lactarius lignyotus</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I167" t="inlineStr"/>
@@ -18305,10 +18305,10 @@
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>572381</v>
+        <v>572441</v>
       </c>
       <c r="R167" t="n">
-        <v>6635179</v>
+        <v>6634990</v>
       </c>
       <c r="S167" t="n">
         <v>10</v>
@@ -18351,6 +18351,11 @@
       </c>
       <c r="AG167" t="b">
         <v>0</v>
+      </c>
+      <c r="AO167" t="inlineStr">
+        <is>
+          <t>tallåga</t>
+        </is>
       </c>
       <c r="AT167" t="inlineStr"/>
       <c r="AW167" t="inlineStr">
@@ -18371,32 +18376,32 @@
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>129419041</v>
+        <v>129419031</v>
       </c>
       <c r="B168" t="n">
-        <v>92515</v>
+        <v>91593</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E168" t="n">
-        <v>4740</v>
+        <v>1202</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Sotriska</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Lactarius lignyotus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I168" t="inlineStr"/>
@@ -18406,10 +18411,10 @@
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>572441</v>
+        <v>572381</v>
       </c>
       <c r="R168" t="n">
-        <v>6634990</v>
+        <v>6635179</v>
       </c>
       <c r="S168" t="n">
         <v>10</v>
@@ -18452,11 +18457,6 @@
       </c>
       <c r="AG168" t="b">
         <v>0</v>
-      </c>
-      <c r="AO168" t="inlineStr">
-        <is>
-          <t>tallåga</t>
-        </is>
       </c>
       <c r="AT168" t="inlineStr"/>
       <c r="AW168" t="inlineStr">
@@ -18578,32 +18578,32 @@
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>129419033</v>
+        <v>129419064</v>
       </c>
       <c r="B170" t="n">
-        <v>91593</v>
+        <v>92243</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E170" t="n">
-        <v>1202</v>
+        <v>1339</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I170" t="inlineStr"/>
@@ -18613,10 +18613,10 @@
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>572416</v>
+        <v>572450</v>
       </c>
       <c r="R170" t="n">
-        <v>6634855</v>
+        <v>6635232</v>
       </c>
       <c r="S170" t="n">
         <v>10</v>
@@ -18679,10 +18679,10 @@
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>129419064</v>
+        <v>129419044</v>
       </c>
       <c r="B171" t="n">
-        <v>92243</v>
+        <v>90380</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -18690,21 +18690,21 @@
         </is>
       </c>
       <c r="E171" t="n">
-        <v>1339</v>
+        <v>6268</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Rökmusseron</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Tricholoma fucatum</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>(Fr.:Fr.) P. Kumm.</t>
         </is>
       </c>
       <c r="I171" t="inlineStr"/>
@@ -18714,10 +18714,10 @@
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>572450</v>
+        <v>572651</v>
       </c>
       <c r="R171" t="n">
-        <v>6635232</v>
+        <v>6635193</v>
       </c>
       <c r="S171" t="n">
         <v>10</v>
@@ -18780,32 +18780,32 @@
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>129419044</v>
+        <v>129419033</v>
       </c>
       <c r="B172" t="n">
-        <v>90380</v>
+        <v>91593</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E172" t="n">
-        <v>6268</v>
+        <v>1202</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Rökmusseron</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>Tricholoma fucatum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Kumm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I172" t="inlineStr"/>
@@ -18815,10 +18815,10 @@
         </is>
       </c>
       <c r="Q172" t="n">
-        <v>572651</v>
+        <v>572416</v>
       </c>
       <c r="R172" t="n">
-        <v>6635193</v>
+        <v>6634855</v>
       </c>
       <c r="S172" t="n">
         <v>10</v>
@@ -19392,45 +19392,48 @@
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>129419030</v>
+        <v>129419062</v>
       </c>
       <c r="B178" t="n">
-        <v>91593</v>
+        <v>92015</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E178" t="n">
-        <v>1202</v>
+        <v>298</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Laxgröppa</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Meruliopsis rubicunda</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Litsch.) Spirin &amp; K.H.Larss.</t>
         </is>
       </c>
       <c r="I178" t="inlineStr"/>
+      <c r="J178" t="inlineStr"/>
+      <c r="K178" t="inlineStr"/>
+      <c r="N178" t="inlineStr"/>
       <c r="P178" t="inlineStr">
         <is>
           <t>Väst Norrby gamla tomt, Vstm</t>
         </is>
       </c>
       <c r="Q178" t="n">
-        <v>572414</v>
+        <v>572637</v>
       </c>
       <c r="R178" t="n">
-        <v>6635279</v>
+        <v>6635268</v>
       </c>
       <c r="S178" t="n">
         <v>10</v>
@@ -19471,6 +19474,7 @@
       <c r="AE178" t="b">
         <v>0</v>
       </c>
+      <c r="AF178" t="inlineStr"/>
       <c r="AG178" t="b">
         <v>0</v>
       </c>
@@ -19493,48 +19497,45 @@
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>129419062</v>
+        <v>129419030</v>
       </c>
       <c r="B179" t="n">
-        <v>92015</v>
+        <v>91593</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E179" t="n">
-        <v>298</v>
+        <v>1202</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Laxgröppa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>Meruliopsis rubicunda</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>(Litsch.) Spirin &amp; K.H.Larss.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I179" t="inlineStr"/>
-      <c r="J179" t="inlineStr"/>
-      <c r="K179" t="inlineStr"/>
-      <c r="N179" t="inlineStr"/>
       <c r="P179" t="inlineStr">
         <is>
           <t>Väst Norrby gamla tomt, Vstm</t>
         </is>
       </c>
       <c r="Q179" t="n">
-        <v>572637</v>
+        <v>572414</v>
       </c>
       <c r="R179" t="n">
-        <v>6635268</v>
+        <v>6635279</v>
       </c>
       <c r="S179" t="n">
         <v>10</v>
@@ -19575,7 +19576,6 @@
       <c r="AE179" t="b">
         <v>0</v>
       </c>
-      <c r="AF179" t="inlineStr"/>
       <c r="AG179" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 12276-2023 artfynd.xlsx
+++ b/artfynd/A 12276-2023 artfynd.xlsx
@@ -18068,32 +18068,32 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>129419024</v>
+        <v>129419035</v>
       </c>
       <c r="B165" t="n">
-        <v>91557</v>
+        <v>91593</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E165" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I165" t="inlineStr"/>
@@ -18103,10 +18103,10 @@
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>572501</v>
+        <v>572625</v>
       </c>
       <c r="R165" t="n">
-        <v>6635056</v>
+        <v>6635270</v>
       </c>
       <c r="S165" t="n">
         <v>10</v>
@@ -18169,32 +18169,32 @@
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>129419035</v>
+        <v>129419024</v>
       </c>
       <c r="B166" t="n">
-        <v>91593</v>
+        <v>91557</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E166" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I166" t="inlineStr"/>
@@ -18204,10 +18204,10 @@
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>572625</v>
+        <v>572501</v>
       </c>
       <c r="R166" t="n">
-        <v>6635270</v>
+        <v>6635056</v>
       </c>
       <c r="S166" t="n">
         <v>10</v>
@@ -18270,32 +18270,32 @@
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>129419041</v>
+        <v>129419031</v>
       </c>
       <c r="B167" t="n">
-        <v>92515</v>
+        <v>91593</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E167" t="n">
-        <v>4740</v>
+        <v>1202</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Sotriska</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Lactarius lignyotus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I167" t="inlineStr"/>
@@ -18305,10 +18305,10 @@
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>572441</v>
+        <v>572381</v>
       </c>
       <c r="R167" t="n">
-        <v>6634990</v>
+        <v>6635179</v>
       </c>
       <c r="S167" t="n">
         <v>10</v>
@@ -18351,11 +18351,6 @@
       </c>
       <c r="AG167" t="b">
         <v>0</v>
-      </c>
-      <c r="AO167" t="inlineStr">
-        <is>
-          <t>tallåga</t>
-        </is>
       </c>
       <c r="AT167" t="inlineStr"/>
       <c r="AW167" t="inlineStr">
@@ -18376,32 +18371,32 @@
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>129419031</v>
+        <v>129419041</v>
       </c>
       <c r="B168" t="n">
-        <v>91593</v>
+        <v>92515</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E168" t="n">
-        <v>1202</v>
+        <v>4740</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Sotriska</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lactarius lignyotus</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I168" t="inlineStr"/>
@@ -18411,10 +18406,10 @@
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>572381</v>
+        <v>572441</v>
       </c>
       <c r="R168" t="n">
-        <v>6635179</v>
+        <v>6634990</v>
       </c>
       <c r="S168" t="n">
         <v>10</v>
@@ -18457,6 +18452,11 @@
       </c>
       <c r="AG168" t="b">
         <v>0</v>
+      </c>
+      <c r="AO168" t="inlineStr">
+        <is>
+          <t>tallåga</t>
+        </is>
       </c>
       <c r="AT168" t="inlineStr"/>
       <c r="AW168" t="inlineStr">
@@ -18578,32 +18578,32 @@
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>129419064</v>
+        <v>129419043</v>
       </c>
       <c r="B170" t="n">
-        <v>92243</v>
+        <v>91117</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E170" t="n">
-        <v>1339</v>
+        <v>5733</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Såpfingersvamp</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Ramaria lutea</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>(Vent.) Schild</t>
         </is>
       </c>
       <c r="I170" t="inlineStr"/>
@@ -18613,10 +18613,10 @@
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>572450</v>
+        <v>572574</v>
       </c>
       <c r="R170" t="n">
-        <v>6635232</v>
+        <v>6634982</v>
       </c>
       <c r="S170" t="n">
         <v>10</v>
@@ -18657,6 +18657,7 @@
       <c r="AE170" t="b">
         <v>0</v>
       </c>
+      <c r="AF170" t="inlineStr"/>
       <c r="AG170" t="b">
         <v>0</v>
       </c>
@@ -18679,10 +18680,10 @@
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>129419044</v>
+        <v>129419023</v>
       </c>
       <c r="B171" t="n">
-        <v>90380</v>
+        <v>91557</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -18690,21 +18691,21 @@
         </is>
       </c>
       <c r="E171" t="n">
-        <v>6268</v>
+        <v>5447</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Rökmusseron</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Tricholoma fucatum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Kumm.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I171" t="inlineStr"/>
@@ -18714,10 +18715,10 @@
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>572651</v>
+        <v>572375</v>
       </c>
       <c r="R171" t="n">
-        <v>6635193</v>
+        <v>6635185</v>
       </c>
       <c r="S171" t="n">
         <v>10</v>
@@ -18881,32 +18882,32 @@
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>129419043</v>
+        <v>129419064</v>
       </c>
       <c r="B173" t="n">
-        <v>91117</v>
+        <v>92243</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E173" t="n">
-        <v>5733</v>
+        <v>1339</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Såpfingersvamp</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>Ramaria lutea</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>(Vent.) Schild</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I173" t="inlineStr"/>
@@ -18916,10 +18917,10 @@
         </is>
       </c>
       <c r="Q173" t="n">
-        <v>572574</v>
+        <v>572450</v>
       </c>
       <c r="R173" t="n">
-        <v>6634982</v>
+        <v>6635232</v>
       </c>
       <c r="S173" t="n">
         <v>10</v>
@@ -18960,7 +18961,6 @@
       <c r="AE173" t="b">
         <v>0</v>
       </c>
-      <c r="AF173" t="inlineStr"/>
       <c r="AG173" t="b">
         <v>0</v>
       </c>
@@ -18983,10 +18983,10 @@
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>129419023</v>
+        <v>129419044</v>
       </c>
       <c r="B174" t="n">
-        <v>91557</v>
+        <v>90380</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -18994,21 +18994,21 @@
         </is>
       </c>
       <c r="E174" t="n">
-        <v>5447</v>
+        <v>6268</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Rökmusseron</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Tricholoma fucatum</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.:Fr.) P. Kumm.</t>
         </is>
       </c>
       <c r="I174" t="inlineStr"/>
@@ -19018,10 +19018,10 @@
         </is>
       </c>
       <c r="Q174" t="n">
-        <v>572375</v>
+        <v>572651</v>
       </c>
       <c r="R174" t="n">
-        <v>6635185</v>
+        <v>6635193</v>
       </c>
       <c r="S174" t="n">
         <v>10</v>
@@ -19392,48 +19392,45 @@
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>129419062</v>
+        <v>129419030</v>
       </c>
       <c r="B178" t="n">
-        <v>92015</v>
+        <v>91593</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E178" t="n">
-        <v>298</v>
+        <v>1202</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Laxgröppa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>Meruliopsis rubicunda</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>(Litsch.) Spirin &amp; K.H.Larss.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I178" t="inlineStr"/>
-      <c r="J178" t="inlineStr"/>
-      <c r="K178" t="inlineStr"/>
-      <c r="N178" t="inlineStr"/>
       <c r="P178" t="inlineStr">
         <is>
           <t>Väst Norrby gamla tomt, Vstm</t>
         </is>
       </c>
       <c r="Q178" t="n">
-        <v>572637</v>
+        <v>572414</v>
       </c>
       <c r="R178" t="n">
-        <v>6635268</v>
+        <v>6635279</v>
       </c>
       <c r="S178" t="n">
         <v>10</v>
@@ -19474,7 +19471,6 @@
       <c r="AE178" t="b">
         <v>0</v>
       </c>
-      <c r="AF178" t="inlineStr"/>
       <c r="AG178" t="b">
         <v>0</v>
       </c>
@@ -19497,45 +19493,48 @@
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>129419030</v>
+        <v>129419062</v>
       </c>
       <c r="B179" t="n">
-        <v>91593</v>
+        <v>92015</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E179" t="n">
-        <v>1202</v>
+        <v>298</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Laxgröppa</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Meruliopsis rubicunda</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Litsch.) Spirin &amp; K.H.Larss.</t>
         </is>
       </c>
       <c r="I179" t="inlineStr"/>
+      <c r="J179" t="inlineStr"/>
+      <c r="K179" t="inlineStr"/>
+      <c r="N179" t="inlineStr"/>
       <c r="P179" t="inlineStr">
         <is>
           <t>Väst Norrby gamla tomt, Vstm</t>
         </is>
       </c>
       <c r="Q179" t="n">
-        <v>572414</v>
+        <v>572637</v>
       </c>
       <c r="R179" t="n">
-        <v>6635279</v>
+        <v>6635268</v>
       </c>
       <c r="S179" t="n">
         <v>10</v>
@@ -19576,6 +19575,7 @@
       <c r="AE179" t="b">
         <v>0</v>
       </c>
+      <c r="AF179" t="inlineStr"/>
       <c r="AG179" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 12276-2023 artfynd.xlsx
+++ b/artfynd/A 12276-2023 artfynd.xlsx
@@ -17061,7 +17061,7 @@
         <v>129419047</v>
       </c>
       <c r="B155" t="n">
-        <v>92867</v>
+        <v>92871</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -17162,7 +17162,7 @@
         <v>129419026</v>
       </c>
       <c r="B156" t="n">
-        <v>91557</v>
+        <v>91561</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -17263,7 +17263,7 @@
         <v>129419048</v>
       </c>
       <c r="B157" t="n">
-        <v>98774</v>
+        <v>98778</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -17364,7 +17364,7 @@
         <v>129419028</v>
       </c>
       <c r="B158" t="n">
-        <v>91593</v>
+        <v>91597</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -17465,7 +17465,7 @@
         <v>129419032</v>
       </c>
       <c r="B159" t="n">
-        <v>91593</v>
+        <v>91597</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -17566,7 +17566,7 @@
         <v>129419034</v>
       </c>
       <c r="B160" t="n">
-        <v>91593</v>
+        <v>91597</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -17667,7 +17667,7 @@
         <v>129419029</v>
       </c>
       <c r="B161" t="n">
-        <v>91593</v>
+        <v>91597</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -17768,7 +17768,7 @@
         <v>129419027</v>
       </c>
       <c r="B162" t="n">
-        <v>91557</v>
+        <v>91561</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -17869,7 +17869,7 @@
         <v>129419063</v>
       </c>
       <c r="B163" t="n">
-        <v>91463</v>
+        <v>91467</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -17970,7 +17970,7 @@
         <v>129419052</v>
       </c>
       <c r="B164" t="n">
-        <v>90975</v>
+        <v>90979</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -18068,32 +18068,32 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>129419035</v>
+        <v>129419024</v>
       </c>
       <c r="B165" t="n">
-        <v>91593</v>
+        <v>91561</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E165" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I165" t="inlineStr"/>
@@ -18103,10 +18103,10 @@
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>572625</v>
+        <v>572501</v>
       </c>
       <c r="R165" t="n">
-        <v>6635270</v>
+        <v>6635056</v>
       </c>
       <c r="S165" t="n">
         <v>10</v>
@@ -18169,32 +18169,32 @@
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>129419024</v>
+        <v>129419035</v>
       </c>
       <c r="B166" t="n">
-        <v>91557</v>
+        <v>91597</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E166" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I166" t="inlineStr"/>
@@ -18204,10 +18204,10 @@
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>572501</v>
+        <v>572625</v>
       </c>
       <c r="R166" t="n">
-        <v>6635056</v>
+        <v>6635270</v>
       </c>
       <c r="S166" t="n">
         <v>10</v>
@@ -18273,7 +18273,7 @@
         <v>129419031</v>
       </c>
       <c r="B167" t="n">
-        <v>91593</v>
+        <v>91597</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -18374,7 +18374,7 @@
         <v>129419041</v>
       </c>
       <c r="B168" t="n">
-        <v>92515</v>
+        <v>92519</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -18480,7 +18480,7 @@
         <v>129419036</v>
       </c>
       <c r="B169" t="n">
-        <v>90429</v>
+        <v>90433</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -18578,10 +18578,10 @@
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>129419043</v>
+        <v>129419033</v>
       </c>
       <c r="B170" t="n">
-        <v>91117</v>
+        <v>91597</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -18589,21 +18589,21 @@
         </is>
       </c>
       <c r="E170" t="n">
-        <v>5733</v>
+        <v>1202</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Såpfingersvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Ramaria lutea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>(Vent.) Schild</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I170" t="inlineStr"/>
@@ -18613,10 +18613,10 @@
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>572574</v>
+        <v>572416</v>
       </c>
       <c r="R170" t="n">
-        <v>6634982</v>
+        <v>6634855</v>
       </c>
       <c r="S170" t="n">
         <v>10</v>
@@ -18657,7 +18657,6 @@
       <c r="AE170" t="b">
         <v>0</v>
       </c>
-      <c r="AF170" t="inlineStr"/>
       <c r="AG170" t="b">
         <v>0</v>
       </c>
@@ -18680,10 +18679,10 @@
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>129419023</v>
+        <v>129419064</v>
       </c>
       <c r="B171" t="n">
-        <v>91557</v>
+        <v>92247</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -18691,21 +18690,21 @@
         </is>
       </c>
       <c r="E171" t="n">
-        <v>5447</v>
+        <v>1339</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I171" t="inlineStr"/>
@@ -18715,10 +18714,10 @@
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>572375</v>
+        <v>572450</v>
       </c>
       <c r="R171" t="n">
-        <v>6635185</v>
+        <v>6635232</v>
       </c>
       <c r="S171" t="n">
         <v>10</v>
@@ -18781,32 +18780,32 @@
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>129419033</v>
+        <v>129419044</v>
       </c>
       <c r="B172" t="n">
-        <v>91593</v>
+        <v>90384</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E172" t="n">
-        <v>1202</v>
+        <v>6268</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rökmusseron</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Tricholoma fucatum</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.:Fr.) P. Kumm.</t>
         </is>
       </c>
       <c r="I172" t="inlineStr"/>
@@ -18816,10 +18815,10 @@
         </is>
       </c>
       <c r="Q172" t="n">
-        <v>572416</v>
+        <v>572651</v>
       </c>
       <c r="R172" t="n">
-        <v>6634855</v>
+        <v>6635193</v>
       </c>
       <c r="S172" t="n">
         <v>10</v>
@@ -18882,32 +18881,32 @@
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>129419064</v>
+        <v>129419043</v>
       </c>
       <c r="B173" t="n">
-        <v>92243</v>
+        <v>91121</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E173" t="n">
-        <v>1339</v>
+        <v>5733</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Såpfingersvamp</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Ramaria lutea</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>(Vent.) Schild</t>
         </is>
       </c>
       <c r="I173" t="inlineStr"/>
@@ -18917,10 +18916,10 @@
         </is>
       </c>
       <c r="Q173" t="n">
-        <v>572450</v>
+        <v>572574</v>
       </c>
       <c r="R173" t="n">
-        <v>6635232</v>
+        <v>6634982</v>
       </c>
       <c r="S173" t="n">
         <v>10</v>
@@ -18961,6 +18960,7 @@
       <c r="AE173" t="b">
         <v>0</v>
       </c>
+      <c r="AF173" t="inlineStr"/>
       <c r="AG173" t="b">
         <v>0</v>
       </c>
@@ -18983,10 +18983,10 @@
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>129419044</v>
+        <v>129419023</v>
       </c>
       <c r="B174" t="n">
-        <v>90380</v>
+        <v>91561</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -18994,21 +18994,21 @@
         </is>
       </c>
       <c r="E174" t="n">
-        <v>6268</v>
+        <v>5447</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Rökmusseron</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>Tricholoma fucatum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Kumm.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I174" t="inlineStr"/>
@@ -19018,10 +19018,10 @@
         </is>
       </c>
       <c r="Q174" t="n">
-        <v>572651</v>
+        <v>572375</v>
       </c>
       <c r="R174" t="n">
-        <v>6635193</v>
+        <v>6635185</v>
       </c>
       <c r="S174" t="n">
         <v>10</v>
@@ -19087,7 +19087,7 @@
         <v>129419049</v>
       </c>
       <c r="B175" t="n">
-        <v>95975</v>
+        <v>95979</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -19193,7 +19193,7 @@
         <v>129419022</v>
       </c>
       <c r="B176" t="n">
-        <v>97020</v>
+        <v>97024</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -19294,7 +19294,7 @@
         <v>129419025</v>
       </c>
       <c r="B177" t="n">
-        <v>91557</v>
+        <v>91561</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -19395,7 +19395,7 @@
         <v>129419030</v>
       </c>
       <c r="B178" t="n">
-        <v>91593</v>
+        <v>91597</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -19496,7 +19496,7 @@
         <v>129419062</v>
       </c>
       <c r="B179" t="n">
-        <v>92015</v>
+        <v>92019</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -19601,7 +19601,7 @@
         <v>129808810</v>
       </c>
       <c r="B180" t="n">
-        <v>98774</v>
+        <v>98778</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>

--- a/artfynd/A 12276-2023 artfynd.xlsx
+++ b/artfynd/A 12276-2023 artfynd.xlsx
@@ -17061,7 +17061,7 @@
         <v>129419047</v>
       </c>
       <c r="B155" t="n">
-        <v>92871</v>
+        <v>92873</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -17162,7 +17162,7 @@
         <v>129419026</v>
       </c>
       <c r="B156" t="n">
-        <v>91561</v>
+        <v>91563</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -17263,7 +17263,7 @@
         <v>129419048</v>
       </c>
       <c r="B157" t="n">
-        <v>98778</v>
+        <v>98780</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -17364,7 +17364,7 @@
         <v>129419028</v>
       </c>
       <c r="B158" t="n">
-        <v>91597</v>
+        <v>91599</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -17465,7 +17465,7 @@
         <v>129419032</v>
       </c>
       <c r="B159" t="n">
-        <v>91597</v>
+        <v>91599</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -17563,32 +17563,32 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>129419034</v>
+        <v>129419027</v>
       </c>
       <c r="B160" t="n">
-        <v>91597</v>
+        <v>91563</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E160" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I160" t="inlineStr"/>
@@ -17598,10 +17598,10 @@
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>572518</v>
+        <v>572637</v>
       </c>
       <c r="R160" t="n">
-        <v>6635088</v>
+        <v>6635268</v>
       </c>
       <c r="S160" t="n">
         <v>10</v>
@@ -17664,10 +17664,10 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>129419029</v>
+        <v>129419034</v>
       </c>
       <c r="B161" t="n">
-        <v>91597</v>
+        <v>91599</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -17699,10 +17699,10 @@
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>572434</v>
+        <v>572518</v>
       </c>
       <c r="R161" t="n">
-        <v>6635240</v>
+        <v>6635088</v>
       </c>
       <c r="S161" t="n">
         <v>10</v>
@@ -17765,32 +17765,32 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>129419027</v>
+        <v>129419029</v>
       </c>
       <c r="B162" t="n">
-        <v>91561</v>
+        <v>91599</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E162" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I162" t="inlineStr"/>
@@ -17800,10 +17800,10 @@
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>572637</v>
+        <v>572434</v>
       </c>
       <c r="R162" t="n">
-        <v>6635268</v>
+        <v>6635240</v>
       </c>
       <c r="S162" t="n">
         <v>10</v>
@@ -17869,7 +17869,7 @@
         <v>129419063</v>
       </c>
       <c r="B163" t="n">
-        <v>91467</v>
+        <v>91469</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -17970,7 +17970,7 @@
         <v>129419052</v>
       </c>
       <c r="B164" t="n">
-        <v>90979</v>
+        <v>90981</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -18068,32 +18068,32 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>129419024</v>
+        <v>129419035</v>
       </c>
       <c r="B165" t="n">
-        <v>91561</v>
+        <v>91599</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E165" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I165" t="inlineStr"/>
@@ -18103,10 +18103,10 @@
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>572501</v>
+        <v>572625</v>
       </c>
       <c r="R165" t="n">
-        <v>6635056</v>
+        <v>6635270</v>
       </c>
       <c r="S165" t="n">
         <v>10</v>
@@ -18169,32 +18169,32 @@
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>129419035</v>
+        <v>129419024</v>
       </c>
       <c r="B166" t="n">
-        <v>91597</v>
+        <v>91563</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E166" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I166" t="inlineStr"/>
@@ -18204,10 +18204,10 @@
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>572625</v>
+        <v>572501</v>
       </c>
       <c r="R166" t="n">
-        <v>6635270</v>
+        <v>6635056</v>
       </c>
       <c r="S166" t="n">
         <v>10</v>
@@ -18273,7 +18273,7 @@
         <v>129419031</v>
       </c>
       <c r="B167" t="n">
-        <v>91597</v>
+        <v>91599</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -18374,7 +18374,7 @@
         <v>129419041</v>
       </c>
       <c r="B168" t="n">
-        <v>92519</v>
+        <v>92521</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -18480,7 +18480,7 @@
         <v>129419036</v>
       </c>
       <c r="B169" t="n">
-        <v>90433</v>
+        <v>90435</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -18578,32 +18578,32 @@
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>129419033</v>
+        <v>129419064</v>
       </c>
       <c r="B170" t="n">
-        <v>91597</v>
+        <v>92249</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E170" t="n">
-        <v>1202</v>
+        <v>1339</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I170" t="inlineStr"/>
@@ -18613,10 +18613,10 @@
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>572416</v>
+        <v>572450</v>
       </c>
       <c r="R170" t="n">
-        <v>6634855</v>
+        <v>6635232</v>
       </c>
       <c r="S170" t="n">
         <v>10</v>
@@ -18679,32 +18679,32 @@
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>129419064</v>
+        <v>129419033</v>
       </c>
       <c r="B171" t="n">
-        <v>92247</v>
+        <v>91599</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E171" t="n">
-        <v>1339</v>
+        <v>1202</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I171" t="inlineStr"/>
@@ -18714,10 +18714,10 @@
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>572450</v>
+        <v>572416</v>
       </c>
       <c r="R171" t="n">
-        <v>6635232</v>
+        <v>6634855</v>
       </c>
       <c r="S171" t="n">
         <v>10</v>
@@ -18780,10 +18780,10 @@
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>129419044</v>
+        <v>129419023</v>
       </c>
       <c r="B172" t="n">
-        <v>90384</v>
+        <v>91563</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -18791,21 +18791,21 @@
         </is>
       </c>
       <c r="E172" t="n">
-        <v>6268</v>
+        <v>5447</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Rökmusseron</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>Tricholoma fucatum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Kumm.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I172" t="inlineStr"/>
@@ -18815,10 +18815,10 @@
         </is>
       </c>
       <c r="Q172" t="n">
-        <v>572651</v>
+        <v>572375</v>
       </c>
       <c r="R172" t="n">
-        <v>6635193</v>
+        <v>6635185</v>
       </c>
       <c r="S172" t="n">
         <v>10</v>
@@ -18881,32 +18881,32 @@
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>129419043</v>
+        <v>129419044</v>
       </c>
       <c r="B173" t="n">
-        <v>91121</v>
+        <v>90386</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E173" t="n">
-        <v>5733</v>
+        <v>6268</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Såpfingersvamp</t>
+          <t>Rökmusseron</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>Ramaria lutea</t>
+          <t>Tricholoma fucatum</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>(Vent.) Schild</t>
+          <t>(Fr.:Fr.) P. Kumm.</t>
         </is>
       </c>
       <c r="I173" t="inlineStr"/>
@@ -18916,10 +18916,10 @@
         </is>
       </c>
       <c r="Q173" t="n">
-        <v>572574</v>
+        <v>572651</v>
       </c>
       <c r="R173" t="n">
-        <v>6634982</v>
+        <v>6635193</v>
       </c>
       <c r="S173" t="n">
         <v>10</v>
@@ -18960,7 +18960,6 @@
       <c r="AE173" t="b">
         <v>0</v>
       </c>
-      <c r="AF173" t="inlineStr"/>
       <c r="AG173" t="b">
         <v>0</v>
       </c>
@@ -18983,32 +18982,32 @@
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>129419023</v>
+        <v>129419043</v>
       </c>
       <c r="B174" t="n">
-        <v>91561</v>
+        <v>91123</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E174" t="n">
-        <v>5447</v>
+        <v>5733</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Såpfingersvamp</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Ramaria lutea</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Vent.) Schild</t>
         </is>
       </c>
       <c r="I174" t="inlineStr"/>
@@ -19018,10 +19017,10 @@
         </is>
       </c>
       <c r="Q174" t="n">
-        <v>572375</v>
+        <v>572574</v>
       </c>
       <c r="R174" t="n">
-        <v>6635185</v>
+        <v>6634982</v>
       </c>
       <c r="S174" t="n">
         <v>10</v>
@@ -19062,6 +19061,7 @@
       <c r="AE174" t="b">
         <v>0</v>
       </c>
+      <c r="AF174" t="inlineStr"/>
       <c r="AG174" t="b">
         <v>0</v>
       </c>
@@ -19087,7 +19087,7 @@
         <v>129419049</v>
       </c>
       <c r="B175" t="n">
-        <v>95979</v>
+        <v>95981</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -19193,7 +19193,7 @@
         <v>129419022</v>
       </c>
       <c r="B176" t="n">
-        <v>97024</v>
+        <v>97026</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -19294,7 +19294,7 @@
         <v>129419025</v>
       </c>
       <c r="B177" t="n">
-        <v>91561</v>
+        <v>91563</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -19392,45 +19392,48 @@
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>129419030</v>
+        <v>129419062</v>
       </c>
       <c r="B178" t="n">
-        <v>91597</v>
+        <v>92021</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E178" t="n">
-        <v>1202</v>
+        <v>298</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Laxgröppa</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Meruliopsis rubicunda</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Litsch.) Spirin &amp; K.H.Larss.</t>
         </is>
       </c>
       <c r="I178" t="inlineStr"/>
+      <c r="J178" t="inlineStr"/>
+      <c r="K178" t="inlineStr"/>
+      <c r="N178" t="inlineStr"/>
       <c r="P178" t="inlineStr">
         <is>
           <t>Väst Norrby gamla tomt, Vstm</t>
         </is>
       </c>
       <c r="Q178" t="n">
-        <v>572414</v>
+        <v>572637</v>
       </c>
       <c r="R178" t="n">
-        <v>6635279</v>
+        <v>6635268</v>
       </c>
       <c r="S178" t="n">
         <v>10</v>
@@ -19471,6 +19474,7 @@
       <c r="AE178" t="b">
         <v>0</v>
       </c>
+      <c r="AF178" t="inlineStr"/>
       <c r="AG178" t="b">
         <v>0</v>
       </c>
@@ -19493,48 +19497,45 @@
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>129419062</v>
+        <v>129419030</v>
       </c>
       <c r="B179" t="n">
-        <v>92019</v>
+        <v>91599</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E179" t="n">
-        <v>298</v>
+        <v>1202</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Laxgröppa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>Meruliopsis rubicunda</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>(Litsch.) Spirin &amp; K.H.Larss.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I179" t="inlineStr"/>
-      <c r="J179" t="inlineStr"/>
-      <c r="K179" t="inlineStr"/>
-      <c r="N179" t="inlineStr"/>
       <c r="P179" t="inlineStr">
         <is>
           <t>Väst Norrby gamla tomt, Vstm</t>
         </is>
       </c>
       <c r="Q179" t="n">
-        <v>572637</v>
+        <v>572414</v>
       </c>
       <c r="R179" t="n">
-        <v>6635268</v>
+        <v>6635279</v>
       </c>
       <c r="S179" t="n">
         <v>10</v>
@@ -19575,7 +19576,6 @@
       <c r="AE179" t="b">
         <v>0</v>
       </c>
-      <c r="AF179" t="inlineStr"/>
       <c r="AG179" t="b">
         <v>0</v>
       </c>
@@ -19601,7 +19601,7 @@
         <v>129808810</v>
       </c>
       <c r="B180" t="n">
-        <v>98778</v>
+        <v>98780</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>

--- a/artfynd/A 12276-2023 artfynd.xlsx
+++ b/artfynd/A 12276-2023 artfynd.xlsx
@@ -17866,32 +17866,32 @@
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>129419063</v>
+        <v>129419052</v>
       </c>
       <c r="B163" t="n">
-        <v>91469</v>
+        <v>90981</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E163" t="n">
-        <v>3290</v>
+        <v>5685</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Gaffelskinn</t>
+          <t>Gullgröppa</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Clavulicium macounii</t>
+          <t>Pseudomerulius aureus</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>(Burt) J.Erikss. &amp; Boidin ex Parmasto</t>
+          <t>(Fr.) Jülich</t>
         </is>
       </c>
       <c r="I163" t="inlineStr"/>
@@ -17901,10 +17901,10 @@
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>572505</v>
+        <v>572365</v>
       </c>
       <c r="R163" t="n">
-        <v>6635049</v>
+        <v>6635062</v>
       </c>
       <c r="S163" t="n">
         <v>10</v>
@@ -17967,32 +17967,32 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>129419052</v>
+        <v>129419063</v>
       </c>
       <c r="B164" t="n">
-        <v>90981</v>
+        <v>91469</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E164" t="n">
-        <v>5685</v>
+        <v>3290</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Gullgröppa</t>
+          <t>Gaffelskinn</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Pseudomerulius aureus</t>
+          <t>Clavulicium macounii</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>(Fr.) Jülich</t>
+          <t>(Burt) J.Erikss. &amp; Boidin ex Parmasto</t>
         </is>
       </c>
       <c r="I164" t="inlineStr"/>
@@ -18002,10 +18002,10 @@
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>572365</v>
+        <v>572505</v>
       </c>
       <c r="R164" t="n">
-        <v>6635062</v>
+        <v>6635049</v>
       </c>
       <c r="S164" t="n">
         <v>10</v>
@@ -19392,48 +19392,45 @@
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>129419062</v>
+        <v>129419030</v>
       </c>
       <c r="B178" t="n">
-        <v>92021</v>
+        <v>91599</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E178" t="n">
-        <v>298</v>
+        <v>1202</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Laxgröppa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>Meruliopsis rubicunda</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>(Litsch.) Spirin &amp; K.H.Larss.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I178" t="inlineStr"/>
-      <c r="J178" t="inlineStr"/>
-      <c r="K178" t="inlineStr"/>
-      <c r="N178" t="inlineStr"/>
       <c r="P178" t="inlineStr">
         <is>
           <t>Väst Norrby gamla tomt, Vstm</t>
         </is>
       </c>
       <c r="Q178" t="n">
-        <v>572637</v>
+        <v>572414</v>
       </c>
       <c r="R178" t="n">
-        <v>6635268</v>
+        <v>6635279</v>
       </c>
       <c r="S178" t="n">
         <v>10</v>
@@ -19474,7 +19471,6 @@
       <c r="AE178" t="b">
         <v>0</v>
       </c>
-      <c r="AF178" t="inlineStr"/>
       <c r="AG178" t="b">
         <v>0</v>
       </c>
@@ -19497,45 +19493,48 @@
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>129419030</v>
+        <v>129419062</v>
       </c>
       <c r="B179" t="n">
-        <v>91599</v>
+        <v>92021</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E179" t="n">
-        <v>1202</v>
+        <v>298</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Laxgröppa</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Meruliopsis rubicunda</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Litsch.) Spirin &amp; K.H.Larss.</t>
         </is>
       </c>
       <c r="I179" t="inlineStr"/>
+      <c r="J179" t="inlineStr"/>
+      <c r="K179" t="inlineStr"/>
+      <c r="N179" t="inlineStr"/>
       <c r="P179" t="inlineStr">
         <is>
           <t>Väst Norrby gamla tomt, Vstm</t>
         </is>
       </c>
       <c r="Q179" t="n">
-        <v>572414</v>
+        <v>572637</v>
       </c>
       <c r="R179" t="n">
-        <v>6635279</v>
+        <v>6635268</v>
       </c>
       <c r="S179" t="n">
         <v>10</v>
@@ -19576,6 +19575,7 @@
       <c r="AE179" t="b">
         <v>0</v>
       </c>
+      <c r="AF179" t="inlineStr"/>
       <c r="AG179" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 12276-2023 artfynd.xlsx
+++ b/artfynd/A 12276-2023 artfynd.xlsx
@@ -17563,32 +17563,32 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>129419027</v>
+        <v>129419034</v>
       </c>
       <c r="B160" t="n">
-        <v>91563</v>
+        <v>91599</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E160" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I160" t="inlineStr"/>
@@ -17598,10 +17598,10 @@
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>572637</v>
+        <v>572518</v>
       </c>
       <c r="R160" t="n">
-        <v>6635268</v>
+        <v>6635088</v>
       </c>
       <c r="S160" t="n">
         <v>10</v>
@@ -17664,7 +17664,7 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>129419034</v>
+        <v>129419029</v>
       </c>
       <c r="B161" t="n">
         <v>91599</v>
@@ -17699,10 +17699,10 @@
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>572518</v>
+        <v>572434</v>
       </c>
       <c r="R161" t="n">
-        <v>6635088</v>
+        <v>6635240</v>
       </c>
       <c r="S161" t="n">
         <v>10</v>
@@ -17765,32 +17765,32 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>129419029</v>
+        <v>129419027</v>
       </c>
       <c r="B162" t="n">
-        <v>91599</v>
+        <v>91563</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E162" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I162" t="inlineStr"/>
@@ -17800,10 +17800,10 @@
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>572434</v>
+        <v>572637</v>
       </c>
       <c r="R162" t="n">
-        <v>6635240</v>
+        <v>6635268</v>
       </c>
       <c r="S162" t="n">
         <v>10</v>

--- a/artfynd/A 12276-2023 artfynd.xlsx
+++ b/artfynd/A 12276-2023 artfynd.xlsx
@@ -17563,32 +17563,32 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>129419034</v>
+        <v>129419027</v>
       </c>
       <c r="B160" t="n">
-        <v>91599</v>
+        <v>91563</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E160" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I160" t="inlineStr"/>
@@ -17598,10 +17598,10 @@
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>572518</v>
+        <v>572637</v>
       </c>
       <c r="R160" t="n">
-        <v>6635088</v>
+        <v>6635268</v>
       </c>
       <c r="S160" t="n">
         <v>10</v>
@@ -17664,7 +17664,7 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>129419029</v>
+        <v>129419034</v>
       </c>
       <c r="B161" t="n">
         <v>91599</v>
@@ -17699,10 +17699,10 @@
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>572434</v>
+        <v>572518</v>
       </c>
       <c r="R161" t="n">
-        <v>6635240</v>
+        <v>6635088</v>
       </c>
       <c r="S161" t="n">
         <v>10</v>
@@ -17765,32 +17765,32 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>129419027</v>
+        <v>129419029</v>
       </c>
       <c r="B162" t="n">
-        <v>91563</v>
+        <v>91599</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E162" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I162" t="inlineStr"/>
@@ -17800,10 +17800,10 @@
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>572637</v>
+        <v>572434</v>
       </c>
       <c r="R162" t="n">
-        <v>6635268</v>
+        <v>6635240</v>
       </c>
       <c r="S162" t="n">
         <v>10</v>
@@ -18578,10 +18578,10 @@
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>129419064</v>
+        <v>129419023</v>
       </c>
       <c r="B170" t="n">
-        <v>92249</v>
+        <v>91563</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -18589,21 +18589,21 @@
         </is>
       </c>
       <c r="E170" t="n">
-        <v>1339</v>
+        <v>5447</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I170" t="inlineStr"/>
@@ -18613,10 +18613,10 @@
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>572450</v>
+        <v>572375</v>
       </c>
       <c r="R170" t="n">
-        <v>6635232</v>
+        <v>6635185</v>
       </c>
       <c r="S170" t="n">
         <v>10</v>
@@ -18679,32 +18679,32 @@
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>129419033</v>
+        <v>129419044</v>
       </c>
       <c r="B171" t="n">
-        <v>91599</v>
+        <v>90386</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E171" t="n">
-        <v>1202</v>
+        <v>6268</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rökmusseron</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Tricholoma fucatum</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.:Fr.) P. Kumm.</t>
         </is>
       </c>
       <c r="I171" t="inlineStr"/>
@@ -18714,10 +18714,10 @@
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>572416</v>
+        <v>572651</v>
       </c>
       <c r="R171" t="n">
-        <v>6634855</v>
+        <v>6635193</v>
       </c>
       <c r="S171" t="n">
         <v>10</v>
@@ -18780,32 +18780,32 @@
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>129419023</v>
+        <v>129419043</v>
       </c>
       <c r="B172" t="n">
-        <v>91563</v>
+        <v>91123</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E172" t="n">
-        <v>5447</v>
+        <v>5733</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Såpfingersvamp</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Ramaria lutea</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Vent.) Schild</t>
         </is>
       </c>
       <c r="I172" t="inlineStr"/>
@@ -18815,10 +18815,10 @@
         </is>
       </c>
       <c r="Q172" t="n">
-        <v>572375</v>
+        <v>572574</v>
       </c>
       <c r="R172" t="n">
-        <v>6635185</v>
+        <v>6634982</v>
       </c>
       <c r="S172" t="n">
         <v>10</v>
@@ -18859,6 +18859,7 @@
       <c r="AE172" t="b">
         <v>0</v>
       </c>
+      <c r="AF172" t="inlineStr"/>
       <c r="AG172" t="b">
         <v>0</v>
       </c>
@@ -18881,10 +18882,10 @@
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>129419044</v>
+        <v>129419064</v>
       </c>
       <c r="B173" t="n">
-        <v>90386</v>
+        <v>92249</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -18892,21 +18893,21 @@
         </is>
       </c>
       <c r="E173" t="n">
-        <v>6268</v>
+        <v>1339</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Rökmusseron</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>Tricholoma fucatum</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Kumm.</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I173" t="inlineStr"/>
@@ -18916,10 +18917,10 @@
         </is>
       </c>
       <c r="Q173" t="n">
-        <v>572651</v>
+        <v>572450</v>
       </c>
       <c r="R173" t="n">
-        <v>6635193</v>
+        <v>6635232</v>
       </c>
       <c r="S173" t="n">
         <v>10</v>
@@ -18982,10 +18983,10 @@
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>129419043</v>
+        <v>129419033</v>
       </c>
       <c r="B174" t="n">
-        <v>91123</v>
+        <v>91599</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -18993,21 +18994,21 @@
         </is>
       </c>
       <c r="E174" t="n">
-        <v>5733</v>
+        <v>1202</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Såpfingersvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>Ramaria lutea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>(Vent.) Schild</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I174" t="inlineStr"/>
@@ -19017,10 +19018,10 @@
         </is>
       </c>
       <c r="Q174" t="n">
-        <v>572574</v>
+        <v>572416</v>
       </c>
       <c r="R174" t="n">
-        <v>6634982</v>
+        <v>6634855</v>
       </c>
       <c r="S174" t="n">
         <v>10</v>
@@ -19061,7 +19062,6 @@
       <c r="AE174" t="b">
         <v>0</v>
       </c>
-      <c r="AF174" t="inlineStr"/>
       <c r="AG174" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 12276-2023 artfynd.xlsx
+++ b/artfynd/A 12276-2023 artfynd.xlsx
@@ -17263,7 +17263,7 @@
         <v>129419048</v>
       </c>
       <c r="B157" t="n">
-        <v>98780</v>
+        <v>98790</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -17563,32 +17563,32 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>129419027</v>
+        <v>129419034</v>
       </c>
       <c r="B160" t="n">
-        <v>91563</v>
+        <v>91599</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E160" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I160" t="inlineStr"/>
@@ -17598,10 +17598,10 @@
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>572637</v>
+        <v>572518</v>
       </c>
       <c r="R160" t="n">
-        <v>6635268</v>
+        <v>6635088</v>
       </c>
       <c r="S160" t="n">
         <v>10</v>
@@ -17664,7 +17664,7 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>129419034</v>
+        <v>129419029</v>
       </c>
       <c r="B161" t="n">
         <v>91599</v>
@@ -17699,10 +17699,10 @@
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>572518</v>
+        <v>572434</v>
       </c>
       <c r="R161" t="n">
-        <v>6635088</v>
+        <v>6635240</v>
       </c>
       <c r="S161" t="n">
         <v>10</v>
@@ -17765,32 +17765,32 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>129419029</v>
+        <v>129419027</v>
       </c>
       <c r="B162" t="n">
-        <v>91599</v>
+        <v>91563</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E162" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I162" t="inlineStr"/>
@@ -17800,10 +17800,10 @@
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>572434</v>
+        <v>572637</v>
       </c>
       <c r="R162" t="n">
-        <v>6635240</v>
+        <v>6635268</v>
       </c>
       <c r="S162" t="n">
         <v>10</v>
@@ -17866,32 +17866,32 @@
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>129419052</v>
+        <v>129419063</v>
       </c>
       <c r="B163" t="n">
-        <v>90981</v>
+        <v>91469</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E163" t="n">
-        <v>5685</v>
+        <v>3290</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Gullgröppa</t>
+          <t>Gaffelskinn</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Pseudomerulius aureus</t>
+          <t>Clavulicium macounii</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>(Fr.) Jülich</t>
+          <t>(Burt) J.Erikss. &amp; Boidin ex Parmasto</t>
         </is>
       </c>
       <c r="I163" t="inlineStr"/>
@@ -17901,10 +17901,10 @@
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>572365</v>
+        <v>572505</v>
       </c>
       <c r="R163" t="n">
-        <v>6635062</v>
+        <v>6635049</v>
       </c>
       <c r="S163" t="n">
         <v>10</v>
@@ -17967,32 +17967,32 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>129419063</v>
+        <v>129419052</v>
       </c>
       <c r="B164" t="n">
-        <v>91469</v>
+        <v>90981</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E164" t="n">
-        <v>3290</v>
+        <v>5685</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Gaffelskinn</t>
+          <t>Gullgröppa</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Clavulicium macounii</t>
+          <t>Pseudomerulius aureus</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>(Burt) J.Erikss. &amp; Boidin ex Parmasto</t>
+          <t>(Fr.) Jülich</t>
         </is>
       </c>
       <c r="I164" t="inlineStr"/>
@@ -18002,10 +18002,10 @@
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>572505</v>
+        <v>572365</v>
       </c>
       <c r="R164" t="n">
-        <v>6635049</v>
+        <v>6635062</v>
       </c>
       <c r="S164" t="n">
         <v>10</v>
@@ -18578,10 +18578,10 @@
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>129419023</v>
+        <v>129419064</v>
       </c>
       <c r="B170" t="n">
-        <v>91563</v>
+        <v>92249</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -18589,21 +18589,21 @@
         </is>
       </c>
       <c r="E170" t="n">
-        <v>5447</v>
+        <v>1339</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I170" t="inlineStr"/>
@@ -18613,10 +18613,10 @@
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>572375</v>
+        <v>572450</v>
       </c>
       <c r="R170" t="n">
-        <v>6635185</v>
+        <v>6635232</v>
       </c>
       <c r="S170" t="n">
         <v>10</v>
@@ -18679,32 +18679,32 @@
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>129419044</v>
+        <v>129419033</v>
       </c>
       <c r="B171" t="n">
-        <v>90386</v>
+        <v>91599</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E171" t="n">
-        <v>6268</v>
+        <v>1202</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Rökmusseron</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Tricholoma fucatum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Kumm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I171" t="inlineStr"/>
@@ -18714,10 +18714,10 @@
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>572651</v>
+        <v>572416</v>
       </c>
       <c r="R171" t="n">
-        <v>6635193</v>
+        <v>6634855</v>
       </c>
       <c r="S171" t="n">
         <v>10</v>
@@ -18780,32 +18780,32 @@
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>129419043</v>
+        <v>129419044</v>
       </c>
       <c r="B172" t="n">
-        <v>91123</v>
+        <v>90386</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E172" t="n">
-        <v>5733</v>
+        <v>6268</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Såpfingersvamp</t>
+          <t>Rökmusseron</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>Ramaria lutea</t>
+          <t>Tricholoma fucatum</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>(Vent.) Schild</t>
+          <t>(Fr.:Fr.) P. Kumm.</t>
         </is>
       </c>
       <c r="I172" t="inlineStr"/>
@@ -18815,10 +18815,10 @@
         </is>
       </c>
       <c r="Q172" t="n">
-        <v>572574</v>
+        <v>572651</v>
       </c>
       <c r="R172" t="n">
-        <v>6634982</v>
+        <v>6635193</v>
       </c>
       <c r="S172" t="n">
         <v>10</v>
@@ -18859,7 +18859,6 @@
       <c r="AE172" t="b">
         <v>0</v>
       </c>
-      <c r="AF172" t="inlineStr"/>
       <c r="AG172" t="b">
         <v>0</v>
       </c>
@@ -18882,32 +18881,32 @@
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>129419064</v>
+        <v>129419043</v>
       </c>
       <c r="B173" t="n">
-        <v>92249</v>
+        <v>91123</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E173" t="n">
-        <v>1339</v>
+        <v>5733</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Såpfingersvamp</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Ramaria lutea</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>(Vent.) Schild</t>
         </is>
       </c>
       <c r="I173" t="inlineStr"/>
@@ -18917,10 +18916,10 @@
         </is>
       </c>
       <c r="Q173" t="n">
-        <v>572450</v>
+        <v>572574</v>
       </c>
       <c r="R173" t="n">
-        <v>6635232</v>
+        <v>6634982</v>
       </c>
       <c r="S173" t="n">
         <v>10</v>
@@ -18961,6 +18960,7 @@
       <c r="AE173" t="b">
         <v>0</v>
       </c>
+      <c r="AF173" t="inlineStr"/>
       <c r="AG173" t="b">
         <v>0</v>
       </c>
@@ -18983,32 +18983,32 @@
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>129419033</v>
+        <v>129419023</v>
       </c>
       <c r="B174" t="n">
-        <v>91599</v>
+        <v>91563</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E174" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I174" t="inlineStr"/>
@@ -19018,10 +19018,10 @@
         </is>
       </c>
       <c r="Q174" t="n">
-        <v>572416</v>
+        <v>572375</v>
       </c>
       <c r="R174" t="n">
-        <v>6634855</v>
+        <v>6635185</v>
       </c>
       <c r="S174" t="n">
         <v>10</v>
@@ -19087,7 +19087,7 @@
         <v>129419049</v>
       </c>
       <c r="B175" t="n">
-        <v>95981</v>
+        <v>95991</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -19193,7 +19193,7 @@
         <v>129419022</v>
       </c>
       <c r="B176" t="n">
-        <v>97026</v>
+        <v>97036</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -19601,7 +19601,7 @@
         <v>129808810</v>
       </c>
       <c r="B180" t="n">
-        <v>98780</v>
+        <v>98790</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>

--- a/artfynd/A 12276-2023 artfynd.xlsx
+++ b/artfynd/A 12276-2023 artfynd.xlsx
@@ -17866,32 +17866,32 @@
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>129419063</v>
+        <v>129419052</v>
       </c>
       <c r="B163" t="n">
-        <v>91469</v>
+        <v>90981</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E163" t="n">
-        <v>3290</v>
+        <v>5685</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Gaffelskinn</t>
+          <t>Gullgröppa</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Clavulicium macounii</t>
+          <t>Pseudomerulius aureus</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>(Burt) J.Erikss. &amp; Boidin ex Parmasto</t>
+          <t>(Fr.) Jülich</t>
         </is>
       </c>
       <c r="I163" t="inlineStr"/>
@@ -17901,10 +17901,10 @@
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>572505</v>
+        <v>572365</v>
       </c>
       <c r="R163" t="n">
-        <v>6635049</v>
+        <v>6635062</v>
       </c>
       <c r="S163" t="n">
         <v>10</v>
@@ -17967,32 +17967,32 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>129419052</v>
+        <v>129419063</v>
       </c>
       <c r="B164" t="n">
-        <v>90981</v>
+        <v>91469</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E164" t="n">
-        <v>5685</v>
+        <v>3290</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Gullgröppa</t>
+          <t>Gaffelskinn</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Pseudomerulius aureus</t>
+          <t>Clavulicium macounii</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>(Fr.) Jülich</t>
+          <t>(Burt) J.Erikss. &amp; Boidin ex Parmasto</t>
         </is>
       </c>
       <c r="I164" t="inlineStr"/>
@@ -18002,10 +18002,10 @@
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>572365</v>
+        <v>572505</v>
       </c>
       <c r="R164" t="n">
-        <v>6635062</v>
+        <v>6635049</v>
       </c>
       <c r="S164" t="n">
         <v>10</v>
@@ -19601,7 +19601,7 @@
         <v>129808810</v>
       </c>
       <c r="B180" t="n">
-        <v>98790</v>
+        <v>98794</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>

--- a/artfynd/A 12276-2023 artfynd.xlsx
+++ b/artfynd/A 12276-2023 artfynd.xlsx
@@ -17061,7 +17061,7 @@
         <v>129419047</v>
       </c>
       <c r="B155" t="n">
-        <v>92873</v>
+        <v>92876</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -17162,7 +17162,7 @@
         <v>129419026</v>
       </c>
       <c r="B156" t="n">
-        <v>91563</v>
+        <v>91566</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -17263,7 +17263,7 @@
         <v>129419048</v>
       </c>
       <c r="B157" t="n">
-        <v>98790</v>
+        <v>98794</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -17364,7 +17364,7 @@
         <v>129419028</v>
       </c>
       <c r="B158" t="n">
-        <v>91599</v>
+        <v>91602</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -17465,7 +17465,7 @@
         <v>129419032</v>
       </c>
       <c r="B159" t="n">
-        <v>91599</v>
+        <v>91602</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -17566,7 +17566,7 @@
         <v>129419034</v>
       </c>
       <c r="B160" t="n">
-        <v>91599</v>
+        <v>91602</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -17667,7 +17667,7 @@
         <v>129419029</v>
       </c>
       <c r="B161" t="n">
-        <v>91599</v>
+        <v>91602</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -17768,7 +17768,7 @@
         <v>129419027</v>
       </c>
       <c r="B162" t="n">
-        <v>91563</v>
+        <v>91566</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -17869,7 +17869,7 @@
         <v>129419052</v>
       </c>
       <c r="B163" t="n">
-        <v>90981</v>
+        <v>90984</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -17970,7 +17970,7 @@
         <v>129419063</v>
       </c>
       <c r="B164" t="n">
-        <v>91469</v>
+        <v>91472</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -18071,7 +18071,7 @@
         <v>129419035</v>
       </c>
       <c r="B165" t="n">
-        <v>91599</v>
+        <v>91602</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -18172,7 +18172,7 @@
         <v>129419024</v>
       </c>
       <c r="B166" t="n">
-        <v>91563</v>
+        <v>91566</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -18273,7 +18273,7 @@
         <v>129419031</v>
       </c>
       <c r="B167" t="n">
-        <v>91599</v>
+        <v>91602</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -18374,7 +18374,7 @@
         <v>129419041</v>
       </c>
       <c r="B168" t="n">
-        <v>92521</v>
+        <v>92524</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -18480,7 +18480,7 @@
         <v>129419036</v>
       </c>
       <c r="B169" t="n">
-        <v>90435</v>
+        <v>90438</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -18578,10 +18578,10 @@
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>129419064</v>
+        <v>129419044</v>
       </c>
       <c r="B170" t="n">
-        <v>92249</v>
+        <v>90389</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -18589,21 +18589,21 @@
         </is>
       </c>
       <c r="E170" t="n">
-        <v>1339</v>
+        <v>6268</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Rökmusseron</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Tricholoma fucatum</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>(Fr.:Fr.) P. Kumm.</t>
         </is>
       </c>
       <c r="I170" t="inlineStr"/>
@@ -18613,10 +18613,10 @@
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>572450</v>
+        <v>572651</v>
       </c>
       <c r="R170" t="n">
-        <v>6635232</v>
+        <v>6635193</v>
       </c>
       <c r="S170" t="n">
         <v>10</v>
@@ -18679,10 +18679,10 @@
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>129419033</v>
+        <v>129419043</v>
       </c>
       <c r="B171" t="n">
-        <v>91599</v>
+        <v>91126</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -18690,21 +18690,21 @@
         </is>
       </c>
       <c r="E171" t="n">
-        <v>1202</v>
+        <v>5733</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Såpfingersvamp</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Ramaria lutea</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Vent.) Schild</t>
         </is>
       </c>
       <c r="I171" t="inlineStr"/>
@@ -18714,10 +18714,10 @@
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>572416</v>
+        <v>572574</v>
       </c>
       <c r="R171" t="n">
-        <v>6634855</v>
+        <v>6634982</v>
       </c>
       <c r="S171" t="n">
         <v>10</v>
@@ -18758,6 +18758,7 @@
       <c r="AE171" t="b">
         <v>0</v>
       </c>
+      <c r="AF171" t="inlineStr"/>
       <c r="AG171" t="b">
         <v>0</v>
       </c>
@@ -18780,10 +18781,10 @@
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>129419044</v>
+        <v>129419064</v>
       </c>
       <c r="B172" t="n">
-        <v>90386</v>
+        <v>92252</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -18791,21 +18792,21 @@
         </is>
       </c>
       <c r="E172" t="n">
-        <v>6268</v>
+        <v>1339</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Rökmusseron</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>Tricholoma fucatum</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Kumm.</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I172" t="inlineStr"/>
@@ -18815,10 +18816,10 @@
         </is>
       </c>
       <c r="Q172" t="n">
-        <v>572651</v>
+        <v>572450</v>
       </c>
       <c r="R172" t="n">
-        <v>6635193</v>
+        <v>6635232</v>
       </c>
       <c r="S172" t="n">
         <v>10</v>
@@ -18881,10 +18882,10 @@
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>129419043</v>
+        <v>129419033</v>
       </c>
       <c r="B173" t="n">
-        <v>91123</v>
+        <v>91602</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -18892,21 +18893,21 @@
         </is>
       </c>
       <c r="E173" t="n">
-        <v>5733</v>
+        <v>1202</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Såpfingersvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>Ramaria lutea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>(Vent.) Schild</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I173" t="inlineStr"/>
@@ -18916,10 +18917,10 @@
         </is>
       </c>
       <c r="Q173" t="n">
-        <v>572574</v>
+        <v>572416</v>
       </c>
       <c r="R173" t="n">
-        <v>6634982</v>
+        <v>6634855</v>
       </c>
       <c r="S173" t="n">
         <v>10</v>
@@ -18960,7 +18961,6 @@
       <c r="AE173" t="b">
         <v>0</v>
       </c>
-      <c r="AF173" t="inlineStr"/>
       <c r="AG173" t="b">
         <v>0</v>
       </c>
@@ -18986,7 +18986,7 @@
         <v>129419023</v>
       </c>
       <c r="B174" t="n">
-        <v>91563</v>
+        <v>91566</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -19087,7 +19087,7 @@
         <v>129419049</v>
       </c>
       <c r="B175" t="n">
-        <v>95991</v>
+        <v>95995</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -19193,7 +19193,7 @@
         <v>129419022</v>
       </c>
       <c r="B176" t="n">
-        <v>97036</v>
+        <v>97040</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -19294,7 +19294,7 @@
         <v>129419025</v>
       </c>
       <c r="B177" t="n">
-        <v>91563</v>
+        <v>91566</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -19395,7 +19395,7 @@
         <v>129419030</v>
       </c>
       <c r="B178" t="n">
-        <v>91599</v>
+        <v>91602</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -19496,7 +19496,7 @@
         <v>129419062</v>
       </c>
       <c r="B179" t="n">
-        <v>92021</v>
+        <v>92024</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>

--- a/artfynd/A 12276-2023 artfynd.xlsx
+++ b/artfynd/A 12276-2023 artfynd.xlsx
@@ -17563,32 +17563,32 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>129419034</v>
+        <v>129419027</v>
       </c>
       <c r="B160" t="n">
-        <v>91602</v>
+        <v>91566</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E160" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I160" t="inlineStr"/>
@@ -17598,10 +17598,10 @@
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>572518</v>
+        <v>572637</v>
       </c>
       <c r="R160" t="n">
-        <v>6635088</v>
+        <v>6635268</v>
       </c>
       <c r="S160" t="n">
         <v>10</v>
@@ -17664,7 +17664,7 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>129419029</v>
+        <v>129419034</v>
       </c>
       <c r="B161" t="n">
         <v>91602</v>
@@ -17699,10 +17699,10 @@
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>572434</v>
+        <v>572518</v>
       </c>
       <c r="R161" t="n">
-        <v>6635240</v>
+        <v>6635088</v>
       </c>
       <c r="S161" t="n">
         <v>10</v>
@@ -17765,32 +17765,32 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>129419027</v>
+        <v>129419029</v>
       </c>
       <c r="B162" t="n">
-        <v>91566</v>
+        <v>91602</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E162" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I162" t="inlineStr"/>
@@ -17800,10 +17800,10 @@
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>572637</v>
+        <v>572434</v>
       </c>
       <c r="R162" t="n">
-        <v>6635268</v>
+        <v>6635240</v>
       </c>
       <c r="S162" t="n">
         <v>10</v>
@@ -19392,45 +19392,48 @@
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>129419030</v>
+        <v>129419062</v>
       </c>
       <c r="B178" t="n">
-        <v>91602</v>
+        <v>92024</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E178" t="n">
-        <v>1202</v>
+        <v>298</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Laxgröppa</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Meruliopsis rubicunda</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Litsch.) Spirin &amp; K.H.Larss.</t>
         </is>
       </c>
       <c r="I178" t="inlineStr"/>
+      <c r="J178" t="inlineStr"/>
+      <c r="K178" t="inlineStr"/>
+      <c r="N178" t="inlineStr"/>
       <c r="P178" t="inlineStr">
         <is>
           <t>Väst Norrby gamla tomt, Vstm</t>
         </is>
       </c>
       <c r="Q178" t="n">
-        <v>572414</v>
+        <v>572637</v>
       </c>
       <c r="R178" t="n">
-        <v>6635279</v>
+        <v>6635268</v>
       </c>
       <c r="S178" t="n">
         <v>10</v>
@@ -19471,6 +19474,7 @@
       <c r="AE178" t="b">
         <v>0</v>
       </c>
+      <c r="AF178" t="inlineStr"/>
       <c r="AG178" t="b">
         <v>0</v>
       </c>
@@ -19493,48 +19497,45 @@
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>129419062</v>
+        <v>129419030</v>
       </c>
       <c r="B179" t="n">
-        <v>92024</v>
+        <v>91602</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E179" t="n">
-        <v>298</v>
+        <v>1202</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Laxgröppa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>Meruliopsis rubicunda</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>(Litsch.) Spirin &amp; K.H.Larss.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I179" t="inlineStr"/>
-      <c r="J179" t="inlineStr"/>
-      <c r="K179" t="inlineStr"/>
-      <c r="N179" t="inlineStr"/>
       <c r="P179" t="inlineStr">
         <is>
           <t>Väst Norrby gamla tomt, Vstm</t>
         </is>
       </c>
       <c r="Q179" t="n">
-        <v>572637</v>
+        <v>572414</v>
       </c>
       <c r="R179" t="n">
-        <v>6635268</v>
+        <v>6635279</v>
       </c>
       <c r="S179" t="n">
         <v>10</v>
@@ -19575,7 +19576,6 @@
       <c r="AE179" t="b">
         <v>0</v>
       </c>
-      <c r="AF179" t="inlineStr"/>
       <c r="AG179" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 12276-2023 artfynd.xlsx
+++ b/artfynd/A 12276-2023 artfynd.xlsx
@@ -17061,7 +17061,7 @@
         <v>129419047</v>
       </c>
       <c r="B155" t="n">
-        <v>92876</v>
+        <v>92879</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -17162,7 +17162,7 @@
         <v>129419026</v>
       </c>
       <c r="B156" t="n">
-        <v>91566</v>
+        <v>91569</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -17263,7 +17263,7 @@
         <v>129419048</v>
       </c>
       <c r="B157" t="n">
-        <v>98794</v>
+        <v>98797</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -17364,7 +17364,7 @@
         <v>129419028</v>
       </c>
       <c r="B158" t="n">
-        <v>91602</v>
+        <v>91605</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -17465,7 +17465,7 @@
         <v>129419032</v>
       </c>
       <c r="B159" t="n">
-        <v>91602</v>
+        <v>91605</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -17563,32 +17563,32 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>129419027</v>
+        <v>129419034</v>
       </c>
       <c r="B160" t="n">
-        <v>91566</v>
+        <v>91605</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E160" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I160" t="inlineStr"/>
@@ -17598,10 +17598,10 @@
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>572637</v>
+        <v>572518</v>
       </c>
       <c r="R160" t="n">
-        <v>6635268</v>
+        <v>6635088</v>
       </c>
       <c r="S160" t="n">
         <v>10</v>
@@ -17664,10 +17664,10 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>129419034</v>
+        <v>129419029</v>
       </c>
       <c r="B161" t="n">
-        <v>91602</v>
+        <v>91605</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -17699,10 +17699,10 @@
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>572518</v>
+        <v>572434</v>
       </c>
       <c r="R161" t="n">
-        <v>6635088</v>
+        <v>6635240</v>
       </c>
       <c r="S161" t="n">
         <v>10</v>
@@ -17765,32 +17765,32 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>129419029</v>
+        <v>129419027</v>
       </c>
       <c r="B162" t="n">
-        <v>91602</v>
+        <v>91569</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E162" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I162" t="inlineStr"/>
@@ -17800,10 +17800,10 @@
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>572434</v>
+        <v>572637</v>
       </c>
       <c r="R162" t="n">
-        <v>6635240</v>
+        <v>6635268</v>
       </c>
       <c r="S162" t="n">
         <v>10</v>
@@ -17869,7 +17869,7 @@
         <v>129419052</v>
       </c>
       <c r="B163" t="n">
-        <v>90984</v>
+        <v>90987</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -17970,7 +17970,7 @@
         <v>129419063</v>
       </c>
       <c r="B164" t="n">
-        <v>91472</v>
+        <v>91475</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -18071,7 +18071,7 @@
         <v>129419035</v>
       </c>
       <c r="B165" t="n">
-        <v>91602</v>
+        <v>91605</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -18172,7 +18172,7 @@
         <v>129419024</v>
       </c>
       <c r="B166" t="n">
-        <v>91566</v>
+        <v>91569</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -18273,7 +18273,7 @@
         <v>129419031</v>
       </c>
       <c r="B167" t="n">
-        <v>91602</v>
+        <v>91605</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -18374,7 +18374,7 @@
         <v>129419041</v>
       </c>
       <c r="B168" t="n">
-        <v>92524</v>
+        <v>92527</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -18480,7 +18480,7 @@
         <v>129419036</v>
       </c>
       <c r="B169" t="n">
-        <v>90438</v>
+        <v>90441</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -18578,32 +18578,32 @@
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>129419044</v>
+        <v>129419033</v>
       </c>
       <c r="B170" t="n">
-        <v>90389</v>
+        <v>91605</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E170" t="n">
-        <v>6268</v>
+        <v>1202</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Rökmusseron</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Tricholoma fucatum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Kumm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I170" t="inlineStr"/>
@@ -18613,10 +18613,10 @@
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>572651</v>
+        <v>572416</v>
       </c>
       <c r="R170" t="n">
-        <v>6635193</v>
+        <v>6634855</v>
       </c>
       <c r="S170" t="n">
         <v>10</v>
@@ -18682,7 +18682,7 @@
         <v>129419043</v>
       </c>
       <c r="B171" t="n">
-        <v>91126</v>
+        <v>91129</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -18781,10 +18781,10 @@
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>129419064</v>
+        <v>129419023</v>
       </c>
       <c r="B172" t="n">
-        <v>92252</v>
+        <v>91569</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -18792,21 +18792,21 @@
         </is>
       </c>
       <c r="E172" t="n">
-        <v>1339</v>
+        <v>5447</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I172" t="inlineStr"/>
@@ -18816,10 +18816,10 @@
         </is>
       </c>
       <c r="Q172" t="n">
-        <v>572450</v>
+        <v>572375</v>
       </c>
       <c r="R172" t="n">
-        <v>6635232</v>
+        <v>6635185</v>
       </c>
       <c r="S172" t="n">
         <v>10</v>
@@ -18882,32 +18882,32 @@
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>129419033</v>
+        <v>129419044</v>
       </c>
       <c r="B173" t="n">
-        <v>91602</v>
+        <v>90392</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E173" t="n">
-        <v>1202</v>
+        <v>6268</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rökmusseron</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Tricholoma fucatum</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.:Fr.) P. Kumm.</t>
         </is>
       </c>
       <c r="I173" t="inlineStr"/>
@@ -18917,10 +18917,10 @@
         </is>
       </c>
       <c r="Q173" t="n">
-        <v>572416</v>
+        <v>572651</v>
       </c>
       <c r="R173" t="n">
-        <v>6634855</v>
+        <v>6635193</v>
       </c>
       <c r="S173" t="n">
         <v>10</v>
@@ -18983,10 +18983,10 @@
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>129419023</v>
+        <v>129419064</v>
       </c>
       <c r="B174" t="n">
-        <v>91566</v>
+        <v>92255</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -18994,21 +18994,21 @@
         </is>
       </c>
       <c r="E174" t="n">
-        <v>5447</v>
+        <v>1339</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I174" t="inlineStr"/>
@@ -19018,10 +19018,10 @@
         </is>
       </c>
       <c r="Q174" t="n">
-        <v>572375</v>
+        <v>572450</v>
       </c>
       <c r="R174" t="n">
-        <v>6635185</v>
+        <v>6635232</v>
       </c>
       <c r="S174" t="n">
         <v>10</v>
@@ -19087,7 +19087,7 @@
         <v>129419049</v>
       </c>
       <c r="B175" t="n">
-        <v>95995</v>
+        <v>95998</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -19190,32 +19190,32 @@
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>129419022</v>
+        <v>129419025</v>
       </c>
       <c r="B176" t="n">
-        <v>97040</v>
+        <v>91569</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E176" t="n">
-        <v>53</v>
+        <v>5447</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I176" t="inlineStr"/>
@@ -19225,10 +19225,10 @@
         </is>
       </c>
       <c r="Q176" t="n">
-        <v>572437</v>
+        <v>572492</v>
       </c>
       <c r="R176" t="n">
-        <v>6634991</v>
+        <v>6634998</v>
       </c>
       <c r="S176" t="n">
         <v>10</v>
@@ -19291,32 +19291,32 @@
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>129419025</v>
+        <v>129419022</v>
       </c>
       <c r="B177" t="n">
-        <v>91566</v>
+        <v>97043</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E177" t="n">
-        <v>5447</v>
+        <v>53</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I177" t="inlineStr"/>
@@ -19326,10 +19326,10 @@
         </is>
       </c>
       <c r="Q177" t="n">
-        <v>572492</v>
+        <v>572437</v>
       </c>
       <c r="R177" t="n">
-        <v>6634998</v>
+        <v>6634991</v>
       </c>
       <c r="S177" t="n">
         <v>10</v>
@@ -19392,48 +19392,45 @@
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>129419062</v>
+        <v>129419030</v>
       </c>
       <c r="B178" t="n">
-        <v>92024</v>
+        <v>91605</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E178" t="n">
-        <v>298</v>
+        <v>1202</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Laxgröppa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>Meruliopsis rubicunda</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>(Litsch.) Spirin &amp; K.H.Larss.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I178" t="inlineStr"/>
-      <c r="J178" t="inlineStr"/>
-      <c r="K178" t="inlineStr"/>
-      <c r="N178" t="inlineStr"/>
       <c r="P178" t="inlineStr">
         <is>
           <t>Väst Norrby gamla tomt, Vstm</t>
         </is>
       </c>
       <c r="Q178" t="n">
-        <v>572637</v>
+        <v>572414</v>
       </c>
       <c r="R178" t="n">
-        <v>6635268</v>
+        <v>6635279</v>
       </c>
       <c r="S178" t="n">
         <v>10</v>
@@ -19474,7 +19471,6 @@
       <c r="AE178" t="b">
         <v>0</v>
       </c>
-      <c r="AF178" t="inlineStr"/>
       <c r="AG178" t="b">
         <v>0</v>
       </c>
@@ -19497,45 +19493,48 @@
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>129419030</v>
+        <v>129419062</v>
       </c>
       <c r="B179" t="n">
-        <v>91602</v>
+        <v>92027</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E179" t="n">
-        <v>1202</v>
+        <v>298</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Laxgröppa</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Meruliopsis rubicunda</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Litsch.) Spirin &amp; K.H.Larss.</t>
         </is>
       </c>
       <c r="I179" t="inlineStr"/>
+      <c r="J179" t="inlineStr"/>
+      <c r="K179" t="inlineStr"/>
+      <c r="N179" t="inlineStr"/>
       <c r="P179" t="inlineStr">
         <is>
           <t>Väst Norrby gamla tomt, Vstm</t>
         </is>
       </c>
       <c r="Q179" t="n">
-        <v>572414</v>
+        <v>572637</v>
       </c>
       <c r="R179" t="n">
-        <v>6635279</v>
+        <v>6635268</v>
       </c>
       <c r="S179" t="n">
         <v>10</v>
@@ -19576,6 +19575,7 @@
       <c r="AE179" t="b">
         <v>0</v>
       </c>
+      <c r="AF179" t="inlineStr"/>
       <c r="AG179" t="b">
         <v>0</v>
       </c>
@@ -19601,7 +19601,7 @@
         <v>129808810</v>
       </c>
       <c r="B180" t="n">
-        <v>98794</v>
+        <v>98797</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>

--- a/artfynd/A 12276-2023 artfynd.xlsx
+++ b/artfynd/A 12276-2023 artfynd.xlsx
@@ -19190,32 +19190,32 @@
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>129419025</v>
+        <v>129419022</v>
       </c>
       <c r="B176" t="n">
-        <v>91569</v>
+        <v>97043</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E176" t="n">
-        <v>5447</v>
+        <v>53</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I176" t="inlineStr"/>
@@ -19225,10 +19225,10 @@
         </is>
       </c>
       <c r="Q176" t="n">
-        <v>572492</v>
+        <v>572437</v>
       </c>
       <c r="R176" t="n">
-        <v>6634998</v>
+        <v>6634991</v>
       </c>
       <c r="S176" t="n">
         <v>10</v>
@@ -19291,32 +19291,32 @@
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>129419022</v>
+        <v>129419025</v>
       </c>
       <c r="B177" t="n">
-        <v>97043</v>
+        <v>91569</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E177" t="n">
-        <v>53</v>
+        <v>5447</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I177" t="inlineStr"/>
@@ -19326,10 +19326,10 @@
         </is>
       </c>
       <c r="Q177" t="n">
-        <v>572437</v>
+        <v>572492</v>
       </c>
       <c r="R177" t="n">
-        <v>6634991</v>
+        <v>6634998</v>
       </c>
       <c r="S177" t="n">
         <v>10</v>
@@ -19392,45 +19392,48 @@
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>129419030</v>
+        <v>129419062</v>
       </c>
       <c r="B178" t="n">
-        <v>91605</v>
+        <v>92027</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E178" t="n">
-        <v>1202</v>
+        <v>298</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Laxgröppa</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Meruliopsis rubicunda</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Litsch.) Spirin &amp; K.H.Larss.</t>
         </is>
       </c>
       <c r="I178" t="inlineStr"/>
+      <c r="J178" t="inlineStr"/>
+      <c r="K178" t="inlineStr"/>
+      <c r="N178" t="inlineStr"/>
       <c r="P178" t="inlineStr">
         <is>
           <t>Väst Norrby gamla tomt, Vstm</t>
         </is>
       </c>
       <c r="Q178" t="n">
-        <v>572414</v>
+        <v>572637</v>
       </c>
       <c r="R178" t="n">
-        <v>6635279</v>
+        <v>6635268</v>
       </c>
       <c r="S178" t="n">
         <v>10</v>
@@ -19471,6 +19474,7 @@
       <c r="AE178" t="b">
         <v>0</v>
       </c>
+      <c r="AF178" t="inlineStr"/>
       <c r="AG178" t="b">
         <v>0</v>
       </c>
@@ -19493,48 +19497,45 @@
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>129419062</v>
+        <v>129419030</v>
       </c>
       <c r="B179" t="n">
-        <v>92027</v>
+        <v>91605</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E179" t="n">
-        <v>298</v>
+        <v>1202</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Laxgröppa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>Meruliopsis rubicunda</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>(Litsch.) Spirin &amp; K.H.Larss.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I179" t="inlineStr"/>
-      <c r="J179" t="inlineStr"/>
-      <c r="K179" t="inlineStr"/>
-      <c r="N179" t="inlineStr"/>
       <c r="P179" t="inlineStr">
         <is>
           <t>Väst Norrby gamla tomt, Vstm</t>
         </is>
       </c>
       <c r="Q179" t="n">
-        <v>572637</v>
+        <v>572414</v>
       </c>
       <c r="R179" t="n">
-        <v>6635268</v>
+        <v>6635279</v>
       </c>
       <c r="S179" t="n">
         <v>10</v>
@@ -19575,7 +19576,6 @@
       <c r="AE179" t="b">
         <v>0</v>
       </c>
-      <c r="AF179" t="inlineStr"/>
       <c r="AG179" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 12276-2023 artfynd.xlsx
+++ b/artfynd/A 12276-2023 artfynd.xlsx
@@ -17061,7 +17061,7 @@
         <v>129419047</v>
       </c>
       <c r="B155" t="n">
-        <v>92879</v>
+        <v>92880</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -17162,7 +17162,7 @@
         <v>129419026</v>
       </c>
       <c r="B156" t="n">
-        <v>91569</v>
+        <v>91570</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -17263,7 +17263,7 @@
         <v>129419048</v>
       </c>
       <c r="B157" t="n">
-        <v>98797</v>
+        <v>98798</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -17364,7 +17364,7 @@
         <v>129419028</v>
       </c>
       <c r="B158" t="n">
-        <v>91605</v>
+        <v>91606</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -17465,7 +17465,7 @@
         <v>129419032</v>
       </c>
       <c r="B159" t="n">
-        <v>91605</v>
+        <v>91606</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -17563,10 +17563,10 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>129419034</v>
+        <v>129419029</v>
       </c>
       <c r="B160" t="n">
-        <v>91605</v>
+        <v>91606</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -17598,10 +17598,10 @@
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>572518</v>
+        <v>572434</v>
       </c>
       <c r="R160" t="n">
-        <v>6635088</v>
+        <v>6635240</v>
       </c>
       <c r="S160" t="n">
         <v>10</v>
@@ -17664,10 +17664,10 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>129419029</v>
+        <v>129419034</v>
       </c>
       <c r="B161" t="n">
-        <v>91605</v>
+        <v>91606</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -17699,10 +17699,10 @@
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>572434</v>
+        <v>572518</v>
       </c>
       <c r="R161" t="n">
-        <v>6635240</v>
+        <v>6635088</v>
       </c>
       <c r="S161" t="n">
         <v>10</v>
@@ -17768,7 +17768,7 @@
         <v>129419027</v>
       </c>
       <c r="B162" t="n">
-        <v>91569</v>
+        <v>91570</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -17869,7 +17869,7 @@
         <v>129419052</v>
       </c>
       <c r="B163" t="n">
-        <v>90987</v>
+        <v>90988</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -17970,7 +17970,7 @@
         <v>129419063</v>
       </c>
       <c r="B164" t="n">
-        <v>91475</v>
+        <v>91476</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -18071,7 +18071,7 @@
         <v>129419035</v>
       </c>
       <c r="B165" t="n">
-        <v>91605</v>
+        <v>91606</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -18172,7 +18172,7 @@
         <v>129419024</v>
       </c>
       <c r="B166" t="n">
-        <v>91569</v>
+        <v>91570</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -18273,7 +18273,7 @@
         <v>129419031</v>
       </c>
       <c r="B167" t="n">
-        <v>91605</v>
+        <v>91606</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -18374,7 +18374,7 @@
         <v>129419041</v>
       </c>
       <c r="B168" t="n">
-        <v>92527</v>
+        <v>92528</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -18480,7 +18480,7 @@
         <v>129419036</v>
       </c>
       <c r="B169" t="n">
-        <v>90441</v>
+        <v>90442</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -18581,7 +18581,7 @@
         <v>129419033</v>
       </c>
       <c r="B170" t="n">
-        <v>91605</v>
+        <v>91606</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -18679,32 +18679,32 @@
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>129419043</v>
+        <v>129419044</v>
       </c>
       <c r="B171" t="n">
-        <v>91129</v>
+        <v>90393</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E171" t="n">
-        <v>5733</v>
+        <v>6268</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Såpfingersvamp</t>
+          <t>Rökmusseron</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Ramaria lutea</t>
+          <t>Tricholoma fucatum</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>(Vent.) Schild</t>
+          <t>(Fr.:Fr.) P. Kumm.</t>
         </is>
       </c>
       <c r="I171" t="inlineStr"/>
@@ -18714,10 +18714,10 @@
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>572574</v>
+        <v>572651</v>
       </c>
       <c r="R171" t="n">
-        <v>6634982</v>
+        <v>6635193</v>
       </c>
       <c r="S171" t="n">
         <v>10</v>
@@ -18758,7 +18758,6 @@
       <c r="AE171" t="b">
         <v>0</v>
       </c>
-      <c r="AF171" t="inlineStr"/>
       <c r="AG171" t="b">
         <v>0</v>
       </c>
@@ -18781,32 +18780,32 @@
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>129419023</v>
+        <v>129419043</v>
       </c>
       <c r="B172" t="n">
-        <v>91569</v>
+        <v>91130</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E172" t="n">
-        <v>5447</v>
+        <v>5733</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Såpfingersvamp</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Ramaria lutea</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Vent.) Schild</t>
         </is>
       </c>
       <c r="I172" t="inlineStr"/>
@@ -18816,10 +18815,10 @@
         </is>
       </c>
       <c r="Q172" t="n">
-        <v>572375</v>
+        <v>572574</v>
       </c>
       <c r="R172" t="n">
-        <v>6635185</v>
+        <v>6634982</v>
       </c>
       <c r="S172" t="n">
         <v>10</v>
@@ -18860,6 +18859,7 @@
       <c r="AE172" t="b">
         <v>0</v>
       </c>
+      <c r="AF172" t="inlineStr"/>
       <c r="AG172" t="b">
         <v>0</v>
       </c>
@@ -18882,10 +18882,10 @@
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>129419044</v>
+        <v>129419023</v>
       </c>
       <c r="B173" t="n">
-        <v>90392</v>
+        <v>91570</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -18893,21 +18893,21 @@
         </is>
       </c>
       <c r="E173" t="n">
-        <v>6268</v>
+        <v>5447</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Rökmusseron</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>Tricholoma fucatum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Kumm.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I173" t="inlineStr"/>
@@ -18917,10 +18917,10 @@
         </is>
       </c>
       <c r="Q173" t="n">
-        <v>572651</v>
+        <v>572375</v>
       </c>
       <c r="R173" t="n">
-        <v>6635193</v>
+        <v>6635185</v>
       </c>
       <c r="S173" t="n">
         <v>10</v>
@@ -18986,7 +18986,7 @@
         <v>129419064</v>
       </c>
       <c r="B174" t="n">
-        <v>92255</v>
+        <v>92256</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -19087,7 +19087,7 @@
         <v>129419049</v>
       </c>
       <c r="B175" t="n">
-        <v>95998</v>
+        <v>95999</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -19193,7 +19193,7 @@
         <v>129419022</v>
       </c>
       <c r="B176" t="n">
-        <v>97043</v>
+        <v>97044</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -19294,7 +19294,7 @@
         <v>129419025</v>
       </c>
       <c r="B177" t="n">
-        <v>91569</v>
+        <v>91570</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -19392,48 +19392,45 @@
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>129419062</v>
+        <v>129419030</v>
       </c>
       <c r="B178" t="n">
-        <v>92027</v>
+        <v>91606</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E178" t="n">
-        <v>298</v>
+        <v>1202</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Laxgröppa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>Meruliopsis rubicunda</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>(Litsch.) Spirin &amp; K.H.Larss.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I178" t="inlineStr"/>
-      <c r="J178" t="inlineStr"/>
-      <c r="K178" t="inlineStr"/>
-      <c r="N178" t="inlineStr"/>
       <c r="P178" t="inlineStr">
         <is>
           <t>Väst Norrby gamla tomt, Vstm</t>
         </is>
       </c>
       <c r="Q178" t="n">
-        <v>572637</v>
+        <v>572414</v>
       </c>
       <c r="R178" t="n">
-        <v>6635268</v>
+        <v>6635279</v>
       </c>
       <c r="S178" t="n">
         <v>10</v>
@@ -19474,7 +19471,6 @@
       <c r="AE178" t="b">
         <v>0</v>
       </c>
-      <c r="AF178" t="inlineStr"/>
       <c r="AG178" t="b">
         <v>0</v>
       </c>
@@ -19497,45 +19493,48 @@
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>129419030</v>
+        <v>129419062</v>
       </c>
       <c r="B179" t="n">
-        <v>91605</v>
+        <v>92028</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E179" t="n">
-        <v>1202</v>
+        <v>298</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Laxgröppa</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Meruliopsis rubicunda</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Litsch.) Spirin &amp; K.H.Larss.</t>
         </is>
       </c>
       <c r="I179" t="inlineStr"/>
+      <c r="J179" t="inlineStr"/>
+      <c r="K179" t="inlineStr"/>
+      <c r="N179" t="inlineStr"/>
       <c r="P179" t="inlineStr">
         <is>
           <t>Väst Norrby gamla tomt, Vstm</t>
         </is>
       </c>
       <c r="Q179" t="n">
-        <v>572414</v>
+        <v>572637</v>
       </c>
       <c r="R179" t="n">
-        <v>6635279</v>
+        <v>6635268</v>
       </c>
       <c r="S179" t="n">
         <v>10</v>
@@ -19576,6 +19575,7 @@
       <c r="AE179" t="b">
         <v>0</v>
       </c>
+      <c r="AF179" t="inlineStr"/>
       <c r="AG179" t="b">
         <v>0</v>
       </c>
@@ -19601,7 +19601,7 @@
         <v>129808810</v>
       </c>
       <c r="B180" t="n">
-        <v>98797</v>
+        <v>98798</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>

--- a/artfynd/A 12276-2023 artfynd.xlsx
+++ b/artfynd/A 12276-2023 artfynd.xlsx
@@ -19601,7 +19601,7 @@
         <v>129808810</v>
       </c>
       <c r="B180" t="n">
-        <v>98798</v>
+        <v>98815</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>

--- a/artfynd/A 12276-2023 artfynd.xlsx
+++ b/artfynd/A 12276-2023 artfynd.xlsx
@@ -19601,7 +19601,7 @@
         <v>129808810</v>
       </c>
       <c r="B180" t="n">
-        <v>98831</v>
+        <v>98833</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>

--- a/artfynd/A 12276-2023 artfynd.xlsx
+++ b/artfynd/A 12276-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY186"/>
+  <dimension ref="A1:AZ186"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112103511</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112276692</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112276693</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1074,6 +1094,11 @@
           <t>Värdefulla skogsmiljöer i Västmanlands län</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118387591</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1185,6 +1210,11 @@
           <t>Värdefulla skogsmiljöer i Västmanlands län</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118387592</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1286,6 +1316,11 @@
           <t>Värdefulla skogsmiljöer i Västmanlands län</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129419022</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1383,6 +1418,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111964109</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1480,6 +1520,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112276738</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1577,6 +1622,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112276739</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1682,6 +1732,11 @@
           <t>Värdefulla skogsmiljöer i Västmanlands län</t>
         </is>
       </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129419062</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1788,6 +1843,11 @@
           <t>Värdefulla skogsmiljöer i Västmanlands län</t>
         </is>
       </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129419049</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1885,6 +1945,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111964090</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1982,6 +2047,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111964091</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2079,6 +2149,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111964064</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2176,6 +2251,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111964066</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2273,6 +2353,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111964067</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2370,6 +2455,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111964068</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2467,6 +2557,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112103517</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2564,6 +2659,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112276703</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2661,6 +2761,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112276704</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2772,6 +2877,11 @@
           <t>Värdefulla skogsmiljöer i Västmanlands län</t>
         </is>
       </c>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118387598</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2883,6 +2993,11 @@
           <t>Värdefulla skogsmiljöer i Västmanlands län</t>
         </is>
       </c>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118387599</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2994,6 +3109,11 @@
           <t>Värdefulla skogsmiljöer i Västmanlands län</t>
         </is>
       </c>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118387600</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3091,6 +3211,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119806747</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3192,6 +3317,11 @@
           <t>Värdefulla skogsmiljöer i Västmanlands län</t>
         </is>
       </c>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129419028</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3293,6 +3423,11 @@
           <t>Värdefulla skogsmiljöer i Västmanlands län</t>
         </is>
       </c>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129419029</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3394,6 +3529,11 @@
           <t>Värdefulla skogsmiljöer i Västmanlands län</t>
         </is>
       </c>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129419030</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3495,6 +3635,11 @@
           <t>Värdefulla skogsmiljöer i Västmanlands län</t>
         </is>
       </c>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129419031</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3596,6 +3741,11 @@
           <t>Värdefulla skogsmiljöer i Västmanlands län</t>
         </is>
       </c>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129419032</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3697,6 +3847,11 @@
           <t>Värdefulla skogsmiljöer i Västmanlands län</t>
         </is>
       </c>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129419033</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3798,6 +3953,11 @@
           <t>Värdefulla skogsmiljöer i Västmanlands län</t>
         </is>
       </c>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129419034</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3899,6 +4059,11 @@
           <t>Värdefulla skogsmiljöer i Västmanlands län</t>
         </is>
       </c>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129419035</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -3996,6 +4161,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112276740</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4097,6 +4267,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111964084</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4198,6 +4373,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111964085</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4295,6 +4475,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112103563</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4392,6 +4577,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112276743</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4491,6 +4681,11 @@
       <c r="AY39" t="inlineStr">
         <is>
           <t>Värdefulla skogsmiljöer i Västmanlands län</t>
+        </is>
+      </c>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129419064</t>
         </is>
       </c>
     </row>
@@ -4594,6 +4789,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112276702</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4705,6 +4905,11 @@
           <t>Värdefulla skogsmiljöer i Västmanlands län</t>
         </is>
       </c>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118387601</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4806,6 +5011,11 @@
           <t>Värdefulla skogsmiljöer i Västmanlands län</t>
         </is>
       </c>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129419063</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -4907,6 +5117,11 @@
           <t>Värdefulla skogsmiljöer i Västmanlands län</t>
         </is>
       </c>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129419047</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5004,6 +5219,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112103523</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5101,6 +5321,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112103524</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5198,6 +5423,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112103525</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5295,6 +5525,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112103526</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5392,6 +5627,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111964081</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5489,6 +5729,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112103522</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5590,6 +5835,11 @@
           <t>Värdefulla skogsmiljöer i Västmanlands län</t>
         </is>
       </c>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129419040</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -5696,6 +5946,11 @@
           <t>Värdefulla skogsmiljöer i Västmanlands län</t>
         </is>
       </c>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129419041</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -5793,6 +6048,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112103520</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -5890,6 +6150,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119806742</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -5987,6 +6252,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111964061</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6084,6 +6354,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111964062</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6181,6 +6456,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111964063</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6278,6 +6558,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112103512</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6375,6 +6660,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112103513</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -6472,6 +6762,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112103514</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -6569,6 +6864,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112103515</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -6666,6 +6966,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112276694</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -6763,6 +7068,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112276695</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -6860,6 +7170,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112276696</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -6957,6 +7272,11 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112276697</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -7054,6 +7374,11 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112276698</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -7151,6 +7476,11 @@
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112276699</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -7248,6 +7578,11 @@
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112276700</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -7359,6 +7694,11 @@
           <t>Värdefulla skogsmiljöer i Västmanlands län</t>
         </is>
       </c>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118387593</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -7470,6 +7810,11 @@
           <t>Värdefulla skogsmiljöer i Västmanlands län</t>
         </is>
       </c>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118387595</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -7581,6 +7926,11 @@
           <t>Värdefulla skogsmiljöer i Västmanlands län</t>
         </is>
       </c>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118387596</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -7692,6 +8042,11 @@
           <t>Värdefulla skogsmiljöer i Västmanlands län</t>
         </is>
       </c>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118387597</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -7793,6 +8148,11 @@
           <t>Värdefulla skogsmiljöer i Västmanlands län</t>
         </is>
       </c>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129419023</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -7894,6 +8254,11 @@
           <t>Värdefulla skogsmiljöer i Västmanlands län</t>
         </is>
       </c>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129419024</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -7995,6 +8360,11 @@
           <t>Värdefulla skogsmiljöer i Västmanlands län</t>
         </is>
       </c>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129419025</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -8096,6 +8466,11 @@
           <t>Värdefulla skogsmiljöer i Västmanlands län</t>
         </is>
       </c>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129419026</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -8197,6 +8572,11 @@
           <t>Värdefulla skogsmiljöer i Västmanlands län</t>
         </is>
       </c>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129419027</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -8294,6 +8674,11 @@
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112276707</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -8391,6 +8776,11 @@
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119806741</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -8492,6 +8882,11 @@
           <t>Värdefulla skogsmiljöer i Västmanlands län</t>
         </is>
       </c>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129419052</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -8593,6 +8988,11 @@
           <t>Värdefulla skogsmiljöer i Västmanlands län</t>
         </is>
       </c>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129419054</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -8690,6 +9090,11 @@
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112103527</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -8792,6 +9197,11 @@
           <t>Värdefulla skogsmiljöer i Västmanlands län</t>
         </is>
       </c>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129419043</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -8889,6 +9299,11 @@
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111964088</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -8990,6 +9405,11 @@
           <t>Värdefulla skogsmiljöer i Västmanlands län</t>
         </is>
       </c>
+      <c r="AZ84" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129419044</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -9091,6 +9511,11 @@
           <t>Värdefulla skogsmiljöer i Västmanlands län</t>
         </is>
       </c>
+      <c r="AZ85" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129419036</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -9197,6 +9622,11 @@
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
+      <c r="AZ86" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111964089</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -9299,6 +9729,11 @@
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
+      <c r="AZ87" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111964079</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -9401,6 +9836,11 @@
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
+      <c r="AZ88" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111964080</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -9503,6 +9943,11 @@
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
+      <c r="AZ89" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112103521</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -9609,6 +10054,11 @@
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
+      <c r="AZ90" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112276709</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -9711,6 +10161,11 @@
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
+      <c r="AZ91" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119806739</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -9822,6 +10277,11 @@
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
+      <c r="AZ92" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111964072</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -9924,6 +10384,11 @@
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
+      <c r="AZ93" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111964073</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -10041,6 +10506,11 @@
           <t>Värdefulla skogsmiljöer i Västmanlands län</t>
         </is>
       </c>
+      <c r="AZ94" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118387612</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -10143,6 +10613,11 @@
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
+      <c r="AZ95" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111964111</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -10245,6 +10720,11 @@
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
+      <c r="AZ96" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111964112</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -10347,6 +10827,11 @@
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
+      <c r="AZ97" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111964113</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -10449,6 +10934,11 @@
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
+      <c r="AZ98" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111964114</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -10551,6 +11041,11 @@
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
+      <c r="AZ99" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112103561</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -10653,6 +11148,11 @@
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
+      <c r="AZ100" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112103562</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -10755,6 +11255,11 @@
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
+      <c r="AZ101" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112276742</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
@@ -10862,6 +11367,11 @@
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
+      <c r="AZ102" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119807129</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
@@ -10982,6 +11492,11 @@
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
+      <c r="AZ103" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112103559</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
@@ -11093,6 +11608,11 @@
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
+      <c r="AZ104" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112276737</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
@@ -11199,6 +11719,11 @@
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
+      <c r="AZ105" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111964074</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
@@ -11305,6 +11830,11 @@
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
+      <c r="AZ106" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111964075</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
@@ -11407,6 +11937,11 @@
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
+      <c r="AZ107" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112103518</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
@@ -11509,6 +12044,11 @@
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
+      <c r="AZ108" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112103519</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
@@ -11606,6 +12146,11 @@
         </is>
       </c>
       <c r="AY109" t="inlineStr"/>
+      <c r="AZ109" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112276705</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
@@ -11721,6 +12266,11 @@
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>
+      <c r="AZ110" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112103516</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
@@ -11823,6 +12373,11 @@
         </is>
       </c>
       <c r="AY111" t="inlineStr"/>
+      <c r="AZ111" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112276701</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
@@ -11930,6 +12485,11 @@
         </is>
       </c>
       <c r="AY112" t="inlineStr"/>
+      <c r="AZ112" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119806744</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
@@ -12032,6 +12592,11 @@
         </is>
       </c>
       <c r="AY113" t="inlineStr"/>
+      <c r="AZ113" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112103528</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
@@ -12134,6 +12699,11 @@
         </is>
       </c>
       <c r="AY114" t="inlineStr"/>
+      <c r="AZ114" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112103529</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
@@ -12231,6 +12801,11 @@
         </is>
       </c>
       <c r="AY115" t="inlineStr"/>
+      <c r="AZ115" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112276713</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
@@ -12333,6 +12908,11 @@
         </is>
       </c>
       <c r="AY116" t="inlineStr"/>
+      <c r="AZ116" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111964115</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
@@ -12435,6 +13015,11 @@
         </is>
       </c>
       <c r="AY117" t="inlineStr"/>
+      <c r="AZ117" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112276744</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
@@ -12550,6 +13135,11 @@
         </is>
       </c>
       <c r="AY118" t="inlineStr"/>
+      <c r="AZ118" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112276712</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
@@ -12652,6 +13242,11 @@
         </is>
       </c>
       <c r="AY119" t="inlineStr"/>
+      <c r="AZ119" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111964095</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
@@ -12754,6 +13349,11 @@
         </is>
       </c>
       <c r="AY120" t="inlineStr"/>
+      <c r="AZ120" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111964096</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
@@ -12856,6 +13456,11 @@
         </is>
       </c>
       <c r="AY121" t="inlineStr"/>
+      <c r="AZ121" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111964097</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
@@ -12958,6 +13563,11 @@
         </is>
       </c>
       <c r="AY122" t="inlineStr"/>
+      <c r="AZ122" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111964098</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
@@ -13060,6 +13670,11 @@
         </is>
       </c>
       <c r="AY123" t="inlineStr"/>
+      <c r="AZ123" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111964099</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
@@ -13162,6 +13777,11 @@
         </is>
       </c>
       <c r="AY124" t="inlineStr"/>
+      <c r="AZ124" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111964100</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
@@ -13264,6 +13884,11 @@
         </is>
       </c>
       <c r="AY125" t="inlineStr"/>
+      <c r="AZ125" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111964101</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
@@ -13366,6 +13991,11 @@
         </is>
       </c>
       <c r="AY126" t="inlineStr"/>
+      <c r="AZ126" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111964102</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
@@ -13468,6 +14098,11 @@
         </is>
       </c>
       <c r="AY127" t="inlineStr"/>
+      <c r="AZ127" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111964103</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
@@ -13570,6 +14205,11 @@
         </is>
       </c>
       <c r="AY128" t="inlineStr"/>
+      <c r="AZ128" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111964104</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
@@ -13672,6 +14312,11 @@
         </is>
       </c>
       <c r="AY129" t="inlineStr"/>
+      <c r="AZ129" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111964105</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="n">
@@ -13774,6 +14419,11 @@
         </is>
       </c>
       <c r="AY130" t="inlineStr"/>
+      <c r="AZ130" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111964106</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
@@ -13876,6 +14526,11 @@
         </is>
       </c>
       <c r="AY131" t="inlineStr"/>
+      <c r="AZ131" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111964107</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="n">
@@ -13978,6 +14633,11 @@
         </is>
       </c>
       <c r="AY132" t="inlineStr"/>
+      <c r="AZ132" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112103532</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="n">
@@ -14080,6 +14740,11 @@
         </is>
       </c>
       <c r="AY133" t="inlineStr"/>
+      <c r="AZ133" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112103533</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="n">
@@ -14182,6 +14847,11 @@
         </is>
       </c>
       <c r="AY134" t="inlineStr"/>
+      <c r="AZ134" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112103534</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="n">
@@ -14284,6 +14954,11 @@
         </is>
       </c>
       <c r="AY135" t="inlineStr"/>
+      <c r="AZ135" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112103535</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="n">
@@ -14386,6 +15061,11 @@
         </is>
       </c>
       <c r="AY136" t="inlineStr"/>
+      <c r="AZ136" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112103536</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="n">
@@ -14488,6 +15168,11 @@
         </is>
       </c>
       <c r="AY137" t="inlineStr"/>
+      <c r="AZ137" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112103537</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="n">
@@ -14590,6 +15275,11 @@
         </is>
       </c>
       <c r="AY138" t="inlineStr"/>
+      <c r="AZ138" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112103538</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="n">
@@ -14692,6 +15382,11 @@
         </is>
       </c>
       <c r="AY139" t="inlineStr"/>
+      <c r="AZ139" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112103539</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="n">
@@ -14794,6 +15489,11 @@
         </is>
       </c>
       <c r="AY140" t="inlineStr"/>
+      <c r="AZ140" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112103540</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="n">
@@ -14896,6 +15596,11 @@
         </is>
       </c>
       <c r="AY141" t="inlineStr"/>
+      <c r="AZ141" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112103541</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="n">
@@ -14998,6 +15703,11 @@
         </is>
       </c>
       <c r="AY142" t="inlineStr"/>
+      <c r="AZ142" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112103542</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="n">
@@ -15100,6 +15810,11 @@
         </is>
       </c>
       <c r="AY143" t="inlineStr"/>
+      <c r="AZ143" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112103543</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="n">
@@ -15202,6 +15917,11 @@
         </is>
       </c>
       <c r="AY144" t="inlineStr"/>
+      <c r="AZ144" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112103544</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="n">
@@ -15304,6 +16024,11 @@
         </is>
       </c>
       <c r="AY145" t="inlineStr"/>
+      <c r="AZ145" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112103545</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="n">
@@ -15406,6 +16131,11 @@
         </is>
       </c>
       <c r="AY146" t="inlineStr"/>
+      <c r="AZ146" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112103546</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="n">
@@ -15508,6 +16238,11 @@
         </is>
       </c>
       <c r="AY147" t="inlineStr"/>
+      <c r="AZ147" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112103547</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="n">
@@ -15610,6 +16345,11 @@
         </is>
       </c>
       <c r="AY148" t="inlineStr"/>
+      <c r="AZ148" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112103548</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="n">
@@ -15712,6 +16452,11 @@
         </is>
       </c>
       <c r="AY149" t="inlineStr"/>
+      <c r="AZ149" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112103549</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="n">
@@ -15814,6 +16559,11 @@
         </is>
       </c>
       <c r="AY150" t="inlineStr"/>
+      <c r="AZ150" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112103550</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="n">
@@ -15916,6 +16666,11 @@
         </is>
       </c>
       <c r="AY151" t="inlineStr"/>
+      <c r="AZ151" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112103551</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="n">
@@ -16018,6 +16773,11 @@
         </is>
       </c>
       <c r="AY152" t="inlineStr"/>
+      <c r="AZ152" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112103552</t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="n">
@@ -16120,6 +16880,11 @@
         </is>
       </c>
       <c r="AY153" t="inlineStr"/>
+      <c r="AZ153" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112103553</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="n">
@@ -16222,6 +16987,11 @@
         </is>
       </c>
       <c r="AY154" t="inlineStr"/>
+      <c r="AZ154" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112103554</t>
+        </is>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="n">
@@ -16324,6 +17094,11 @@
         </is>
       </c>
       <c r="AY155" t="inlineStr"/>
+      <c r="AZ155" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112103555</t>
+        </is>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="n">
@@ -16426,6 +17201,11 @@
         </is>
       </c>
       <c r="AY156" t="inlineStr"/>
+      <c r="AZ156" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112276714</t>
+        </is>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="n">
@@ -16528,6 +17308,11 @@
         </is>
       </c>
       <c r="AY157" t="inlineStr"/>
+      <c r="AZ157" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112276715</t>
+        </is>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="n">
@@ -16630,6 +17415,11 @@
         </is>
       </c>
       <c r="AY158" t="inlineStr"/>
+      <c r="AZ158" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112276716</t>
+        </is>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="n">
@@ -16732,6 +17522,11 @@
         </is>
       </c>
       <c r="AY159" t="inlineStr"/>
+      <c r="AZ159" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112276717</t>
+        </is>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="n">
@@ -16834,6 +17629,11 @@
         </is>
       </c>
       <c r="AY160" t="inlineStr"/>
+      <c r="AZ160" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112276718</t>
+        </is>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="n">
@@ -16936,6 +17736,11 @@
         </is>
       </c>
       <c r="AY161" t="inlineStr"/>
+      <c r="AZ161" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112276719</t>
+        </is>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="n">
@@ -17038,6 +17843,11 @@
         </is>
       </c>
       <c r="AY162" t="inlineStr"/>
+      <c r="AZ162" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112276720</t>
+        </is>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="n">
@@ -17140,6 +17950,11 @@
         </is>
       </c>
       <c r="AY163" t="inlineStr"/>
+      <c r="AZ163" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112276722</t>
+        </is>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="n">
@@ -17242,6 +18057,11 @@
         </is>
       </c>
       <c r="AY164" t="inlineStr"/>
+      <c r="AZ164" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112276723</t>
+        </is>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="n">
@@ -17344,6 +18164,11 @@
         </is>
       </c>
       <c r="AY165" t="inlineStr"/>
+      <c r="AZ165" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112276724</t>
+        </is>
+      </c>
     </row>
     <row r="166">
       <c r="A166" t="n">
@@ -17446,6 +18271,11 @@
         </is>
       </c>
       <c r="AY166" t="inlineStr"/>
+      <c r="AZ166" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112276725</t>
+        </is>
+      </c>
     </row>
     <row r="167">
       <c r="A167" t="n">
@@ -17548,6 +18378,11 @@
         </is>
       </c>
       <c r="AY167" t="inlineStr"/>
+      <c r="AZ167" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112276726</t>
+        </is>
+      </c>
     </row>
     <row r="168">
       <c r="A168" t="n">
@@ -17650,6 +18485,11 @@
         </is>
       </c>
       <c r="AY168" t="inlineStr"/>
+      <c r="AZ168" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112276727</t>
+        </is>
+      </c>
     </row>
     <row r="169">
       <c r="A169" t="n">
@@ -17752,6 +18592,11 @@
         </is>
       </c>
       <c r="AY169" t="inlineStr"/>
+      <c r="AZ169" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112276728</t>
+        </is>
+      </c>
     </row>
     <row r="170">
       <c r="A170" t="n">
@@ -17854,6 +18699,11 @@
         </is>
       </c>
       <c r="AY170" t="inlineStr"/>
+      <c r="AZ170" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112276729</t>
+        </is>
+      </c>
     </row>
     <row r="171">
       <c r="A171" t="n">
@@ -17956,6 +18806,11 @@
         </is>
       </c>
       <c r="AY171" t="inlineStr"/>
+      <c r="AZ171" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112276730</t>
+        </is>
+      </c>
     </row>
     <row r="172">
       <c r="A172" t="n">
@@ -18058,6 +18913,11 @@
         </is>
       </c>
       <c r="AY172" t="inlineStr"/>
+      <c r="AZ172" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112276731</t>
+        </is>
+      </c>
     </row>
     <row r="173">
       <c r="A173" t="n">
@@ -18160,6 +19020,11 @@
         </is>
       </c>
       <c r="AY173" t="inlineStr"/>
+      <c r="AZ173" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112276732</t>
+        </is>
+      </c>
     </row>
     <row r="174">
       <c r="A174" t="n">
@@ -18262,6 +19127,11 @@
         </is>
       </c>
       <c r="AY174" t="inlineStr"/>
+      <c r="AZ174" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112276733</t>
+        </is>
+      </c>
     </row>
     <row r="175">
       <c r="A175" t="n">
@@ -18364,6 +19234,11 @@
         </is>
       </c>
       <c r="AY175" t="inlineStr"/>
+      <c r="AZ175" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112276735</t>
+        </is>
+      </c>
     </row>
     <row r="176">
       <c r="A176" t="n">
@@ -18466,6 +19341,11 @@
         </is>
       </c>
       <c r="AY176" t="inlineStr"/>
+      <c r="AZ176" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112276736</t>
+        </is>
+      </c>
     </row>
     <row r="177">
       <c r="A177" t="n">
@@ -18577,6 +19457,11 @@
           <t>Floraväkteri Sverige</t>
         </is>
       </c>
+      <c r="AZ177" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113544517</t>
+        </is>
+      </c>
     </row>
     <row r="178">
       <c r="A178" t="n">
@@ -18683,6 +19568,11 @@
           <t>Värdefulla skogsmiljöer i Västmanlands län</t>
         </is>
       </c>
+      <c r="AZ178" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118387606</t>
+        </is>
+      </c>
     </row>
     <row r="179">
       <c r="A179" t="n">
@@ -18789,6 +19679,11 @@
           <t>Värdefulla skogsmiljöer i Västmanlands län</t>
         </is>
       </c>
+      <c r="AZ179" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118387607</t>
+        </is>
+      </c>
     </row>
     <row r="180">
       <c r="A180" t="n">
@@ -18895,6 +19790,11 @@
           <t>Värdefulla skogsmiljöer i Västmanlands län</t>
         </is>
       </c>
+      <c r="AZ180" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118387608</t>
+        </is>
+      </c>
     </row>
     <row r="181">
       <c r="A181" t="n">
@@ -19001,6 +19901,11 @@
           <t>Värdefulla skogsmiljöer i Västmanlands län</t>
         </is>
       </c>
+      <c r="AZ181" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118387609</t>
+        </is>
+      </c>
     </row>
     <row r="182">
       <c r="A182" t="n">
@@ -19107,6 +20012,11 @@
           <t>Värdefulla skogsmiljöer i Västmanlands län</t>
         </is>
       </c>
+      <c r="AZ182" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118387610</t>
+        </is>
+      </c>
     </row>
     <row r="183">
       <c r="A183" t="n">
@@ -19213,6 +20123,11 @@
         </is>
       </c>
       <c r="AY183" t="inlineStr"/>
+      <c r="AZ183" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119806745</t>
+        </is>
+      </c>
     </row>
     <row r="184">
       <c r="A184" t="n">
@@ -19319,6 +20234,11 @@
         </is>
       </c>
       <c r="AY184" t="inlineStr"/>
+      <c r="AZ184" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119806746</t>
+        </is>
+      </c>
     </row>
     <row r="185">
       <c r="A185" t="n">
@@ -19420,6 +20340,11 @@
           <t>Värdefulla skogsmiljöer i Västmanlands län</t>
         </is>
       </c>
+      <c r="AZ185" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129419048</t>
+        </is>
+      </c>
     </row>
     <row r="186">
       <c r="A186" t="n">
@@ -19544,8 +20469,200 @@
           <t>Floraväkteri Sverige</t>
         </is>
       </c>
+      <c r="AZ186" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129808810</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ87" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ88" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ89" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ90" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ91" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ92" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ93" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ94" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ95" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ96" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ97" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ98" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ99" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ100" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ101" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ102" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ103" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ104" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ105" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ106" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ107" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ108" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ109" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ110" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ111" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ112" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ113" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ114" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ115" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ116" r:id="rId115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ117" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ118" r:id="rId117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ119" r:id="rId118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ120" r:id="rId119"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ121" r:id="rId120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ122" r:id="rId121"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ123" r:id="rId122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ124" r:id="rId123"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ125" r:id="rId124"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ126" r:id="rId125"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ127" r:id="rId126"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ128" r:id="rId127"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ129" r:id="rId128"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ130" r:id="rId129"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ131" r:id="rId130"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ132" r:id="rId131"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ133" r:id="rId132"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ134" r:id="rId133"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ135" r:id="rId134"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ136" r:id="rId135"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ137" r:id="rId136"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ138" r:id="rId137"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ139" r:id="rId138"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ140" r:id="rId139"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ141" r:id="rId140"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ142" r:id="rId141"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ143" r:id="rId142"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ144" r:id="rId143"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ145" r:id="rId144"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ146" r:id="rId145"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ147" r:id="rId146"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ148" r:id="rId147"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ149" r:id="rId148"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ150" r:id="rId149"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ151" r:id="rId150"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ152" r:id="rId151"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ153" r:id="rId152"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ154" r:id="rId153"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ155" r:id="rId154"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ156" r:id="rId155"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ157" r:id="rId156"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ158" r:id="rId157"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ159" r:id="rId158"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ160" r:id="rId159"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ161" r:id="rId160"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ162" r:id="rId161"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ163" r:id="rId162"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ164" r:id="rId163"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ165" r:id="rId164"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ166" r:id="rId165"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ167" r:id="rId166"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ168" r:id="rId167"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ169" r:id="rId168"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ170" r:id="rId169"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ171" r:id="rId170"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ172" r:id="rId171"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ173" r:id="rId172"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ174" r:id="rId173"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ175" r:id="rId174"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ176" r:id="rId175"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ177" r:id="rId176"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ178" r:id="rId177"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ179" r:id="rId178"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ180" r:id="rId179"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ181" r:id="rId180"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ182" r:id="rId181"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ183" r:id="rId182"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ184" r:id="rId183"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ185" r:id="rId184"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ186" r:id="rId185"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>